--- a/data/seat/06-junio2026.xlsx
+++ b/data/seat/06-junio2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoefe.sharepoint.com/sites/GOFEFEVALPARASO/Documentos compartidos/UNIDAD DE GESTION/Datos Operacionales/Energía/SEAT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="6_{022934C4-186F-4BE2-B034-0206DAC59087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C514F52-39CD-47E7-9923-63B87C131B6E}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="6_{022934C4-186F-4BE2-B034-0206DAC59087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44CA7CAF-F811-49F2-9643-F63B369A3379}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2124,6 +2124,36 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2142,25 +2172,46 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2173,57 +2224,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2322,7 +2322,77 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="138">
+  <dxfs count="140">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3111,62 +3181,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4574,7 +4588,7 @@
                   <c:v>2483</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0</c:v>
+                  <c:v>2541.4300000000003</c:v>
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>0</c:v>
@@ -7471,293 +7485,293 @@
       <c r="A1" s="126">
         <v>1.1111111E+55</v>
       </c>
-      <c r="B1" s="236" t="s">
+      <c r="B1" s="218" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="127"/>
-      <c r="D1" s="238" t="s">
+      <c r="D1" s="220" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="239"/>
-      <c r="F1" s="239"/>
-      <c r="G1" s="239"/>
-      <c r="H1" s="239"/>
-      <c r="I1" s="239"/>
-      <c r="J1" s="239"/>
-      <c r="K1" s="239"/>
-      <c r="L1" s="239"/>
-      <c r="M1" s="239"/>
-      <c r="N1" s="239"/>
-      <c r="O1" s="240"/>
-      <c r="P1" s="241"/>
+      <c r="E1" s="221"/>
+      <c r="F1" s="221"/>
+      <c r="G1" s="221"/>
+      <c r="H1" s="221"/>
+      <c r="I1" s="221"/>
+      <c r="J1" s="221"/>
+      <c r="K1" s="221"/>
+      <c r="L1" s="221"/>
+      <c r="M1" s="221"/>
+      <c r="N1" s="221"/>
+      <c r="O1" s="222"/>
+      <c r="P1" s="223"/>
       <c r="Q1" s="128"/>
-      <c r="R1" s="218" t="s">
+      <c r="R1" s="228" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="219"/>
-      <c r="T1" s="219"/>
-      <c r="U1" s="219"/>
-      <c r="V1" s="219"/>
-      <c r="W1" s="219"/>
-      <c r="X1" s="219"/>
-      <c r="Y1" s="219"/>
-      <c r="Z1" s="219"/>
-      <c r="AA1" s="220"/>
+      <c r="S1" s="229"/>
+      <c r="T1" s="229"/>
+      <c r="U1" s="229"/>
+      <c r="V1" s="229"/>
+      <c r="W1" s="229"/>
+      <c r="X1" s="229"/>
+      <c r="Y1" s="229"/>
+      <c r="Z1" s="229"/>
+      <c r="AA1" s="230"/>
       <c r="AB1" s="129"/>
-      <c r="AC1" s="218" t="s">
+      <c r="AC1" s="228" t="s">
         <v>3</v>
       </c>
-      <c r="AD1" s="219"/>
-      <c r="AE1" s="219"/>
-      <c r="AF1" s="219"/>
-      <c r="AG1" s="219"/>
-      <c r="AH1" s="219"/>
-      <c r="AI1" s="219"/>
-      <c r="AJ1" s="219"/>
-      <c r="AK1" s="220"/>
+      <c r="AD1" s="229"/>
+      <c r="AE1" s="229"/>
+      <c r="AF1" s="229"/>
+      <c r="AG1" s="229"/>
+      <c r="AH1" s="229"/>
+      <c r="AI1" s="229"/>
+      <c r="AJ1" s="229"/>
+      <c r="AK1" s="230"/>
       <c r="AL1" s="130"/>
-      <c r="AM1" s="218" t="s">
+      <c r="AM1" s="228" t="s">
         <v>4</v>
       </c>
-      <c r="AN1" s="219"/>
-      <c r="AO1" s="219"/>
-      <c r="AP1" s="219"/>
-      <c r="AQ1" s="219"/>
-      <c r="AR1" s="219"/>
-      <c r="AS1" s="219"/>
-      <c r="AT1" s="219"/>
-      <c r="AU1" s="220"/>
+      <c r="AN1" s="229"/>
+      <c r="AO1" s="229"/>
+      <c r="AP1" s="229"/>
+      <c r="AQ1" s="229"/>
+      <c r="AR1" s="229"/>
+      <c r="AS1" s="229"/>
+      <c r="AT1" s="229"/>
+      <c r="AU1" s="230"/>
       <c r="AV1" s="130"/>
-      <c r="AW1" s="218" t="s">
+      <c r="AW1" s="228" t="s">
         <v>57</v>
       </c>
-      <c r="AX1" s="219"/>
-      <c r="AY1" s="219"/>
-      <c r="AZ1" s="219"/>
-      <c r="BA1" s="219"/>
-      <c r="BB1" s="219"/>
-      <c r="BC1" s="219"/>
-      <c r="BD1" s="219"/>
-      <c r="BE1" s="219"/>
-      <c r="BF1" s="219"/>
-      <c r="BG1" s="219"/>
-      <c r="BH1" s="220"/>
+      <c r="AX1" s="229"/>
+      <c r="AY1" s="229"/>
+      <c r="AZ1" s="229"/>
+      <c r="BA1" s="229"/>
+      <c r="BB1" s="229"/>
+      <c r="BC1" s="229"/>
+      <c r="BD1" s="229"/>
+      <c r="BE1" s="229"/>
+      <c r="BF1" s="229"/>
+      <c r="BG1" s="229"/>
+      <c r="BH1" s="230"/>
       <c r="BI1" s="130"/>
-      <c r="BJ1" s="218" t="s">
+      <c r="BJ1" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="BK1" s="219"/>
-      <c r="BL1" s="219"/>
-      <c r="BM1" s="219"/>
-      <c r="BN1" s="219"/>
-      <c r="BO1" s="219"/>
-      <c r="BP1" s="219"/>
-      <c r="BQ1" s="219"/>
-      <c r="BR1" s="220"/>
+      <c r="BK1" s="229"/>
+      <c r="BL1" s="229"/>
+      <c r="BM1" s="229"/>
+      <c r="BN1" s="229"/>
+      <c r="BO1" s="229"/>
+      <c r="BP1" s="229"/>
+      <c r="BQ1" s="229"/>
+      <c r="BR1" s="230"/>
       <c r="BS1" s="131"/>
     </row>
     <row r="2" spans="1:71" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="236"/>
+      <c r="B2" s="218"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="242"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="243"/>
-      <c r="H2" s="243"/>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
-      <c r="M2" s="243"/>
-      <c r="N2" s="243"/>
-      <c r="O2" s="244"/>
-      <c r="P2" s="245"/>
+      <c r="D2" s="224"/>
+      <c r="E2" s="225"/>
+      <c r="F2" s="225"/>
+      <c r="G2" s="225"/>
+      <c r="H2" s="225"/>
+      <c r="I2" s="225"/>
+      <c r="J2" s="225"/>
+      <c r="K2" s="225"/>
+      <c r="L2" s="225"/>
+      <c r="M2" s="225"/>
+      <c r="N2" s="225"/>
+      <c r="O2" s="226"/>
+      <c r="P2" s="227"/>
       <c r="Q2" s="57"/>
-      <c r="R2" s="221"/>
-      <c r="S2" s="222"/>
-      <c r="T2" s="222"/>
-      <c r="U2" s="222"/>
-      <c r="V2" s="222"/>
-      <c r="W2" s="222"/>
-      <c r="X2" s="222"/>
-      <c r="Y2" s="222"/>
-      <c r="Z2" s="222"/>
-      <c r="AA2" s="223"/>
+      <c r="R2" s="231"/>
+      <c r="S2" s="232"/>
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
+      <c r="AA2" s="233"/>
       <c r="AB2" s="59"/>
-      <c r="AC2" s="221"/>
-      <c r="AD2" s="222"/>
-      <c r="AE2" s="222"/>
-      <c r="AF2" s="222"/>
-      <c r="AG2" s="222"/>
-      <c r="AH2" s="222"/>
-      <c r="AI2" s="222"/>
-      <c r="AJ2" s="222"/>
-      <c r="AK2" s="223"/>
+      <c r="AC2" s="231"/>
+      <c r="AD2" s="232"/>
+      <c r="AE2" s="232"/>
+      <c r="AF2" s="232"/>
+      <c r="AG2" s="232"/>
+      <c r="AH2" s="232"/>
+      <c r="AI2" s="232"/>
+      <c r="AJ2" s="232"/>
+      <c r="AK2" s="233"/>
       <c r="AL2" s="58"/>
-      <c r="AM2" s="221"/>
-      <c r="AN2" s="222"/>
-      <c r="AO2" s="222"/>
-      <c r="AP2" s="222"/>
-      <c r="AQ2" s="222"/>
-      <c r="AR2" s="222"/>
-      <c r="AS2" s="222"/>
-      <c r="AT2" s="222"/>
-      <c r="AU2" s="223"/>
+      <c r="AM2" s="231"/>
+      <c r="AN2" s="232"/>
+      <c r="AO2" s="232"/>
+      <c r="AP2" s="232"/>
+      <c r="AQ2" s="232"/>
+      <c r="AR2" s="232"/>
+      <c r="AS2" s="232"/>
+      <c r="AT2" s="232"/>
+      <c r="AU2" s="233"/>
       <c r="AV2" s="58"/>
-      <c r="AW2" s="221"/>
-      <c r="AX2" s="222"/>
-      <c r="AY2" s="222"/>
-      <c r="AZ2" s="222"/>
-      <c r="BA2" s="222"/>
-      <c r="BB2" s="222"/>
-      <c r="BC2" s="222"/>
-      <c r="BD2" s="222"/>
-      <c r="BE2" s="222"/>
-      <c r="BF2" s="222"/>
-      <c r="BG2" s="222"/>
-      <c r="BH2" s="223"/>
+      <c r="AW2" s="231"/>
+      <c r="AX2" s="232"/>
+      <c r="AY2" s="232"/>
+      <c r="AZ2" s="232"/>
+      <c r="BA2" s="232"/>
+      <c r="BB2" s="232"/>
+      <c r="BC2" s="232"/>
+      <c r="BD2" s="232"/>
+      <c r="BE2" s="232"/>
+      <c r="BF2" s="232"/>
+      <c r="BG2" s="232"/>
+      <c r="BH2" s="233"/>
       <c r="BI2" s="58"/>
-      <c r="BJ2" s="221"/>
-      <c r="BK2" s="222"/>
-      <c r="BL2" s="222"/>
-      <c r="BM2" s="222"/>
-      <c r="BN2" s="222"/>
-      <c r="BO2" s="222"/>
-      <c r="BP2" s="222"/>
-      <c r="BQ2" s="222"/>
-      <c r="BR2" s="223"/>
+      <c r="BJ2" s="231"/>
+      <c r="BK2" s="232"/>
+      <c r="BL2" s="232"/>
+      <c r="BM2" s="232"/>
+      <c r="BN2" s="232"/>
+      <c r="BO2" s="232"/>
+      <c r="BP2" s="232"/>
+      <c r="BQ2" s="232"/>
+      <c r="BR2" s="233"/>
       <c r="BS2" s="134"/>
     </row>
     <row r="3" spans="1:71" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="236"/>
+      <c r="B3" s="218"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="224" t="s">
+      <c r="D3" s="237" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="224" t="s">
+      <c r="E3" s="237" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="224" t="s">
+      <c r="F3" s="237" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="224" t="s">
+      <c r="G3" s="237" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="224" t="s">
+      <c r="H3" s="237" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="246" t="s">
+      <c r="I3" s="239" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="247"/>
-      <c r="K3" s="248"/>
-      <c r="L3" s="249"/>
-      <c r="M3" s="246" t="s">
+      <c r="J3" s="240"/>
+      <c r="K3" s="241"/>
+      <c r="L3" s="242"/>
+      <c r="M3" s="239" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="247"/>
-      <c r="O3" s="248"/>
-      <c r="P3" s="249"/>
+      <c r="N3" s="240"/>
+      <c r="O3" s="241"/>
+      <c r="P3" s="242"/>
       <c r="Q3" s="57"/>
-      <c r="R3" s="228" t="s">
+      <c r="R3" s="243" t="s">
         <v>13</v>
       </c>
-      <c r="S3" s="229"/>
-      <c r="T3" s="250"/>
-      <c r="U3" s="250"/>
-      <c r="V3" s="228" t="s">
+      <c r="S3" s="235"/>
+      <c r="T3" s="244"/>
+      <c r="U3" s="244"/>
+      <c r="V3" s="243" t="s">
         <v>14</v>
       </c>
-      <c r="W3" s="229"/>
-      <c r="X3" s="229"/>
-      <c r="Y3" s="229"/>
-      <c r="Z3" s="229"/>
-      <c r="AA3" s="230"/>
+      <c r="W3" s="235"/>
+      <c r="X3" s="235"/>
+      <c r="Y3" s="235"/>
+      <c r="Z3" s="235"/>
+      <c r="AA3" s="236"/>
       <c r="AB3" s="59"/>
-      <c r="AC3" s="226" t="s">
+      <c r="AC3" s="245" t="s">
         <v>15</v>
       </c>
-      <c r="AD3" s="251" t="s">
+      <c r="AD3" s="247" t="s">
         <v>9</v>
       </c>
-      <c r="AE3" s="228" t="s">
+      <c r="AE3" s="243" t="s">
         <v>13</v>
       </c>
-      <c r="AF3" s="229"/>
-      <c r="AG3" s="230"/>
-      <c r="AH3" s="228" t="s">
+      <c r="AF3" s="235"/>
+      <c r="AG3" s="236"/>
+      <c r="AH3" s="243" t="s">
         <v>14</v>
       </c>
-      <c r="AI3" s="229"/>
-      <c r="AJ3" s="229"/>
-      <c r="AK3" s="230"/>
+      <c r="AI3" s="235"/>
+      <c r="AJ3" s="235"/>
+      <c r="AK3" s="236"/>
       <c r="AL3" s="58"/>
-      <c r="AM3" s="231" t="s">
+      <c r="AM3" s="248" t="s">
         <v>15</v>
       </c>
-      <c r="AN3" s="226" t="s">
+      <c r="AN3" s="245" t="s">
         <v>9</v>
       </c>
-      <c r="AO3" s="235" t="s">
+      <c r="AO3" s="234" t="s">
         <v>13</v>
       </c>
-      <c r="AP3" s="229"/>
-      <c r="AQ3" s="230"/>
-      <c r="AR3" s="228" t="s">
+      <c r="AP3" s="235"/>
+      <c r="AQ3" s="236"/>
+      <c r="AR3" s="243" t="s">
         <v>14</v>
       </c>
-      <c r="AS3" s="229"/>
-      <c r="AT3" s="229"/>
-      <c r="AU3" s="230"/>
+      <c r="AS3" s="235"/>
+      <c r="AT3" s="235"/>
+      <c r="AU3" s="236"/>
       <c r="AV3" s="58"/>
-      <c r="AW3" s="226" t="s">
+      <c r="AW3" s="245" t="s">
         <v>15</v>
       </c>
-      <c r="AX3" s="226" t="s">
+      <c r="AX3" s="245" t="s">
         <v>9</v>
       </c>
-      <c r="AY3" s="235" t="s">
+      <c r="AY3" s="234" t="s">
         <v>13</v>
       </c>
-      <c r="AZ3" s="235"/>
-      <c r="BA3" s="229"/>
-      <c r="BB3" s="230"/>
-      <c r="BC3" s="228" t="s">
+      <c r="AZ3" s="234"/>
+      <c r="BA3" s="235"/>
+      <c r="BB3" s="236"/>
+      <c r="BC3" s="243" t="s">
         <v>14</v>
       </c>
-      <c r="BD3" s="235"/>
-      <c r="BE3" s="235"/>
-      <c r="BF3" s="229"/>
-      <c r="BG3" s="229"/>
-      <c r="BH3" s="230"/>
+      <c r="BD3" s="234"/>
+      <c r="BE3" s="234"/>
+      <c r="BF3" s="235"/>
+      <c r="BG3" s="235"/>
+      <c r="BH3" s="236"/>
       <c r="BI3" s="58"/>
-      <c r="BJ3" s="231" t="s">
+      <c r="BJ3" s="248" t="s">
         <v>16</v>
       </c>
-      <c r="BK3" s="226" t="s">
+      <c r="BK3" s="245" t="s">
         <v>17</v>
       </c>
-      <c r="BL3" s="232" t="s">
+      <c r="BL3" s="249" t="s">
         <v>18</v>
       </c>
-      <c r="BM3" s="233"/>
-      <c r="BN3" s="234"/>
-      <c r="BO3" s="235" t="s">
+      <c r="BM3" s="250"/>
+      <c r="BN3" s="251"/>
+      <c r="BO3" s="234" t="s">
         <v>14</v>
       </c>
-      <c r="BP3" s="229"/>
-      <c r="BQ3" s="229"/>
-      <c r="BR3" s="230"/>
+      <c r="BP3" s="235"/>
+      <c r="BQ3" s="235"/>
+      <c r="BR3" s="236"/>
       <c r="BS3" s="134"/>
     </row>
     <row r="4" spans="1:71" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="237"/>
+      <c r="B4" s="219"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="225"/>
-      <c r="E4" s="225"/>
-      <c r="F4" s="225"/>
-      <c r="G4" s="225"/>
-      <c r="H4" s="225"/>
+      <c r="D4" s="238"/>
+      <c r="E4" s="238"/>
+      <c r="F4" s="238"/>
+      <c r="G4" s="238"/>
+      <c r="H4" s="238"/>
       <c r="I4" s="79" t="s">
         <v>3</v>
       </c>
@@ -7814,8 +7828,8 @@
         <v>24</v>
       </c>
       <c r="AB4" s="59"/>
-      <c r="AC4" s="227"/>
-      <c r="AD4" s="219"/>
+      <c r="AC4" s="246"/>
+      <c r="AD4" s="229"/>
       <c r="AE4" s="61" t="s">
         <v>27</v>
       </c>
@@ -7838,8 +7852,8 @@
         <v>24</v>
       </c>
       <c r="AL4" s="60"/>
-      <c r="AM4" s="218"/>
-      <c r="AN4" s="227"/>
+      <c r="AM4" s="228"/>
+      <c r="AN4" s="246"/>
       <c r="AO4" s="122" t="s">
         <v>27</v>
       </c>
@@ -7862,8 +7876,8 @@
         <v>24</v>
       </c>
       <c r="AV4" s="60"/>
-      <c r="AW4" s="227"/>
-      <c r="AX4" s="227"/>
+      <c r="AW4" s="246"/>
+      <c r="AX4" s="246"/>
       <c r="AY4" s="122" t="s">
         <v>27</v>
       </c>
@@ -7895,8 +7909,8 @@
         <v>24</v>
       </c>
       <c r="BI4" s="60"/>
-      <c r="BJ4" s="218"/>
-      <c r="BK4" s="227"/>
+      <c r="BJ4" s="228"/>
+      <c r="BK4" s="246"/>
       <c r="BL4" s="122" t="s">
         <v>32</v>
       </c>
@@ -9293,11 +9307,11 @@
         <v>46178</v>
       </c>
       <c r="AC11" s="75">
-        <f t="shared" ref="AC11:AC34" si="46">+AF11/AE11</f>
+        <f t="shared" ref="AC11:AC35" si="46">+AF11/AE11</f>
         <v>1</v>
       </c>
       <c r="AD11" s="161">
-        <f t="shared" ref="AD11:AD34" si="47">+AG11/AE11</f>
+        <f t="shared" ref="AD11:AD35" si="47">+AG11/AE11</f>
         <v>0</v>
       </c>
       <c r="AE11" s="162">
@@ -9327,7 +9341,7 @@
         <v>46178</v>
       </c>
       <c r="AM11" s="76">
-        <f t="shared" ref="AM11:AM34" si="48">+AP11/AO11</f>
+        <f t="shared" ref="AM11:AM35" si="48">+AP11/AO11</f>
         <v>0.60748468606431849</v>
       </c>
       <c r="AN11" s="75">
@@ -9361,11 +9375,11 @@
         <v>46178</v>
       </c>
       <c r="AW11" s="109">
-        <f t="shared" ref="AW11:AW34" si="50">BA11/AZ11</f>
+        <f t="shared" ref="AW11:AW35" si="50">BA11/AZ11</f>
         <v>0.63236836584854206</v>
       </c>
       <c r="AX11" s="109">
-        <f t="shared" ref="AX11:AX34" si="51">BB11/AZ11</f>
+        <f t="shared" ref="AX11:AX35" si="51">BB11/AZ11</f>
         <v>0.36763163415145794</v>
       </c>
       <c r="AY11" s="110">
@@ -9406,15 +9420,15 @@
         <v>46178</v>
       </c>
       <c r="BJ11" s="77">
-        <f t="shared" ref="BJ11:BJ34" si="52">+BM11/BL11</f>
+        <f t="shared" ref="BJ11:BJ35" si="52">+BM11/BL11</f>
         <v>0.60549950105333183</v>
       </c>
       <c r="BK11" s="75">
-        <f t="shared" ref="BK11:BK34" si="53">+BN11/BL11</f>
+        <f t="shared" ref="BK11:BK35" si="53">+BN11/BL11</f>
         <v>0.39450049894666817</v>
       </c>
       <c r="BL11" s="78">
-        <f t="shared" ref="BL11:BL34" si="54">BM11+BN11</f>
+        <f t="shared" ref="BL11:BL35" si="54">BM11+BN11</f>
         <v>36076</v>
       </c>
       <c r="BM11" s="154">
@@ -14970,171 +14984,244 @@
     </row>
     <row r="35" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14"/>
-      <c r="B35" s="55">
+      <c r="B35" s="167">
         <f t="shared" si="37"/>
         <v>46202</v>
       </c>
-      <c r="C35" s="163"/>
+      <c r="C35" s="217"/>
       <c r="D35" s="86">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E35" s="158" t="e">
+        <v>28428</v>
+      </c>
+      <c r="E35" s="158">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.75188863092725489</v>
       </c>
       <c r="F35" s="86">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G35" s="158" t="e">
+        <v>21374.690000000002</v>
+      </c>
+      <c r="G35" s="158">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>0.24811136907274517</v>
       </c>
       <c r="H35" s="145">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I35" s="159" t="e">
+        <v>7053.3099999999995</v>
+      </c>
+      <c r="I35" s="159">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J35" s="158" t="e">
+        <v>6.7205237625026545E-2</v>
+      </c>
+      <c r="J35" s="158">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K35" s="158" t="e">
+        <v>0.16864829211924529</v>
+      </c>
+      <c r="K35" s="158">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L35" s="160" t="e">
+        <v>0.18637679263486664</v>
+      </c>
+      <c r="L35" s="160">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M35" s="145" t="e">
+        <v>0.61789051366991132</v>
+      </c>
+      <c r="M35" s="145">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N35" s="145" t="e">
+        <v>1824.7062080665021</v>
+      </c>
+      <c r="N35" s="145">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O35" s="145" t="e">
+        <v>4579.0119414026585</v>
+      </c>
+      <c r="O35" s="145">
         <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P35" s="145" t="e">
+        <v>5060.3628910274228</v>
+      </c>
+      <c r="P35" s="145">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q35" s="55">
+        <v>16776.49980928018</v>
+      </c>
+      <c r="Q35" s="167">
         <f t="shared" si="38"/>
         <v>46202</v>
       </c>
-      <c r="R35" s="138"/>
-      <c r="S35" s="139"/>
-      <c r="T35" s="139"/>
-      <c r="U35" s="139"/>
-      <c r="V35" s="140"/>
-      <c r="W35" s="141"/>
-      <c r="X35" s="140"/>
-      <c r="Y35" s="141"/>
-      <c r="Z35" s="140"/>
-      <c r="AA35" s="141"/>
-      <c r="AB35" s="55">
+      <c r="R35" s="138">
+        <v>28428</v>
+      </c>
+      <c r="S35" s="139">
+        <v>0</v>
+      </c>
+      <c r="T35" s="139">
+        <v>27151.25</v>
+      </c>
+      <c r="U35" s="139">
+        <v>0</v>
+      </c>
+      <c r="V35" s="140">
+        <v>5689.24</v>
+      </c>
+      <c r="W35" s="141">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="X35" s="140">
+        <v>1984</v>
+      </c>
+      <c r="Y35" s="141">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="Z35" s="140">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="141">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="167">
         <f t="shared" si="39"/>
         <v>46202</v>
       </c>
-      <c r="AC35" s="75" t="e">
-        <f t="shared" ref="AC35" si="63">+AF35/AE35</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD35" s="161" t="e">
-        <f t="shared" ref="AD35" si="64">+AG35/AE35</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE35" s="162"/>
+      <c r="AC35" s="75">
+        <f t="shared" si="46"/>
+        <v>1</v>
+      </c>
+      <c r="AD35" s="161">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="AE35" s="162">
+        <v>2094.88</v>
+      </c>
       <c r="AF35" s="117">
-        <f t="shared" ref="AF35" si="65">AE35-AG35</f>
-        <v>0</v>
-      </c>
-      <c r="AG35" s="146"/>
-      <c r="AH35" s="147"/>
-      <c r="AI35" s="148"/>
-      <c r="AJ35" s="147"/>
-      <c r="AK35" s="164"/>
-      <c r="AL35" s="55">
+        <f t="shared" si="44"/>
+        <v>2094.88</v>
+      </c>
+      <c r="AG35" s="146">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="147">
+        <v>1982.57</v>
+      </c>
+      <c r="AI35" s="148">
+        <v>0.3840277777777778</v>
+      </c>
+      <c r="AJ35" s="147">
+        <v>0</v>
+      </c>
+      <c r="AK35" s="164">
+        <v>0</v>
+      </c>
+      <c r="AL35" s="167">
         <f t="shared" si="28"/>
         <v>46202</v>
       </c>
-      <c r="AM35" s="76" t="e">
-        <f t="shared" ref="AM35" si="66">+AP35/AO35</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AN35" s="75" t="e">
-        <f t="shared" ref="AN35" si="67">+AQ35/AO35</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AO35" s="149"/>
+      <c r="AM35" s="76">
+        <f t="shared" si="48"/>
+        <v>0.29661784287616516</v>
+      </c>
+      <c r="AN35" s="75">
+        <f t="shared" ref="AN35" si="63">+AQ35/AO35</f>
+        <v>0.70338215712383489</v>
+      </c>
+      <c r="AO35" s="149">
+        <v>5257</v>
+      </c>
       <c r="AP35" s="116">
-        <f t="shared" ref="AP35" si="68">AO35-AQ35</f>
-        <v>0</v>
-      </c>
-      <c r="AQ35" s="150"/>
-      <c r="AR35" s="151"/>
-      <c r="AS35" s="152"/>
-      <c r="AT35" s="151"/>
-      <c r="AU35" s="153"/>
-      <c r="AV35" s="55">
+        <f t="shared" si="40"/>
+        <v>1559.3200000000002</v>
+      </c>
+      <c r="AQ35" s="150">
+        <v>3697.68</v>
+      </c>
+      <c r="AR35" s="151">
+        <v>1559.09</v>
+      </c>
+      <c r="AS35" s="152">
+        <v>0.56805555555555554</v>
+      </c>
+      <c r="AT35" s="151">
+        <v>176</v>
+      </c>
+      <c r="AU35" s="153">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="AV35" s="167">
         <f t="shared" si="41"/>
         <v>46202</v>
       </c>
-      <c r="AW35" s="109" t="e">
-        <f t="shared" ref="AW35" si="69">BA35/AZ35</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AX35" s="109" t="e">
-        <f t="shared" ref="AX35" si="70">BB35/AZ35</f>
-        <v>#DIV/0!</v>
+      <c r="AW35" s="168">
+        <f t="shared" si="50"/>
+        <v>0.263954814652336</v>
+      </c>
+      <c r="AX35" s="168">
+        <f t="shared" si="51"/>
+        <v>0.73604518534766394</v>
       </c>
       <c r="AY35" s="110">
-        <f t="shared" ref="AY35" si="71">BA35+BB35</f>
-        <v>0</v>
-      </c>
-      <c r="AZ35" s="111"/>
-      <c r="BA35" s="119">
-        <f t="shared" ref="BA35" si="72">AZ35-BB35</f>
-        <v>0</v>
-      </c>
-      <c r="BB35" s="112"/>
-      <c r="BC35" s="111"/>
-      <c r="BD35" s="113"/>
-      <c r="BE35" s="114"/>
-      <c r="BF35" s="113"/>
-      <c r="BG35" s="114"/>
-      <c r="BH35" s="113"/>
-      <c r="BI35" s="55">
+        <f t="shared" si="45"/>
+        <v>4559</v>
+      </c>
+      <c r="AZ35" s="111">
+        <v>4559</v>
+      </c>
+      <c r="BA35" s="216">
+        <f t="shared" si="42"/>
+        <v>1203.3699999999999</v>
+      </c>
+      <c r="BB35" s="112">
+        <f>2784.63+571</f>
+        <v>3355.63</v>
+      </c>
+      <c r="BC35" s="111">
+        <v>1438.3</v>
+      </c>
+      <c r="BD35" s="113">
+        <v>0.71875</v>
+      </c>
+      <c r="BE35" s="114">
+        <v>0</v>
+      </c>
+      <c r="BF35" s="113">
+        <v>0</v>
+      </c>
+      <c r="BG35" s="114">
+        <v>162</v>
+      </c>
+      <c r="BH35" s="113">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="BI35" s="167">
         <f t="shared" si="43"/>
         <v>46202</v>
       </c>
-      <c r="BJ35" s="77" t="e">
-        <f t="shared" ref="BJ35" si="73">+BM35/BL35</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BK35" s="75" t="e">
-        <f t="shared" ref="BK35" si="74">+BN35/BL35</f>
-        <v>#DIV/0!</v>
+      <c r="BJ35" s="169">
+        <f t="shared" si="52"/>
+        <v>0.60688974844889798</v>
+      </c>
+      <c r="BK35" s="75">
+        <f t="shared" si="53"/>
+        <v>0.39311025155110202</v>
       </c>
       <c r="BL35" s="78">
-        <f t="shared" ref="BL35" si="75">BM35+BN35</f>
-        <v>0</v>
-      </c>
-      <c r="BM35" s="154"/>
-      <c r="BN35" s="154"/>
-      <c r="BO35" s="155"/>
-      <c r="BP35" s="156"/>
-      <c r="BQ35" s="157"/>
-      <c r="BR35" s="156"/>
+        <f t="shared" si="54"/>
+        <v>19260.5</v>
+      </c>
+      <c r="BM35" s="154">
+        <v>11689</v>
+      </c>
+      <c r="BN35" s="154">
+        <v>7571.5</v>
+      </c>
+      <c r="BO35" s="155">
+        <v>2656.22</v>
+      </c>
+      <c r="BP35" s="156">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="BQ35" s="157">
+        <v>1755.96</v>
+      </c>
+      <c r="BR35" s="156">
+        <v>0.41388888888888886</v>
+      </c>
     </row>
     <row r="36" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="14"/>
@@ -15214,11 +15301,11 @@
         <v>46203</v>
       </c>
       <c r="AC36" s="75" t="e">
-        <f t="shared" ref="AC32:AC36" si="76">+AF36/AE36</f>
+        <f t="shared" ref="AC36" si="64">+AF36/AE36</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AD36" s="161" t="e">
-        <f t="shared" ref="AD32:AD36" si="77">+AG36/AE36</f>
+        <f t="shared" ref="AD36" si="65">+AG36/AE36</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AE36" s="162"/>
@@ -15236,11 +15323,11 @@
         <v>46203</v>
       </c>
       <c r="AM36" s="76" t="e">
-        <f t="shared" ref="AM32:AM36" si="78">+AP36/AO36</f>
+        <f t="shared" ref="AM36" si="66">+AP36/AO36</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AN36" s="75" t="e">
-        <f t="shared" ref="AN32:AN36" si="79">+AQ36/AO36</f>
+        <f t="shared" ref="AN36" si="67">+AQ36/AO36</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AO36" s="149"/>
@@ -15258,11 +15345,11 @@
         <v>46203</v>
       </c>
       <c r="AW36" s="109" t="e">
-        <f t="shared" ref="AW32:AW36" si="80">BA36/AZ36</f>
+        <f t="shared" ref="AW36" si="68">BA36/AZ36</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AX36" s="109" t="e">
-        <f t="shared" ref="AX32:AX36" si="81">BB36/AZ36</f>
+        <f t="shared" ref="AX36" si="69">BB36/AZ36</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AY36" s="110">
@@ -15286,15 +15373,15 @@
         <v>46203</v>
       </c>
       <c r="BJ36" s="77" t="e">
-        <f t="shared" ref="BJ32:BJ36" si="82">+BM36/BL36</f>
+        <f t="shared" ref="BJ36" si="70">+BM36/BL36</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BK36" s="75" t="e">
-        <f t="shared" ref="BK32:BK36" si="83">+BN36/BL36</f>
+        <f t="shared" ref="BK36" si="71">+BN36/BL36</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BL36" s="78">
-        <f t="shared" ref="BL32:BL36" si="84">BM36+BN36</f>
+        <f t="shared" ref="BL36" si="72">BM36+BN36</f>
         <v>0</v>
       </c>
       <c r="BM36" s="154"/>
@@ -15380,11 +15467,11 @@
         <v>46204</v>
       </c>
       <c r="AC37" s="75" t="e">
-        <f t="shared" ref="AC37" si="85">+AF37/AE37</f>
+        <f t="shared" ref="AC37" si="73">+AF37/AE37</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AD37" s="161" t="e">
-        <f t="shared" ref="AD37" si="86">+AG37/AE37</f>
+        <f t="shared" ref="AD37" si="74">+AG37/AE37</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AE37" s="162"/>
@@ -15402,16 +15489,16 @@
         <v>46204</v>
       </c>
       <c r="AM37" s="76" t="e">
-        <f t="shared" ref="AM37" si="87">+AP37/AO37</f>
+        <f t="shared" ref="AM37" si="75">+AP37/AO37</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AN37" s="75" t="e">
-        <f t="shared" ref="AN37" si="88">+AQ37/AO37</f>
+        <f t="shared" ref="AN37" si="76">+AQ37/AO37</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AO37" s="149"/>
       <c r="AP37" s="116">
-        <f t="shared" ref="AP37" si="89">AO37-AQ37</f>
+        <f t="shared" ref="AP37" si="77">AO37-AQ37</f>
         <v>0</v>
       </c>
       <c r="AQ37" s="150"/>
@@ -15424,11 +15511,11 @@
         <v>46204</v>
       </c>
       <c r="AW37" s="109" t="e">
-        <f t="shared" ref="AW37" si="90">BA37/AZ37</f>
+        <f t="shared" ref="AW37" si="78">BA37/AZ37</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AX37" s="109" t="e">
-        <f t="shared" ref="AX37" si="91">BB37/AZ37</f>
+        <f t="shared" ref="AX37" si="79">BB37/AZ37</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AY37" s="110">
@@ -15452,15 +15539,15 @@
         <v>46204</v>
       </c>
       <c r="BJ37" s="77" t="e">
-        <f t="shared" ref="BJ37" si="92">+BM37/BL37</f>
+        <f t="shared" ref="BJ37" si="80">+BM37/BL37</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BK37" s="75" t="e">
-        <f t="shared" ref="BK37" si="93">+BN37/BL37</f>
+        <f t="shared" ref="BK37" si="81">+BN37/BL37</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BL37" s="78">
-        <f t="shared" ref="BL37" si="94">BM37+BN37</f>
+        <f t="shared" ref="BL37" si="82">BM37+BN37</f>
         <v>0</v>
       </c>
       <c r="BM37" s="154"/>
@@ -15514,6 +15601,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="BJ1:BR2"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="AN3:AN4"/>
+    <mergeCell ref="AR3:AU3"/>
+    <mergeCell ref="BJ3:BJ4"/>
+    <mergeCell ref="BK3:BK4"/>
+    <mergeCell ref="BL3:BN3"/>
+    <mergeCell ref="BO3:BR3"/>
+    <mergeCell ref="AW1:BH2"/>
+    <mergeCell ref="AW3:AW4"/>
+    <mergeCell ref="AX3:AX4"/>
+    <mergeCell ref="AY3:BB3"/>
+    <mergeCell ref="BC3:BH3"/>
     <mergeCell ref="B1:B4"/>
     <mergeCell ref="D1:P2"/>
     <mergeCell ref="R1:AA2"/>
@@ -15530,22 +15633,6 @@
     <mergeCell ref="AE3:AG3"/>
     <mergeCell ref="AH3:AK3"/>
     <mergeCell ref="AM3:AM4"/>
-    <mergeCell ref="BJ1:BR2"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="AN3:AN4"/>
-    <mergeCell ref="AR3:AU3"/>
-    <mergeCell ref="BJ3:BJ4"/>
-    <mergeCell ref="BK3:BK4"/>
-    <mergeCell ref="BL3:BN3"/>
-    <mergeCell ref="BO3:BR3"/>
-    <mergeCell ref="AW1:BH2"/>
-    <mergeCell ref="AW3:AW4"/>
-    <mergeCell ref="AX3:AX4"/>
-    <mergeCell ref="AY3:BB3"/>
-    <mergeCell ref="BC3:BH3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="88" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -18004,45 +18091,78 @@
       </c>
     </row>
     <row r="43" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="89">
+      <c r="B43" s="173">
         <f t="shared" si="5"/>
         <v>46202</v>
       </c>
-      <c r="D43" s="170"/>
-      <c r="E43" s="88"/>
-      <c r="F43" s="87"/>
-      <c r="G43" s="92">
+      <c r="C43" s="52"/>
+      <c r="D43" s="190">
+        <v>83.21</v>
+      </c>
+      <c r="E43" s="189">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="F43" s="188">
+        <v>887.07</v>
+      </c>
+      <c r="G43" s="192">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H43" s="87"/>
-      <c r="I43" s="89">
+        <v>455.08000000000004</v>
+      </c>
+      <c r="H43" s="188">
+        <v>431.99</v>
+      </c>
+      <c r="I43" s="173">
         <f t="shared" si="3"/>
         <v>46202</v>
       </c>
-      <c r="J43" s="90"/>
-      <c r="K43" s="88"/>
-      <c r="L43" s="87"/>
+      <c r="J43" s="190">
+        <v>35.82</v>
+      </c>
+      <c r="K43" s="189">
+        <v>0.13541666666666666</v>
+      </c>
+      <c r="L43" s="188">
+        <v>639.27</v>
+      </c>
       <c r="M43" s="173">
         <f t="shared" si="4"/>
         <v>46202</v>
       </c>
-      <c r="N43" s="90"/>
-      <c r="O43" s="88"/>
-      <c r="P43" s="90"/>
-      <c r="Q43" s="88"/>
-      <c r="R43" s="91">
+      <c r="N43" s="190">
+        <v>21.9</v>
+      </c>
+      <c r="O43" s="189">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="P43" s="190">
+        <v>11.79</v>
+      </c>
+      <c r="Q43" s="189">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="R43" s="191">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="S43" s="87"/>
-      <c r="T43" s="87"/>
-      <c r="U43" s="89">
+        <v>513.11</v>
+      </c>
+      <c r="S43" s="188">
+        <v>320.8</v>
+      </c>
+      <c r="T43" s="188">
+        <v>192.31</v>
+      </c>
+      <c r="U43" s="173">
         <v>46202</v>
       </c>
-      <c r="V43" s="90"/>
-      <c r="W43" s="88"/>
-      <c r="X43" s="87"/>
+      <c r="V43" s="190">
+        <v>27.32</v>
+      </c>
+      <c r="W43" s="189">
+        <v>0.23958333333333334</v>
+      </c>
+      <c r="X43" s="188">
+        <v>501.98</v>
+      </c>
     </row>
     <row r="44" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="89">
@@ -18991,29 +19111,29 @@
       <c r="D77" s="179">
         <v>45867</v>
       </c>
-      <c r="E77" s="177" t="e">
+      <c r="E77" s="177">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F77" s="177" t="e">
+        <v>0.34904364865449766</v>
+      </c>
+      <c r="F77" s="177">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G77" s="177" t="e">
+        <v>0.2515394876113054</v>
+      </c>
+      <c r="G77" s="177">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H77" s="177" t="e">
+        <v>0.12622814714550468</v>
+      </c>
+      <c r="H77" s="177">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I77" s="177" t="e">
+        <v>7.5669996812817969E-2</v>
+      </c>
+      <c r="I77" s="177">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>0.19751871977587421</v>
       </c>
       <c r="J77" s="178">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>2541.4300000000003</v>
       </c>
     </row>
     <row r="78" spans="4:10" x14ac:dyDescent="0.25">
@@ -19090,643 +19210,668 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="L16:L19 L27:L32 L21:L25">
-    <cfRule type="cellIs" dxfId="137" priority="377" operator="equal">
+    <cfRule type="cellIs" dxfId="139" priority="387" operator="equal">
       <formula>MAX($L$14:$L$16)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T16:T19 T27:T32 T21:T25 T43">
-    <cfRule type="cellIs" dxfId="136" priority="378" operator="equal">
+  <conditionalFormatting sqref="T16:T19 T27:T32 T21:T25">
+    <cfRule type="cellIs" dxfId="138" priority="388" operator="equal">
       <formula>MAX($T$14:$T$16)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X16:X19 X27:X32 X21:X25 X43">
-    <cfRule type="cellIs" dxfId="135" priority="379" operator="equal">
+  <conditionalFormatting sqref="X16:X19 X27:X32 X21:X25">
+    <cfRule type="cellIs" dxfId="137" priority="389" operator="equal">
       <formula>MAX($X$14:$X$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J16:J19 J27:J32 J21 J23:J25">
-    <cfRule type="cellIs" dxfId="134" priority="380" operator="equal">
+    <cfRule type="cellIs" dxfId="136" priority="390" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V16:V19 V27:V32 V21 V43 V23">
-    <cfRule type="cellIs" dxfId="133" priority="381" operator="equal">
+  <conditionalFormatting sqref="V16:V19 V27:V32 V21 V23">
+    <cfRule type="cellIs" dxfId="135" priority="391" operator="equal">
       <formula>MAX($V$14:$V$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D19">
-    <cfRule type="cellIs" dxfId="132" priority="382" operator="equal">
+    <cfRule type="cellIs" dxfId="134" priority="392" operator="equal">
       <formula>MAX($D$14:$D$16)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S16:S19 S27:S32 S21:S25 S43">
-    <cfRule type="cellIs" dxfId="131" priority="383" operator="equal">
+  <conditionalFormatting sqref="S16:S19 S27:S32 S21:S25">
+    <cfRule type="cellIs" dxfId="133" priority="393" operator="equal">
       <formula>MAX($S$14:$S$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N16:N19 N27:N32 N21 N23:N25">
-    <cfRule type="cellIs" dxfId="130" priority="384" operator="equal">
+    <cfRule type="cellIs" dxfId="132" priority="394" operator="equal">
       <formula>MAX($N$14:$N$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P16:P19 P27:P32 P21 P23:P25">
-    <cfRule type="cellIs" dxfId="129" priority="385" operator="equal">
+    <cfRule type="cellIs" dxfId="131" priority="395" operator="equal">
       <formula>MAX($P$14:$P$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L26">
-    <cfRule type="cellIs" dxfId="128" priority="309" operator="equal">
+    <cfRule type="cellIs" dxfId="130" priority="319" operator="equal">
       <formula>MAX($L$14:$L$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T26">
-    <cfRule type="cellIs" dxfId="127" priority="310" operator="equal">
+    <cfRule type="cellIs" dxfId="129" priority="320" operator="equal">
       <formula>MAX($T$14:$T$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X26">
-    <cfRule type="cellIs" dxfId="126" priority="311" operator="equal">
+    <cfRule type="cellIs" dxfId="128" priority="321" operator="equal">
       <formula>MAX($X$14:$X$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J26">
-    <cfRule type="cellIs" dxfId="125" priority="312" operator="equal">
+    <cfRule type="cellIs" dxfId="127" priority="322" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V26">
-    <cfRule type="cellIs" dxfId="124" priority="313" operator="equal">
+    <cfRule type="cellIs" dxfId="126" priority="323" operator="equal">
       <formula>MAX($V$14:$V$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S26">
-    <cfRule type="cellIs" dxfId="123" priority="315" operator="equal">
+    <cfRule type="cellIs" dxfId="125" priority="325" operator="equal">
       <formula>MAX($S$14:$S$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N26">
-    <cfRule type="cellIs" dxfId="122" priority="316" operator="equal">
+    <cfRule type="cellIs" dxfId="124" priority="326" operator="equal">
       <formula>MAX($N$14:$N$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P26">
-    <cfRule type="cellIs" dxfId="121" priority="317" operator="equal">
+    <cfRule type="cellIs" dxfId="123" priority="327" operator="equal">
       <formula>MAX($P$14:$P$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D20:D32 D45">
-    <cfRule type="cellIs" dxfId="112" priority="295" operator="equal">
+    <cfRule type="cellIs" dxfId="122" priority="305" operator="equal">
       <formula>MAX($D$14:$D$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L20">
-    <cfRule type="cellIs" dxfId="111" priority="286" operator="equal">
+    <cfRule type="cellIs" dxfId="121" priority="296" operator="equal">
       <formula>MAX($L$14:$L$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T20">
-    <cfRule type="cellIs" dxfId="110" priority="287" operator="equal">
+    <cfRule type="cellIs" dxfId="120" priority="297" operator="equal">
       <formula>MAX($T$14:$T$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X20">
-    <cfRule type="cellIs" dxfId="109" priority="288" operator="equal">
+    <cfRule type="cellIs" dxfId="119" priority="298" operator="equal">
       <formula>MAX($X$14:$X$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J20">
-    <cfRule type="cellIs" dxfId="108" priority="289" operator="equal">
+    <cfRule type="cellIs" dxfId="118" priority="299" operator="equal">
       <formula>MAX($J$14:$J$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V20">
-    <cfRule type="cellIs" dxfId="107" priority="290" operator="equal">
+    <cfRule type="cellIs" dxfId="117" priority="300" operator="equal">
       <formula>MAX($V$14:$V$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S20">
-    <cfRule type="cellIs" dxfId="106" priority="291" operator="equal">
+    <cfRule type="cellIs" dxfId="116" priority="301" operator="equal">
       <formula>MAX($S$14:$S$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N20">
-    <cfRule type="cellIs" dxfId="105" priority="292" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="302" operator="equal">
       <formula>MAX($N$14:$N$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P20">
-    <cfRule type="cellIs" dxfId="104" priority="293" operator="equal">
+    <cfRule type="cellIs" dxfId="114" priority="303" operator="equal">
       <formula>MAX($P$14:$P$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E48:E64">
-    <cfRule type="top10" dxfId="103" priority="285" rank="2"/>
+    <cfRule type="top10" dxfId="113" priority="295" rank="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F79">
-    <cfRule type="top10" dxfId="102" priority="284" rank="2"/>
+    <cfRule type="top10" dxfId="112" priority="294" rank="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G48:G64">
-    <cfRule type="top10" dxfId="101" priority="283" rank="2"/>
+    <cfRule type="top10" dxfId="111" priority="293" rank="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H48:H64">
-    <cfRule type="top10" dxfId="100" priority="282" rank="2"/>
+    <cfRule type="top10" dxfId="110" priority="292" rank="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I48:I64">
-    <cfRule type="top10" dxfId="99" priority="281" rank="2"/>
+    <cfRule type="top10" dxfId="109" priority="291" rank="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="V24">
-    <cfRule type="cellIs" dxfId="98" priority="251" operator="equal">
+    <cfRule type="cellIs" dxfId="108" priority="261" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V25">
-    <cfRule type="cellIs" dxfId="97" priority="250" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="260" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G18:G32 G43:G45">
-    <cfRule type="cellIs" dxfId="96" priority="239" operator="equal">
+  <conditionalFormatting sqref="G18:G32 G44:G45">
+    <cfRule type="cellIs" dxfId="106" priority="249" operator="equal">
       <formula>MAX($G$14:$G$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L45">
-    <cfRule type="cellIs" dxfId="95" priority="229" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="239" operator="equal">
       <formula>MAX($L$14:$L$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T45">
-    <cfRule type="cellIs" dxfId="94" priority="230" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="240" operator="equal">
       <formula>MAX($T$14:$T$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X45">
-    <cfRule type="cellIs" dxfId="93" priority="231" operator="equal">
+    <cfRule type="cellIs" dxfId="103" priority="241" operator="equal">
       <formula>MAX($X$14:$X$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J45">
-    <cfRule type="cellIs" dxfId="92" priority="232" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="242" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V45">
-    <cfRule type="cellIs" dxfId="91" priority="233" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="243" operator="equal">
       <formula>MAX($V$14:$V$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S45">
-    <cfRule type="cellIs" dxfId="90" priority="235" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="245" operator="equal">
       <formula>MAX($S$14:$S$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N45">
-    <cfRule type="cellIs" dxfId="89" priority="236" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="246" operator="equal">
       <formula>MAX($N$14:$N$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P45">
-    <cfRule type="cellIs" dxfId="88" priority="237" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="247" operator="equal">
       <formula>MAX($P$14:$P$16)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G16:G17">
+    <cfRule type="cellIs" dxfId="92" priority="133" operator="equal">
+      <formula>MAX($G$14:$G$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D44">
+    <cfRule type="cellIs" dxfId="91" priority="104" operator="equal">
+      <formula>MAX($D$14:$D$42)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L44">
+    <cfRule type="cellIs" dxfId="90" priority="100" operator="equal">
+      <formula>MAX($L$14:$L$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J44">
+    <cfRule type="cellIs" dxfId="89" priority="101" operator="equal">
+      <formula>MAX($J$14:$J$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N44">
+    <cfRule type="cellIs" dxfId="88" priority="96" operator="equal">
+      <formula>MAX($N$14:$N$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P44">
+    <cfRule type="cellIs" dxfId="87" priority="97" operator="equal">
+      <formula>MAX($P$14:$P$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T44">
+    <cfRule type="cellIs" dxfId="86" priority="92" operator="equal">
+      <formula>MAX($T$14:$T$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S44">
+    <cfRule type="cellIs" dxfId="85" priority="93" operator="equal">
+      <formula>MAX($S$14:$S$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X44">
+    <cfRule type="cellIs" dxfId="84" priority="88" operator="equal">
+      <formula>MAX($X$14:$X$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V44">
+    <cfRule type="cellIs" dxfId="83" priority="89" operator="equal">
+      <formula>MAX($V$14:$V$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D14">
+    <cfRule type="cellIs" dxfId="82" priority="87" operator="equal">
+      <formula>MAX($D$14:$D$42)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G14">
+    <cfRule type="cellIs" dxfId="81" priority="86" operator="equal">
+      <formula>MAX($G$14:$G$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L14">
+    <cfRule type="cellIs" dxfId="80" priority="78" operator="equal">
+      <formula>MAX($L$14:$L$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T14">
+    <cfRule type="cellIs" dxfId="79" priority="79" operator="equal">
+      <formula>MAX($T$14:$T$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X14">
+    <cfRule type="cellIs" dxfId="78" priority="80" operator="equal">
+      <formula>MAX($X$14:$X$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J14">
+    <cfRule type="cellIs" dxfId="77" priority="81" operator="equal">
+      <formula>MAX($J$14:$J$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V14">
+    <cfRule type="cellIs" dxfId="76" priority="82" operator="equal">
+      <formula>MAX($V$14:$V$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S14">
+    <cfRule type="cellIs" dxfId="75" priority="83" operator="equal">
+      <formula>MAX($S$14:$S$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N14">
+    <cfRule type="cellIs" dxfId="74" priority="84" operator="equal">
+      <formula>MAX($N$14:$N$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P14">
+    <cfRule type="cellIs" dxfId="73" priority="85" operator="equal">
+      <formula>MAX($P$14:$P$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15">
+    <cfRule type="cellIs" dxfId="72" priority="77" operator="equal">
+      <formula>MAX($D$14:$D$42)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15">
+    <cfRule type="cellIs" dxfId="71" priority="76" operator="equal">
+      <formula>MAX($G$14:$G$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L15">
+    <cfRule type="cellIs" dxfId="70" priority="74" operator="equal">
+      <formula>MAX($L$14:$L$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J15">
+    <cfRule type="cellIs" dxfId="69" priority="75" operator="equal">
+      <formula>MAX($J$14:$J$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T15">
+    <cfRule type="cellIs" dxfId="68" priority="70" operator="equal">
+      <formula>MAX($T$14:$T$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S15">
+    <cfRule type="cellIs" dxfId="67" priority="71" operator="equal">
+      <formula>MAX($S$14:$S$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N15">
+    <cfRule type="cellIs" dxfId="66" priority="72" operator="equal">
+      <formula>MAX($N$14:$N$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P15">
+    <cfRule type="cellIs" dxfId="65" priority="73" operator="equal">
+      <formula>MAX($P$14:$P$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X15">
+    <cfRule type="cellIs" dxfId="64" priority="68" operator="equal">
+      <formula>MAX($X$14:$X$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V15">
+    <cfRule type="cellIs" dxfId="63" priority="69" operator="equal">
+      <formula>MAX($V$14:$V$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V22">
+    <cfRule type="cellIs" dxfId="62" priority="66" operator="equal">
+      <formula>MAX($V$14:$V$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N22">
+    <cfRule type="cellIs" dxfId="61" priority="62" operator="equal">
+      <formula>MAX($N$14:$N$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P22">
+    <cfRule type="cellIs" dxfId="60" priority="63" operator="equal">
+      <formula>MAX($P$14:$P$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J22">
+    <cfRule type="cellIs" dxfId="59" priority="60" operator="equal">
+      <formula>MAX($J$14:$J$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L34:L35">
+    <cfRule type="cellIs" dxfId="58" priority="52" operator="equal">
+      <formula>MAX($L$14:$L$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T34:T35">
+    <cfRule type="cellIs" dxfId="57" priority="53" operator="equal">
+      <formula>MAX($T$14:$T$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X34:X35">
+    <cfRule type="cellIs" dxfId="56" priority="54" operator="equal">
+      <formula>MAX($X$14:$X$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J34:J35">
+    <cfRule type="cellIs" dxfId="55" priority="55" operator="equal">
+      <formula>MAX($J$14:$J$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V34:V35">
+    <cfRule type="cellIs" dxfId="54" priority="56" operator="equal">
+      <formula>MAX($V$14:$V$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S34:S35">
+    <cfRule type="cellIs" dxfId="53" priority="57" operator="equal">
+      <formula>MAX($S$14:$S$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N34:N35">
+    <cfRule type="cellIs" dxfId="52" priority="58" operator="equal">
+      <formula>MAX($N$14:$N$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P34:P35">
+    <cfRule type="cellIs" dxfId="51" priority="59" operator="equal">
+      <formula>MAX($P$14:$P$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D34:D35">
+    <cfRule type="cellIs" dxfId="50" priority="51" operator="equal">
+      <formula>MAX($D$14:$D$42)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G34:G35">
+    <cfRule type="cellIs" dxfId="49" priority="50" operator="equal">
+      <formula>MAX($G$14:$G$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L33">
+    <cfRule type="cellIs" dxfId="48" priority="42" operator="equal">
+      <formula>MAX($L$14:$L$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T33">
+    <cfRule type="cellIs" dxfId="47" priority="43" operator="equal">
+      <formula>MAX($T$14:$T$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X33">
+    <cfRule type="cellIs" dxfId="46" priority="44" operator="equal">
+      <formula>MAX($X$14:$X$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J33">
+    <cfRule type="cellIs" dxfId="45" priority="45" operator="equal">
+      <formula>MAX($J$14:$J$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V33">
+    <cfRule type="cellIs" dxfId="44" priority="46" operator="equal">
+      <formula>MAX($V$14:$V$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S33">
+    <cfRule type="cellIs" dxfId="43" priority="47" operator="equal">
+      <formula>MAX($S$14:$S$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N33">
+    <cfRule type="cellIs" dxfId="42" priority="48" operator="equal">
+      <formula>MAX($N$14:$N$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P33">
+    <cfRule type="cellIs" dxfId="41" priority="49" operator="equal">
+      <formula>MAX($P$14:$P$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D33">
+    <cfRule type="cellIs" dxfId="40" priority="41" operator="equal">
+      <formula>MAX($D$14:$D$42)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G33">
+    <cfRule type="cellIs" dxfId="39" priority="40" operator="equal">
+      <formula>MAX($G$14:$G$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L36:L39">
+    <cfRule type="cellIs" dxfId="38" priority="32" operator="equal">
+      <formula>MAX($L$14:$L$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T36:T39">
+    <cfRule type="cellIs" dxfId="37" priority="33" operator="equal">
+      <formula>MAX($T$14:$T$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X36:X39">
+    <cfRule type="cellIs" dxfId="36" priority="34" operator="equal">
+      <formula>MAX($X$14:$X$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J36:J39">
+    <cfRule type="cellIs" dxfId="35" priority="35" operator="equal">
+      <formula>MAX($J$14:$J$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V36:V39">
+    <cfRule type="cellIs" dxfId="34" priority="36" operator="equal">
+      <formula>MAX($V$14:$V$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S36:S39">
+    <cfRule type="cellIs" dxfId="33" priority="37" operator="equal">
+      <formula>MAX($S$14:$S$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N36:N39">
+    <cfRule type="cellIs" dxfId="32" priority="38" operator="equal">
+      <formula>MAX($N$14:$N$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P39 P36:P37">
+    <cfRule type="cellIs" dxfId="31" priority="39" operator="equal">
+      <formula>MAX($P$14:$P$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D36:D39">
+    <cfRule type="cellIs" dxfId="30" priority="31" operator="equal">
+      <formula>MAX($D$14:$D$42)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G36:G39">
+    <cfRule type="cellIs" dxfId="29" priority="30" operator="equal">
+      <formula>MAX($G$14:$G$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P38">
+    <cfRule type="cellIs" dxfId="28" priority="29" operator="equal">
+      <formula>MAX($P$14:$P$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L41:L42">
+    <cfRule type="cellIs" dxfId="27" priority="21" operator="equal">
+      <formula>MAX($L$14:$L$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T41:T42">
+    <cfRule type="cellIs" dxfId="26" priority="22" operator="equal">
+      <formula>MAX($T$14:$T$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X41:X42">
+    <cfRule type="cellIs" dxfId="25" priority="23" operator="equal">
+      <formula>MAX($X$14:$X$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J41:J42">
+    <cfRule type="cellIs" dxfId="24" priority="24" operator="equal">
+      <formula>MAX($J$14:$J$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V41:V42">
+    <cfRule type="cellIs" dxfId="23" priority="25" operator="equal">
+      <formula>MAX($V$14:$V$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S41:S42">
+    <cfRule type="cellIs" dxfId="22" priority="26" operator="equal">
+      <formula>MAX($S$14:$S$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N41:N42">
+    <cfRule type="cellIs" dxfId="21" priority="27" operator="equal">
+      <formula>MAX($N$14:$N$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P41:P42">
+    <cfRule type="cellIs" dxfId="20" priority="28" operator="equal">
+      <formula>MAX($P$14:$P$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L40">
+    <cfRule type="cellIs" dxfId="19" priority="13" operator="equal">
+      <formula>MAX($L$14:$L$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T40">
+    <cfRule type="cellIs" dxfId="18" priority="14" operator="equal">
+      <formula>MAX($T$14:$T$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X40">
+    <cfRule type="cellIs" dxfId="17" priority="15" operator="equal">
+      <formula>MAX($X$14:$X$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J40">
+    <cfRule type="cellIs" dxfId="16" priority="16" operator="equal">
+      <formula>MAX($J$14:$J$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V40">
+    <cfRule type="cellIs" dxfId="15" priority="17" operator="equal">
+      <formula>MAX($V$14:$V$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S40">
+    <cfRule type="cellIs" dxfId="14" priority="18" operator="equal">
+      <formula>MAX($S$14:$S$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N40">
+    <cfRule type="cellIs" dxfId="13" priority="19" operator="equal">
+      <formula>MAX($N$14:$N$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P40">
+    <cfRule type="cellIs" dxfId="12" priority="20" operator="equal">
+      <formula>MAX($P$14:$P$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D40:D42">
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+      <formula>MAX($D$14:$D$42)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G40:G42">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+      <formula>MAX($G$14:$G$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T43">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
+      <formula>MAX($T$14:$T$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X43">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
+      <formula>MAX($X$14:$X$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V43">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
+      <formula>MAX($V$14:$V$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S43">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
+      <formula>MAX($S$14:$S$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G43">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>MAX($G$14:$G$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="N43">
-    <cfRule type="cellIs" dxfId="87" priority="188" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>MAX($N$14:$N$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P43">
-    <cfRule type="cellIs" dxfId="86" priority="189" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>MAX($P$14:$P$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L43">
-    <cfRule type="cellIs" dxfId="85" priority="184" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>MAX($L$14:$L$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J43">
-    <cfRule type="cellIs" dxfId="84" priority="185" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43">
-    <cfRule type="cellIs" dxfId="83" priority="182" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>MAX($D$14:$D$42)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G16:G17">
-    <cfRule type="cellIs" dxfId="82" priority="123" operator="equal">
-      <formula>MAX($G$14:$G$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D44">
-    <cfRule type="cellIs" dxfId="81" priority="94" operator="equal">
-      <formula>MAX($D$14:$D$42)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L44">
-    <cfRule type="cellIs" dxfId="80" priority="90" operator="equal">
-      <formula>MAX($L$14:$L$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J44">
-    <cfRule type="cellIs" dxfId="79" priority="91" operator="equal">
-      <formula>MAX($J$14:$J$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N44">
-    <cfRule type="cellIs" dxfId="78" priority="86" operator="equal">
-      <formula>MAX($N$14:$N$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P44">
-    <cfRule type="cellIs" dxfId="77" priority="87" operator="equal">
-      <formula>MAX($P$14:$P$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T44">
-    <cfRule type="cellIs" dxfId="76" priority="82" operator="equal">
-      <formula>MAX($T$14:$T$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S44">
-    <cfRule type="cellIs" dxfId="75" priority="83" operator="equal">
-      <formula>MAX($S$14:$S$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X44">
-    <cfRule type="cellIs" dxfId="74" priority="78" operator="equal">
-      <formula>MAX($X$14:$X$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V44">
-    <cfRule type="cellIs" dxfId="73" priority="79" operator="equal">
-      <formula>MAX($V$14:$V$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D14">
-    <cfRule type="cellIs" dxfId="72" priority="77" operator="equal">
-      <formula>MAX($D$14:$D$42)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G14">
-    <cfRule type="cellIs" dxfId="71" priority="76" operator="equal">
-      <formula>MAX($G$14:$G$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L14">
-    <cfRule type="cellIs" dxfId="70" priority="68" operator="equal">
-      <formula>MAX($L$14:$L$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T14">
-    <cfRule type="cellIs" dxfId="69" priority="69" operator="equal">
-      <formula>MAX($T$14:$T$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X14">
-    <cfRule type="cellIs" dxfId="68" priority="70" operator="equal">
-      <formula>MAX($X$14:$X$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J14">
-    <cfRule type="cellIs" dxfId="67" priority="71" operator="equal">
-      <formula>MAX($J$14:$J$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V14">
-    <cfRule type="cellIs" dxfId="66" priority="72" operator="equal">
-      <formula>MAX($V$14:$V$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S14">
-    <cfRule type="cellIs" dxfId="65" priority="73" operator="equal">
-      <formula>MAX($S$14:$S$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N14">
-    <cfRule type="cellIs" dxfId="64" priority="74" operator="equal">
-      <formula>MAX($N$14:$N$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P14">
-    <cfRule type="cellIs" dxfId="63" priority="75" operator="equal">
-      <formula>MAX($P$14:$P$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D15">
-    <cfRule type="cellIs" dxfId="62" priority="67" operator="equal">
-      <formula>MAX($D$14:$D$42)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G15">
-    <cfRule type="cellIs" dxfId="61" priority="66" operator="equal">
-      <formula>MAX($G$14:$G$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L15">
-    <cfRule type="cellIs" dxfId="60" priority="64" operator="equal">
-      <formula>MAX($L$14:$L$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J15">
-    <cfRule type="cellIs" dxfId="59" priority="65" operator="equal">
-      <formula>MAX($J$14:$J$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T15">
-    <cfRule type="cellIs" dxfId="58" priority="60" operator="equal">
-      <formula>MAX($T$14:$T$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S15">
-    <cfRule type="cellIs" dxfId="57" priority="61" operator="equal">
-      <formula>MAX($S$14:$S$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N15">
-    <cfRule type="cellIs" dxfId="56" priority="62" operator="equal">
-      <formula>MAX($N$14:$N$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P15">
-    <cfRule type="cellIs" dxfId="55" priority="63" operator="equal">
-      <formula>MAX($P$14:$P$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X15">
-    <cfRule type="cellIs" dxfId="54" priority="58" operator="equal">
-      <formula>MAX($X$14:$X$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V15">
-    <cfRule type="cellIs" dxfId="53" priority="59" operator="equal">
-      <formula>MAX($V$14:$V$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V22">
-    <cfRule type="cellIs" dxfId="52" priority="56" operator="equal">
-      <formula>MAX($V$14:$V$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N22">
-    <cfRule type="cellIs" dxfId="51" priority="52" operator="equal">
-      <formula>MAX($N$14:$N$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P22">
-    <cfRule type="cellIs" dxfId="50" priority="53" operator="equal">
-      <formula>MAX($P$14:$P$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J22">
-    <cfRule type="cellIs" dxfId="49" priority="50" operator="equal">
-      <formula>MAX($J$14:$J$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L34:L35">
-    <cfRule type="cellIs" dxfId="48" priority="42" operator="equal">
-      <formula>MAX($L$14:$L$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T34:T35">
-    <cfRule type="cellIs" dxfId="47" priority="43" operator="equal">
-      <formula>MAX($T$14:$T$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X34:X35">
-    <cfRule type="cellIs" dxfId="46" priority="44" operator="equal">
-      <formula>MAX($X$14:$X$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J34:J35">
-    <cfRule type="cellIs" dxfId="45" priority="45" operator="equal">
-      <formula>MAX($J$14:$J$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V34:V35">
-    <cfRule type="cellIs" dxfId="44" priority="46" operator="equal">
-      <formula>MAX($V$14:$V$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S34:S35">
-    <cfRule type="cellIs" dxfId="43" priority="47" operator="equal">
-      <formula>MAX($S$14:$S$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N34:N35">
-    <cfRule type="cellIs" dxfId="42" priority="48" operator="equal">
-      <formula>MAX($N$14:$N$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P34:P35">
-    <cfRule type="cellIs" dxfId="41" priority="49" operator="equal">
-      <formula>MAX($P$14:$P$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D34:D35">
-    <cfRule type="cellIs" dxfId="40" priority="41" operator="equal">
-      <formula>MAX($D$14:$D$42)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G34:G35">
-    <cfRule type="cellIs" dxfId="39" priority="40" operator="equal">
-      <formula>MAX($G$14:$G$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L33">
-    <cfRule type="cellIs" dxfId="38" priority="32" operator="equal">
-      <formula>MAX($L$14:$L$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T33">
-    <cfRule type="cellIs" dxfId="37" priority="33" operator="equal">
-      <formula>MAX($T$14:$T$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X33">
-    <cfRule type="cellIs" dxfId="36" priority="34" operator="equal">
-      <formula>MAX($X$14:$X$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J33">
-    <cfRule type="cellIs" dxfId="35" priority="35" operator="equal">
-      <formula>MAX($J$14:$J$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V33">
-    <cfRule type="cellIs" dxfId="34" priority="36" operator="equal">
-      <formula>MAX($V$14:$V$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S33">
-    <cfRule type="cellIs" dxfId="33" priority="37" operator="equal">
-      <formula>MAX($S$14:$S$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N33">
-    <cfRule type="cellIs" dxfId="32" priority="38" operator="equal">
-      <formula>MAX($N$14:$N$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P33">
-    <cfRule type="cellIs" dxfId="31" priority="39" operator="equal">
-      <formula>MAX($P$14:$P$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D33">
-    <cfRule type="cellIs" dxfId="30" priority="31" operator="equal">
-      <formula>MAX($D$14:$D$42)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G33">
-    <cfRule type="cellIs" dxfId="29" priority="30" operator="equal">
-      <formula>MAX($G$14:$G$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L36:L39">
-    <cfRule type="cellIs" dxfId="28" priority="22" operator="equal">
-      <formula>MAX($L$14:$L$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T36:T39">
-    <cfRule type="cellIs" dxfId="27" priority="23" operator="equal">
-      <formula>MAX($T$14:$T$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X36:X39">
-    <cfRule type="cellIs" dxfId="26" priority="24" operator="equal">
-      <formula>MAX($X$14:$X$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J36:J39">
-    <cfRule type="cellIs" dxfId="25" priority="25" operator="equal">
-      <formula>MAX($J$14:$J$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V36:V39">
-    <cfRule type="cellIs" dxfId="24" priority="26" operator="equal">
-      <formula>MAX($V$14:$V$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S36:S39">
-    <cfRule type="cellIs" dxfId="23" priority="27" operator="equal">
-      <formula>MAX($S$14:$S$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N36:N39">
-    <cfRule type="cellIs" dxfId="22" priority="28" operator="equal">
-      <formula>MAX($N$14:$N$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P39 P36:P37">
-    <cfRule type="cellIs" dxfId="21" priority="29" operator="equal">
-      <formula>MAX($P$14:$P$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D36:D39">
-    <cfRule type="cellIs" dxfId="20" priority="21" operator="equal">
-      <formula>MAX($D$14:$D$42)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G36:G39">
-    <cfRule type="cellIs" dxfId="19" priority="20" operator="equal">
-      <formula>MAX($G$14:$G$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P38">
-    <cfRule type="cellIs" dxfId="18" priority="19" operator="equal">
-      <formula>MAX($P$14:$P$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L41:L42">
-    <cfRule type="cellIs" dxfId="17" priority="11" operator="equal">
-      <formula>MAX($L$14:$L$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T41:T42">
-    <cfRule type="cellIs" dxfId="16" priority="12" operator="equal">
-      <formula>MAX($T$14:$T$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X41:X42">
-    <cfRule type="cellIs" dxfId="15" priority="13" operator="equal">
-      <formula>MAX($X$14:$X$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J41:J42">
-    <cfRule type="cellIs" dxfId="14" priority="14" operator="equal">
-      <formula>MAX($J$14:$J$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V41:V42">
-    <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
-      <formula>MAX($V$14:$V$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S41:S42">
-    <cfRule type="cellIs" dxfId="12" priority="16" operator="equal">
-      <formula>MAX($S$14:$S$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N41:N42">
-    <cfRule type="cellIs" dxfId="11" priority="17" operator="equal">
-      <formula>MAX($N$14:$N$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P41:P42">
-    <cfRule type="cellIs" dxfId="10" priority="18" operator="equal">
-      <formula>MAX($P$14:$P$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L40">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
-      <formula>MAX($L$14:$L$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T40">
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
-      <formula>MAX($T$14:$T$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X40">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
-      <formula>MAX($X$14:$X$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J40">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
-      <formula>MAX($J$14:$J$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V40">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
-      <formula>MAX($V$14:$V$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S40">
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
-      <formula>MAX($S$14:$S$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N40">
-    <cfRule type="cellIs" dxfId="3" priority="9" operator="equal">
-      <formula>MAX($N$14:$N$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P40">
-    <cfRule type="cellIs" dxfId="2" priority="10" operator="equal">
-      <formula>MAX($P$14:$P$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D40:D42">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>MAX($D$14:$D$42)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G40:G42">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>MAX($G$14:$G$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19769,6 +19914,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E3C748FF7EC2ED4E8EAD43CD1EEC2D0E" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ea203103aa5aa41fa7dd49b43cb8a2de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xmlns:ns3="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49b0a91519af75797ffa607b75695ffb" ns2:_="" ns3:_="">
     <xsd:import namespace="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
@@ -20015,29 +20182,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5BCA511-7B91-4B72-B4F3-8175C2C806EF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F8AAD19-02EA-4280-B365-8810DF5CEEF3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3450C23-B9A2-45D4-8942-0C308DF3F8F2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20054,23 +20218,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F8AAD19-02EA-4280-B365-8810DF5CEEF3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5BCA511-7B91-4B72-B4F3-8175C2C806EF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
-    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/seat/06-junio2026.xlsx
+++ b/data/seat/06-junio2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoefe.sharepoint.com/sites/GOFEFEVALPARASO/Documentos compartidos/UNIDAD DE GESTION/Datos Operacionales/Energía/SEAT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoefe.sharepoint.com/sites/GOFEFEVALPARASO/Documentos compartidos/UNIDAD DE GESTION/Datos Operacionales/Energía/SEAT/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="6_{022934C4-186F-4BE2-B034-0206DAC59087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44CA7CAF-F811-49F2-9643-F63B369A3379}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="6_{022934C4-186F-4BE2-B034-0206DAC59087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DCC99C0-3FE5-4C63-9364-A866B40F38E2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2124,6 +2124,60 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2154,39 +2208,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2199,31 +2220,10 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2322,7 +2322,77 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="140">
+  <dxfs count="145">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2971,41 +3041,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4591,7 +4626,7 @@
                   <c:v>2541.4300000000003</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0</c:v>
+                  <c:v>3220.5499999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7485,293 +7520,293 @@
       <c r="A1" s="126">
         <v>1.1111111E+55</v>
       </c>
-      <c r="B1" s="218" t="s">
+      <c r="B1" s="236" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="127"/>
-      <c r="D1" s="220" t="s">
+      <c r="D1" s="238" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="221"/>
-      <c r="F1" s="221"/>
-      <c r="G1" s="221"/>
-      <c r="H1" s="221"/>
-      <c r="I1" s="221"/>
-      <c r="J1" s="221"/>
-      <c r="K1" s="221"/>
-      <c r="L1" s="221"/>
-      <c r="M1" s="221"/>
-      <c r="N1" s="221"/>
-      <c r="O1" s="222"/>
-      <c r="P1" s="223"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="239"/>
+      <c r="H1" s="239"/>
+      <c r="I1" s="239"/>
+      <c r="J1" s="239"/>
+      <c r="K1" s="239"/>
+      <c r="L1" s="239"/>
+      <c r="M1" s="239"/>
+      <c r="N1" s="239"/>
+      <c r="O1" s="240"/>
+      <c r="P1" s="241"/>
       <c r="Q1" s="128"/>
-      <c r="R1" s="228" t="s">
+      <c r="R1" s="218" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="229"/>
-      <c r="T1" s="229"/>
-      <c r="U1" s="229"/>
-      <c r="V1" s="229"/>
-      <c r="W1" s="229"/>
-      <c r="X1" s="229"/>
-      <c r="Y1" s="229"/>
-      <c r="Z1" s="229"/>
-      <c r="AA1" s="230"/>
+      <c r="S1" s="219"/>
+      <c r="T1" s="219"/>
+      <c r="U1" s="219"/>
+      <c r="V1" s="219"/>
+      <c r="W1" s="219"/>
+      <c r="X1" s="219"/>
+      <c r="Y1" s="219"/>
+      <c r="Z1" s="219"/>
+      <c r="AA1" s="220"/>
       <c r="AB1" s="129"/>
-      <c r="AC1" s="228" t="s">
+      <c r="AC1" s="218" t="s">
         <v>3</v>
       </c>
-      <c r="AD1" s="229"/>
-      <c r="AE1" s="229"/>
-      <c r="AF1" s="229"/>
-      <c r="AG1" s="229"/>
-      <c r="AH1" s="229"/>
-      <c r="AI1" s="229"/>
-      <c r="AJ1" s="229"/>
-      <c r="AK1" s="230"/>
+      <c r="AD1" s="219"/>
+      <c r="AE1" s="219"/>
+      <c r="AF1" s="219"/>
+      <c r="AG1" s="219"/>
+      <c r="AH1" s="219"/>
+      <c r="AI1" s="219"/>
+      <c r="AJ1" s="219"/>
+      <c r="AK1" s="220"/>
       <c r="AL1" s="130"/>
-      <c r="AM1" s="228" t="s">
+      <c r="AM1" s="218" t="s">
         <v>4</v>
       </c>
-      <c r="AN1" s="229"/>
-      <c r="AO1" s="229"/>
-      <c r="AP1" s="229"/>
-      <c r="AQ1" s="229"/>
-      <c r="AR1" s="229"/>
-      <c r="AS1" s="229"/>
-      <c r="AT1" s="229"/>
-      <c r="AU1" s="230"/>
+      <c r="AN1" s="219"/>
+      <c r="AO1" s="219"/>
+      <c r="AP1" s="219"/>
+      <c r="AQ1" s="219"/>
+      <c r="AR1" s="219"/>
+      <c r="AS1" s="219"/>
+      <c r="AT1" s="219"/>
+      <c r="AU1" s="220"/>
       <c r="AV1" s="130"/>
-      <c r="AW1" s="228" t="s">
+      <c r="AW1" s="218" t="s">
         <v>57</v>
       </c>
-      <c r="AX1" s="229"/>
-      <c r="AY1" s="229"/>
-      <c r="AZ1" s="229"/>
-      <c r="BA1" s="229"/>
-      <c r="BB1" s="229"/>
-      <c r="BC1" s="229"/>
-      <c r="BD1" s="229"/>
-      <c r="BE1" s="229"/>
-      <c r="BF1" s="229"/>
-      <c r="BG1" s="229"/>
-      <c r="BH1" s="230"/>
+      <c r="AX1" s="219"/>
+      <c r="AY1" s="219"/>
+      <c r="AZ1" s="219"/>
+      <c r="BA1" s="219"/>
+      <c r="BB1" s="219"/>
+      <c r="BC1" s="219"/>
+      <c r="BD1" s="219"/>
+      <c r="BE1" s="219"/>
+      <c r="BF1" s="219"/>
+      <c r="BG1" s="219"/>
+      <c r="BH1" s="220"/>
       <c r="BI1" s="130"/>
-      <c r="BJ1" s="228" t="s">
+      <c r="BJ1" s="218" t="s">
         <v>5</v>
       </c>
-      <c r="BK1" s="229"/>
-      <c r="BL1" s="229"/>
-      <c r="BM1" s="229"/>
-      <c r="BN1" s="229"/>
-      <c r="BO1" s="229"/>
-      <c r="BP1" s="229"/>
-      <c r="BQ1" s="229"/>
-      <c r="BR1" s="230"/>
+      <c r="BK1" s="219"/>
+      <c r="BL1" s="219"/>
+      <c r="BM1" s="219"/>
+      <c r="BN1" s="219"/>
+      <c r="BO1" s="219"/>
+      <c r="BP1" s="219"/>
+      <c r="BQ1" s="219"/>
+      <c r="BR1" s="220"/>
       <c r="BS1" s="131"/>
     </row>
     <row r="2" spans="1:71" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="218"/>
+      <c r="B2" s="236"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="224"/>
-      <c r="E2" s="225"/>
-      <c r="F2" s="225"/>
-      <c r="G2" s="225"/>
-      <c r="H2" s="225"/>
-      <c r="I2" s="225"/>
-      <c r="J2" s="225"/>
-      <c r="K2" s="225"/>
-      <c r="L2" s="225"/>
-      <c r="M2" s="225"/>
-      <c r="N2" s="225"/>
-      <c r="O2" s="226"/>
-      <c r="P2" s="227"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="243"/>
+      <c r="H2" s="243"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
+      <c r="M2" s="243"/>
+      <c r="N2" s="243"/>
+      <c r="O2" s="244"/>
+      <c r="P2" s="245"/>
       <c r="Q2" s="57"/>
-      <c r="R2" s="231"/>
-      <c r="S2" s="232"/>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232"/>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
-      <c r="AA2" s="233"/>
+      <c r="R2" s="221"/>
+      <c r="S2" s="222"/>
+      <c r="T2" s="222"/>
+      <c r="U2" s="222"/>
+      <c r="V2" s="222"/>
+      <c r="W2" s="222"/>
+      <c r="X2" s="222"/>
+      <c r="Y2" s="222"/>
+      <c r="Z2" s="222"/>
+      <c r="AA2" s="223"/>
       <c r="AB2" s="59"/>
-      <c r="AC2" s="231"/>
-      <c r="AD2" s="232"/>
-      <c r="AE2" s="232"/>
-      <c r="AF2" s="232"/>
-      <c r="AG2" s="232"/>
-      <c r="AH2" s="232"/>
-      <c r="AI2" s="232"/>
-      <c r="AJ2" s="232"/>
-      <c r="AK2" s="233"/>
+      <c r="AC2" s="221"/>
+      <c r="AD2" s="222"/>
+      <c r="AE2" s="222"/>
+      <c r="AF2" s="222"/>
+      <c r="AG2" s="222"/>
+      <c r="AH2" s="222"/>
+      <c r="AI2" s="222"/>
+      <c r="AJ2" s="222"/>
+      <c r="AK2" s="223"/>
       <c r="AL2" s="58"/>
-      <c r="AM2" s="231"/>
-      <c r="AN2" s="232"/>
-      <c r="AO2" s="232"/>
-      <c r="AP2" s="232"/>
-      <c r="AQ2" s="232"/>
-      <c r="AR2" s="232"/>
-      <c r="AS2" s="232"/>
-      <c r="AT2" s="232"/>
-      <c r="AU2" s="233"/>
+      <c r="AM2" s="221"/>
+      <c r="AN2" s="222"/>
+      <c r="AO2" s="222"/>
+      <c r="AP2" s="222"/>
+      <c r="AQ2" s="222"/>
+      <c r="AR2" s="222"/>
+      <c r="AS2" s="222"/>
+      <c r="AT2" s="222"/>
+      <c r="AU2" s="223"/>
       <c r="AV2" s="58"/>
-      <c r="AW2" s="231"/>
-      <c r="AX2" s="232"/>
-      <c r="AY2" s="232"/>
-      <c r="AZ2" s="232"/>
-      <c r="BA2" s="232"/>
-      <c r="BB2" s="232"/>
-      <c r="BC2" s="232"/>
-      <c r="BD2" s="232"/>
-      <c r="BE2" s="232"/>
-      <c r="BF2" s="232"/>
-      <c r="BG2" s="232"/>
-      <c r="BH2" s="233"/>
+      <c r="AW2" s="221"/>
+      <c r="AX2" s="222"/>
+      <c r="AY2" s="222"/>
+      <c r="AZ2" s="222"/>
+      <c r="BA2" s="222"/>
+      <c r="BB2" s="222"/>
+      <c r="BC2" s="222"/>
+      <c r="BD2" s="222"/>
+      <c r="BE2" s="222"/>
+      <c r="BF2" s="222"/>
+      <c r="BG2" s="222"/>
+      <c r="BH2" s="223"/>
       <c r="BI2" s="58"/>
-      <c r="BJ2" s="231"/>
-      <c r="BK2" s="232"/>
-      <c r="BL2" s="232"/>
-      <c r="BM2" s="232"/>
-      <c r="BN2" s="232"/>
-      <c r="BO2" s="232"/>
-      <c r="BP2" s="232"/>
-      <c r="BQ2" s="232"/>
-      <c r="BR2" s="233"/>
+      <c r="BJ2" s="221"/>
+      <c r="BK2" s="222"/>
+      <c r="BL2" s="222"/>
+      <c r="BM2" s="222"/>
+      <c r="BN2" s="222"/>
+      <c r="BO2" s="222"/>
+      <c r="BP2" s="222"/>
+      <c r="BQ2" s="222"/>
+      <c r="BR2" s="223"/>
       <c r="BS2" s="134"/>
     </row>
     <row r="3" spans="1:71" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="218"/>
+      <c r="B3" s="236"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="237" t="s">
+      <c r="D3" s="224" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="237" t="s">
+      <c r="E3" s="224" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="237" t="s">
+      <c r="F3" s="224" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="237" t="s">
+      <c r="G3" s="224" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="237" t="s">
+      <c r="H3" s="224" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="239" t="s">
+      <c r="I3" s="246" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="240"/>
-      <c r="K3" s="241"/>
-      <c r="L3" s="242"/>
-      <c r="M3" s="239" t="s">
+      <c r="J3" s="247"/>
+      <c r="K3" s="248"/>
+      <c r="L3" s="249"/>
+      <c r="M3" s="246" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="240"/>
-      <c r="O3" s="241"/>
-      <c r="P3" s="242"/>
+      <c r="N3" s="247"/>
+      <c r="O3" s="248"/>
+      <c r="P3" s="249"/>
       <c r="Q3" s="57"/>
-      <c r="R3" s="243" t="s">
+      <c r="R3" s="228" t="s">
         <v>13</v>
       </c>
-      <c r="S3" s="235"/>
-      <c r="T3" s="244"/>
-      <c r="U3" s="244"/>
-      <c r="V3" s="243" t="s">
+      <c r="S3" s="229"/>
+      <c r="T3" s="250"/>
+      <c r="U3" s="250"/>
+      <c r="V3" s="228" t="s">
         <v>14</v>
       </c>
-      <c r="W3" s="235"/>
-      <c r="X3" s="235"/>
-      <c r="Y3" s="235"/>
-      <c r="Z3" s="235"/>
-      <c r="AA3" s="236"/>
+      <c r="W3" s="229"/>
+      <c r="X3" s="229"/>
+      <c r="Y3" s="229"/>
+      <c r="Z3" s="229"/>
+      <c r="AA3" s="230"/>
       <c r="AB3" s="59"/>
-      <c r="AC3" s="245" t="s">
+      <c r="AC3" s="226" t="s">
         <v>15</v>
       </c>
-      <c r="AD3" s="247" t="s">
+      <c r="AD3" s="251" t="s">
         <v>9</v>
       </c>
-      <c r="AE3" s="243" t="s">
+      <c r="AE3" s="228" t="s">
         <v>13</v>
       </c>
-      <c r="AF3" s="235"/>
-      <c r="AG3" s="236"/>
-      <c r="AH3" s="243" t="s">
+      <c r="AF3" s="229"/>
+      <c r="AG3" s="230"/>
+      <c r="AH3" s="228" t="s">
         <v>14</v>
       </c>
-      <c r="AI3" s="235"/>
-      <c r="AJ3" s="235"/>
-      <c r="AK3" s="236"/>
+      <c r="AI3" s="229"/>
+      <c r="AJ3" s="229"/>
+      <c r="AK3" s="230"/>
       <c r="AL3" s="58"/>
-      <c r="AM3" s="248" t="s">
+      <c r="AM3" s="231" t="s">
         <v>15</v>
       </c>
-      <c r="AN3" s="245" t="s">
+      <c r="AN3" s="226" t="s">
         <v>9</v>
       </c>
-      <c r="AO3" s="234" t="s">
+      <c r="AO3" s="235" t="s">
         <v>13</v>
       </c>
-      <c r="AP3" s="235"/>
-      <c r="AQ3" s="236"/>
-      <c r="AR3" s="243" t="s">
+      <c r="AP3" s="229"/>
+      <c r="AQ3" s="230"/>
+      <c r="AR3" s="228" t="s">
         <v>14</v>
       </c>
-      <c r="AS3" s="235"/>
-      <c r="AT3" s="235"/>
-      <c r="AU3" s="236"/>
+      <c r="AS3" s="229"/>
+      <c r="AT3" s="229"/>
+      <c r="AU3" s="230"/>
       <c r="AV3" s="58"/>
-      <c r="AW3" s="245" t="s">
+      <c r="AW3" s="226" t="s">
         <v>15</v>
       </c>
-      <c r="AX3" s="245" t="s">
+      <c r="AX3" s="226" t="s">
         <v>9</v>
       </c>
-      <c r="AY3" s="234" t="s">
+      <c r="AY3" s="235" t="s">
         <v>13</v>
       </c>
-      <c r="AZ3" s="234"/>
-      <c r="BA3" s="235"/>
-      <c r="BB3" s="236"/>
-      <c r="BC3" s="243" t="s">
+      <c r="AZ3" s="235"/>
+      <c r="BA3" s="229"/>
+      <c r="BB3" s="230"/>
+      <c r="BC3" s="228" t="s">
         <v>14</v>
       </c>
-      <c r="BD3" s="234"/>
-      <c r="BE3" s="234"/>
-      <c r="BF3" s="235"/>
-      <c r="BG3" s="235"/>
-      <c r="BH3" s="236"/>
+      <c r="BD3" s="235"/>
+      <c r="BE3" s="235"/>
+      <c r="BF3" s="229"/>
+      <c r="BG3" s="229"/>
+      <c r="BH3" s="230"/>
       <c r="BI3" s="58"/>
-      <c r="BJ3" s="248" t="s">
+      <c r="BJ3" s="231" t="s">
         <v>16</v>
       </c>
-      <c r="BK3" s="245" t="s">
+      <c r="BK3" s="226" t="s">
         <v>17</v>
       </c>
-      <c r="BL3" s="249" t="s">
+      <c r="BL3" s="232" t="s">
         <v>18</v>
       </c>
-      <c r="BM3" s="250"/>
-      <c r="BN3" s="251"/>
-      <c r="BO3" s="234" t="s">
+      <c r="BM3" s="233"/>
+      <c r="BN3" s="234"/>
+      <c r="BO3" s="235" t="s">
         <v>14</v>
       </c>
-      <c r="BP3" s="235"/>
-      <c r="BQ3" s="235"/>
-      <c r="BR3" s="236"/>
+      <c r="BP3" s="229"/>
+      <c r="BQ3" s="229"/>
+      <c r="BR3" s="230"/>
       <c r="BS3" s="134"/>
     </row>
     <row r="4" spans="1:71" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="219"/>
+      <c r="B4" s="237"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="238"/>
-      <c r="E4" s="238"/>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
-      <c r="H4" s="238"/>
+      <c r="D4" s="225"/>
+      <c r="E4" s="225"/>
+      <c r="F4" s="225"/>
+      <c r="G4" s="225"/>
+      <c r="H4" s="225"/>
       <c r="I4" s="79" t="s">
         <v>3</v>
       </c>
@@ -7828,8 +7863,8 @@
         <v>24</v>
       </c>
       <c r="AB4" s="59"/>
-      <c r="AC4" s="246"/>
-      <c r="AD4" s="229"/>
+      <c r="AC4" s="227"/>
+      <c r="AD4" s="219"/>
       <c r="AE4" s="61" t="s">
         <v>27</v>
       </c>
@@ -7852,8 +7887,8 @@
         <v>24</v>
       </c>
       <c r="AL4" s="60"/>
-      <c r="AM4" s="228"/>
-      <c r="AN4" s="246"/>
+      <c r="AM4" s="218"/>
+      <c r="AN4" s="227"/>
       <c r="AO4" s="122" t="s">
         <v>27</v>
       </c>
@@ -7876,8 +7911,8 @@
         <v>24</v>
       </c>
       <c r="AV4" s="60"/>
-      <c r="AW4" s="246"/>
-      <c r="AX4" s="246"/>
+      <c r="AW4" s="227"/>
+      <c r="AX4" s="227"/>
       <c r="AY4" s="122" t="s">
         <v>27</v>
       </c>
@@ -7909,8 +7944,8 @@
         <v>24</v>
       </c>
       <c r="BI4" s="60"/>
-      <c r="BJ4" s="228"/>
-      <c r="BK4" s="246"/>
+      <c r="BJ4" s="218"/>
+      <c r="BK4" s="227"/>
       <c r="BL4" s="122" t="s">
         <v>32</v>
       </c>
@@ -9307,11 +9342,11 @@
         <v>46178</v>
       </c>
       <c r="AC11" s="75">
-        <f t="shared" ref="AC11:AC35" si="46">+AF11/AE11</f>
+        <f t="shared" ref="AC11:AC36" si="46">+AF11/AE11</f>
         <v>1</v>
       </c>
       <c r="AD11" s="161">
-        <f t="shared" ref="AD11:AD35" si="47">+AG11/AE11</f>
+        <f t="shared" ref="AD11:AD36" si="47">+AG11/AE11</f>
         <v>0</v>
       </c>
       <c r="AE11" s="162">
@@ -9341,7 +9376,7 @@
         <v>46178</v>
       </c>
       <c r="AM11" s="76">
-        <f t="shared" ref="AM11:AM35" si="48">+AP11/AO11</f>
+        <f t="shared" ref="AM11:AM36" si="48">+AP11/AO11</f>
         <v>0.60748468606431849</v>
       </c>
       <c r="AN11" s="75">
@@ -9375,11 +9410,11 @@
         <v>46178</v>
       </c>
       <c r="AW11" s="109">
-        <f t="shared" ref="AW11:AW35" si="50">BA11/AZ11</f>
+        <f t="shared" ref="AW11:AW36" si="50">BA11/AZ11</f>
         <v>0.63236836584854206</v>
       </c>
       <c r="AX11" s="109">
-        <f t="shared" ref="AX11:AX35" si="51">BB11/AZ11</f>
+        <f t="shared" ref="AX11:AX36" si="51">BB11/AZ11</f>
         <v>0.36763163415145794</v>
       </c>
       <c r="AY11" s="110">
@@ -9420,15 +9455,15 @@
         <v>46178</v>
       </c>
       <c r="BJ11" s="77">
-        <f t="shared" ref="BJ11:BJ35" si="52">+BM11/BL11</f>
+        <f t="shared" ref="BJ11:BJ36" si="52">+BM11/BL11</f>
         <v>0.60549950105333183</v>
       </c>
       <c r="BK11" s="75">
-        <f t="shared" ref="BK11:BK35" si="53">+BN11/BL11</f>
+        <f t="shared" ref="BK11:BK36" si="53">+BN11/BL11</f>
         <v>0.39450049894666817</v>
       </c>
       <c r="BL11" s="78">
-        <f t="shared" ref="BL11:BL35" si="54">BM11+BN11</f>
+        <f t="shared" ref="BL11:BL36" si="54">BM11+BN11</f>
         <v>36076</v>
       </c>
       <c r="BM11" s="154">
@@ -15118,7 +15153,7 @@
         <v>0.29661784287616516</v>
       </c>
       <c r="AN35" s="75">
-        <f t="shared" ref="AN35" si="63">+AQ35/AO35</f>
+        <f t="shared" ref="AN35:AN36" si="63">+AQ35/AO35</f>
         <v>0.70338215712383489</v>
       </c>
       <c r="AO35" s="149">
@@ -15225,171 +15260,244 @@
     </row>
     <row r="36" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="14"/>
-      <c r="B36" s="55">
+      <c r="B36" s="167">
         <f t="shared" si="37"/>
         <v>46203</v>
       </c>
-      <c r="C36" s="163"/>
+      <c r="C36" s="217"/>
       <c r="D36" s="86">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E36" s="158" t="e">
+        <f>R36+S36</f>
+        <v>58638</v>
+      </c>
+      <c r="E36" s="158">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.87303796173130044</v>
       </c>
       <c r="F36" s="86">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G36" s="158" t="e">
+        <v>51193.2</v>
+      </c>
+      <c r="G36" s="158">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>0.12696203826869948</v>
       </c>
       <c r="H36" s="145">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I36" s="159" t="e">
+        <v>7444.8</v>
+      </c>
+      <c r="I36" s="159">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J36" s="158" t="e">
+        <v>0.12131587009803922</v>
+      </c>
+      <c r="J36" s="158">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K36" s="158" t="e">
+        <v>0.15663296568627452</v>
+      </c>
+      <c r="K36" s="158">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L36" s="160" t="e">
+        <v>0.17157384741921888</v>
+      </c>
+      <c r="L36" s="160">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M36" s="145" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N36" s="145" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O36" s="145" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P36" s="145" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q36" s="55">
+        <v>0.57457873774509804</v>
+      </c>
+      <c r="M36" s="145">
+        <f>(S36+R36)*I36</f>
+        <v>7113.7199908088242</v>
+      </c>
+      <c r="N36" s="145">
+        <f>(S36+R36)*J36</f>
+        <v>9184.6438419117658</v>
+      </c>
+      <c r="O36" s="145">
+        <f>(S36+R36)*K36</f>
+        <v>10060.747264968157</v>
+      </c>
+      <c r="P36" s="145">
+        <f>(S36+R36)*L36</f>
+        <v>33692.148023897062</v>
+      </c>
+      <c r="Q36" s="167">
         <f t="shared" si="38"/>
         <v>46203</v>
       </c>
-      <c r="R36" s="138"/>
-      <c r="S36" s="139"/>
-      <c r="T36" s="139"/>
-      <c r="U36" s="139"/>
-      <c r="V36" s="140"/>
-      <c r="W36" s="141"/>
-      <c r="X36" s="140"/>
-      <c r="Y36" s="141"/>
-      <c r="Z36" s="140"/>
-      <c r="AA36" s="141"/>
-      <c r="AB36" s="55">
+      <c r="R36" s="139">
+        <v>58638</v>
+      </c>
+      <c r="S36" s="139">
+        <v>0</v>
+      </c>
+      <c r="T36" s="139">
+        <v>57394</v>
+      </c>
+      <c r="U36" s="139">
+        <v>0</v>
+      </c>
+      <c r="V36" s="140">
+        <v>14064.68</v>
+      </c>
+      <c r="W36" s="141">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="X36" s="140">
+        <v>4782.46</v>
+      </c>
+      <c r="Y36" s="141">
+        <v>0.40625</v>
+      </c>
+      <c r="Z36" s="140">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="141">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="167">
         <f t="shared" si="39"/>
         <v>46203</v>
       </c>
-      <c r="AC36" s="75" t="e">
-        <f t="shared" ref="AC36" si="64">+AF36/AE36</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD36" s="161" t="e">
-        <f t="shared" ref="AD36" si="65">+AG36/AE36</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE36" s="162"/>
+      <c r="AC36" s="75">
+        <f t="shared" si="46"/>
+        <v>1</v>
+      </c>
+      <c r="AD36" s="161">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="AE36" s="162">
+        <v>7919.5</v>
+      </c>
       <c r="AF36" s="117">
         <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="AG36" s="146"/>
-      <c r="AH36" s="147"/>
-      <c r="AI36" s="148"/>
-      <c r="AJ36" s="147"/>
-      <c r="AK36" s="164"/>
-      <c r="AL36" s="55">
+        <v>7919.5</v>
+      </c>
+      <c r="AG36" s="146">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="147">
+        <v>4071.65</v>
+      </c>
+      <c r="AI36" s="148">
+        <v>0.34444444444444444</v>
+      </c>
+      <c r="AJ36" s="147">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="164">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="167">
         <f t="shared" si="28"/>
         <v>46203</v>
       </c>
-      <c r="AM36" s="76" t="e">
-        <f t="shared" ref="AM36" si="66">+AP36/AO36</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AN36" s="75" t="e">
-        <f t="shared" ref="AN36" si="67">+AQ36/AO36</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AO36" s="149"/>
+      <c r="AM36" s="76">
+        <f t="shared" si="48"/>
+        <v>0.61036185819070898</v>
+      </c>
+      <c r="AN36" s="75">
+        <f t="shared" si="63"/>
+        <v>0.38963814180929096</v>
+      </c>
+      <c r="AO36" s="149">
+        <v>10225</v>
+      </c>
       <c r="AP36" s="116">
         <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="AQ36" s="150"/>
-      <c r="AR36" s="151"/>
-      <c r="AS36" s="152"/>
-      <c r="AT36" s="151"/>
-      <c r="AU36" s="153"/>
-      <c r="AV36" s="55">
+        <v>6240.95</v>
+      </c>
+      <c r="AQ36" s="150">
+        <v>3984.05</v>
+      </c>
+      <c r="AR36" s="151">
+        <v>3875.13</v>
+      </c>
+      <c r="AS36" s="152">
+        <v>0.71805555555555556</v>
+      </c>
+      <c r="AT36" s="151">
+        <v>191.11</v>
+      </c>
+      <c r="AU36" s="153">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="AV36" s="167">
         <f t="shared" si="41"/>
         <v>46203</v>
       </c>
-      <c r="AW36" s="109" t="e">
-        <f t="shared" ref="AW36" si="68">BA36/AZ36</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AX36" s="109" t="e">
-        <f t="shared" ref="AX36" si="69">BB36/AZ36</f>
-        <v>#DIV/0!</v>
+      <c r="AW36" s="168">
+        <f t="shared" si="50"/>
+        <v>0.64051625636231435</v>
+      </c>
+      <c r="AX36" s="168">
+        <f t="shared" si="51"/>
+        <v>0.35948374363768565</v>
       </c>
       <c r="AY36" s="110">
         <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="AZ36" s="111"/>
-      <c r="BA36" s="119">
+        <v>9627</v>
+      </c>
+      <c r="AZ36" s="111">
+        <v>9627</v>
+      </c>
+      <c r="BA36" s="216">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="BB36" s="112"/>
-      <c r="BC36" s="111"/>
-      <c r="BD36" s="113"/>
-      <c r="BE36" s="114"/>
-      <c r="BF36" s="113"/>
-      <c r="BG36" s="114"/>
-      <c r="BH36" s="113"/>
-      <c r="BI36" s="55">
+        <v>6166.25</v>
+      </c>
+      <c r="BB36" s="112">
+        <f>2889.75+571</f>
+        <v>3460.75</v>
+      </c>
+      <c r="BC36" s="111">
+        <v>3669.13</v>
+      </c>
+      <c r="BD36" s="113">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="BE36" s="114">
+        <v>0</v>
+      </c>
+      <c r="BF36" s="113">
+        <v>0</v>
+      </c>
+      <c r="BG36" s="114">
+        <v>169.5</v>
+      </c>
+      <c r="BH36" s="113">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="BI36" s="167">
         <f t="shared" si="43"/>
         <v>46203</v>
       </c>
-      <c r="BJ36" s="77" t="e">
-        <f t="shared" ref="BJ36" si="70">+BM36/BL36</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BK36" s="75" t="e">
-        <f t="shared" ref="BK36" si="71">+BN36/BL36</f>
-        <v>#DIV/0!</v>
+      <c r="BJ36" s="169">
+        <f t="shared" si="52"/>
+        <v>0.6050761827319141</v>
+      </c>
+      <c r="BK36" s="75">
+        <f t="shared" si="53"/>
+        <v>0.3949238172680859</v>
       </c>
       <c r="BL36" s="78">
-        <f t="shared" ref="BL36" si="72">BM36+BN36</f>
-        <v>0</v>
-      </c>
-      <c r="BM36" s="154"/>
-      <c r="BN36" s="154"/>
-      <c r="BO36" s="155"/>
-      <c r="BP36" s="156"/>
-      <c r="BQ36" s="157"/>
-      <c r="BR36" s="156"/>
+        <f t="shared" si="54"/>
+        <v>37508.5</v>
+      </c>
+      <c r="BM36" s="154">
+        <v>22695.5</v>
+      </c>
+      <c r="BN36" s="154">
+        <v>14813</v>
+      </c>
+      <c r="BO36" s="155">
+        <v>1212.9100000000001</v>
+      </c>
+      <c r="BP36" s="156">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="BQ36" s="157">
+        <v>2821.84</v>
+      </c>
+      <c r="BR36" s="156">
+        <v>0.41666666666666669</v>
+      </c>
     </row>
     <row r="37" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="55">
@@ -15467,11 +15575,11 @@
         <v>46204</v>
       </c>
       <c r="AC37" s="75" t="e">
-        <f t="shared" ref="AC37" si="73">+AF37/AE37</f>
+        <f t="shared" ref="AC37" si="64">+AF37/AE37</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AD37" s="161" t="e">
-        <f t="shared" ref="AD37" si="74">+AG37/AE37</f>
+        <f t="shared" ref="AD37" si="65">+AG37/AE37</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AE37" s="162"/>
@@ -15489,16 +15597,16 @@
         <v>46204</v>
       </c>
       <c r="AM37" s="76" t="e">
-        <f t="shared" ref="AM37" si="75">+AP37/AO37</f>
+        <f t="shared" ref="AM37" si="66">+AP37/AO37</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AN37" s="75" t="e">
-        <f t="shared" ref="AN37" si="76">+AQ37/AO37</f>
+        <f t="shared" ref="AN37" si="67">+AQ37/AO37</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AO37" s="149"/>
       <c r="AP37" s="116">
-        <f t="shared" ref="AP37" si="77">AO37-AQ37</f>
+        <f t="shared" ref="AP37" si="68">AO37-AQ37</f>
         <v>0</v>
       </c>
       <c r="AQ37" s="150"/>
@@ -15511,11 +15619,11 @@
         <v>46204</v>
       </c>
       <c r="AW37" s="109" t="e">
-        <f t="shared" ref="AW37" si="78">BA37/AZ37</f>
+        <f t="shared" ref="AW37" si="69">BA37/AZ37</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AX37" s="109" t="e">
-        <f t="shared" ref="AX37" si="79">BB37/AZ37</f>
+        <f t="shared" ref="AX37" si="70">BB37/AZ37</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AY37" s="110">
@@ -15539,15 +15647,15 @@
         <v>46204</v>
       </c>
       <c r="BJ37" s="77" t="e">
-        <f t="shared" ref="BJ37" si="80">+BM37/BL37</f>
+        <f t="shared" ref="BJ37" si="71">+BM37/BL37</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BK37" s="75" t="e">
-        <f t="shared" ref="BK37" si="81">+BN37/BL37</f>
+        <f t="shared" ref="BK37" si="72">+BN37/BL37</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BL37" s="78">
-        <f t="shared" ref="BL37" si="82">BM37+BN37</f>
+        <f t="shared" ref="BL37" si="73">BM37+BN37</f>
         <v>0</v>
       </c>
       <c r="BM37" s="154"/>
@@ -15578,7 +15686,7 @@
     <row r="39" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="S39" s="175">
         <f>R36-T36</f>
-        <v>0</v>
+        <v>1244</v>
       </c>
       <c r="T39" s="175"/>
       <c r="U39" s="174"/>
@@ -15601,6 +15709,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="D1:P2"/>
+    <mergeCell ref="R1:AA2"/>
+    <mergeCell ref="AC1:AK2"/>
+    <mergeCell ref="AM1:AU2"/>
+    <mergeCell ref="AO3:AQ3"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:AA3"/>
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="AD3:AD4"/>
+    <mergeCell ref="AE3:AG3"/>
+    <mergeCell ref="AH3:AK3"/>
+    <mergeCell ref="AM3:AM4"/>
     <mergeCell ref="BJ1:BR2"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
@@ -15617,22 +15741,6 @@
     <mergeCell ref="AX3:AX4"/>
     <mergeCell ref="AY3:BB3"/>
     <mergeCell ref="BC3:BH3"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="D1:P2"/>
-    <mergeCell ref="R1:AA2"/>
-    <mergeCell ref="AC1:AK2"/>
-    <mergeCell ref="AM1:AU2"/>
-    <mergeCell ref="AO3:AQ3"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="M3:P3"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:AA3"/>
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="AD3:AD4"/>
-    <mergeCell ref="AE3:AG3"/>
-    <mergeCell ref="AH3:AK3"/>
-    <mergeCell ref="AM3:AM4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="88" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -18165,45 +18273,78 @@
       </c>
     </row>
     <row r="44" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="89">
+      <c r="B44" s="173">
         <f t="shared" si="5"/>
         <v>46203</v>
       </c>
-      <c r="D44" s="170"/>
-      <c r="E44" s="88"/>
-      <c r="F44" s="87"/>
-      <c r="G44" s="92">
+      <c r="C44" s="52"/>
+      <c r="D44" s="190">
+        <v>131.57</v>
+      </c>
+      <c r="E44" s="189">
+        <v>0.34375</v>
+      </c>
+      <c r="F44" s="188">
+        <v>1468.22</v>
+      </c>
+      <c r="G44" s="192">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H44" s="87"/>
-      <c r="I44" s="89">
+        <v>965.96</v>
+      </c>
+      <c r="H44" s="188">
+        <v>502.26</v>
+      </c>
+      <c r="I44" s="173">
         <f t="shared" si="3"/>
         <v>46203</v>
       </c>
-      <c r="J44" s="90"/>
-      <c r="K44" s="88"/>
-      <c r="L44" s="87"/>
-      <c r="M44" s="89">
+      <c r="J44" s="190">
+        <v>35.74</v>
+      </c>
+      <c r="K44" s="189">
+        <v>9.375E-2</v>
+      </c>
+      <c r="L44" s="188">
+        <v>667.4</v>
+      </c>
+      <c r="M44" s="173">
         <f t="shared" si="4"/>
         <v>46203</v>
       </c>
-      <c r="N44" s="90"/>
-      <c r="O44" s="88"/>
-      <c r="P44" s="90"/>
-      <c r="Q44" s="88"/>
-      <c r="R44" s="91">
+      <c r="N44" s="190">
+        <v>20.89</v>
+      </c>
+      <c r="O44" s="189">
+        <v>0.625</v>
+      </c>
+      <c r="P44" s="190">
+        <v>10.96</v>
+      </c>
+      <c r="Q44" s="189">
+        <v>0.53125</v>
+      </c>
+      <c r="R44" s="191">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="S44" s="87"/>
-      <c r="T44" s="87"/>
-      <c r="U44" s="89">
+        <v>518.56000000000006</v>
+      </c>
+      <c r="S44" s="188">
+        <v>331.79</v>
+      </c>
+      <c r="T44" s="188">
+        <v>186.77</v>
+      </c>
+      <c r="U44" s="173">
         <v>46203</v>
       </c>
-      <c r="V44" s="90"/>
-      <c r="W44" s="88"/>
-      <c r="X44" s="87"/>
+      <c r="V44" s="190">
+        <v>31.87</v>
+      </c>
+      <c r="W44" s="189">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="X44" s="188">
+        <v>566.37</v>
+      </c>
     </row>
     <row r="45" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B45" s="89">
@@ -19140,29 +19281,29 @@
       <c r="D78" s="179">
         <v>45868</v>
       </c>
-      <c r="E78" s="177" t="e">
+      <c r="E78" s="177">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F78" s="177" t="e">
+        <v>0.45589107450590743</v>
+      </c>
+      <c r="F78" s="177">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G78" s="177" t="e">
+        <v>0.20723168402912548</v>
+      </c>
+      <c r="G78" s="177">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H78" s="177" t="e">
+        <v>0.10302277561286118</v>
+      </c>
+      <c r="H78" s="177">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I78" s="177" t="e">
+        <v>5.7993199919268455E-2</v>
+      </c>
+      <c r="I78" s="177">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>0.17586126593283757</v>
       </c>
       <c r="J78" s="178">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3220.5499999999997</v>
       </c>
     </row>
     <row r="79" spans="4:10" x14ac:dyDescent="0.25">
@@ -19210,668 +19351,673 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="L16:L19 L27:L32 L21:L25">
-    <cfRule type="cellIs" dxfId="139" priority="387" operator="equal">
+    <cfRule type="cellIs" dxfId="144" priority="397" operator="equal">
       <formula>MAX($L$14:$L$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T16:T19 T27:T32 T21:T25">
-    <cfRule type="cellIs" dxfId="138" priority="388" operator="equal">
+    <cfRule type="cellIs" dxfId="143" priority="398" operator="equal">
       <formula>MAX($T$14:$T$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X16:X19 X27:X32 X21:X25">
-    <cfRule type="cellIs" dxfId="137" priority="389" operator="equal">
+    <cfRule type="cellIs" dxfId="142" priority="399" operator="equal">
       <formula>MAX($X$14:$X$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J16:J19 J27:J32 J21 J23:J25">
-    <cfRule type="cellIs" dxfId="136" priority="390" operator="equal">
+    <cfRule type="cellIs" dxfId="141" priority="400" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V16:V19 V27:V32 V21 V23">
-    <cfRule type="cellIs" dxfId="135" priority="391" operator="equal">
+    <cfRule type="cellIs" dxfId="140" priority="401" operator="equal">
       <formula>MAX($V$14:$V$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D19">
-    <cfRule type="cellIs" dxfId="134" priority="392" operator="equal">
+    <cfRule type="cellIs" dxfId="139" priority="402" operator="equal">
       <formula>MAX($D$14:$D$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S16:S19 S27:S32 S21:S25">
-    <cfRule type="cellIs" dxfId="133" priority="393" operator="equal">
+    <cfRule type="cellIs" dxfId="138" priority="403" operator="equal">
       <formula>MAX($S$14:$S$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N16:N19 N27:N32 N21 N23:N25">
-    <cfRule type="cellIs" dxfId="132" priority="394" operator="equal">
+    <cfRule type="cellIs" dxfId="137" priority="404" operator="equal">
       <formula>MAX($N$14:$N$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P16:P19 P27:P32 P21 P23:P25">
-    <cfRule type="cellIs" dxfId="131" priority="395" operator="equal">
+    <cfRule type="cellIs" dxfId="136" priority="405" operator="equal">
       <formula>MAX($P$14:$P$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L26">
-    <cfRule type="cellIs" dxfId="130" priority="319" operator="equal">
+    <cfRule type="cellIs" dxfId="135" priority="329" operator="equal">
       <formula>MAX($L$14:$L$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T26">
-    <cfRule type="cellIs" dxfId="129" priority="320" operator="equal">
+    <cfRule type="cellIs" dxfId="134" priority="330" operator="equal">
       <formula>MAX($T$14:$T$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X26">
-    <cfRule type="cellIs" dxfId="128" priority="321" operator="equal">
+    <cfRule type="cellIs" dxfId="133" priority="331" operator="equal">
       <formula>MAX($X$14:$X$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J26">
-    <cfRule type="cellIs" dxfId="127" priority="322" operator="equal">
+    <cfRule type="cellIs" dxfId="132" priority="332" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V26">
-    <cfRule type="cellIs" dxfId="126" priority="323" operator="equal">
+    <cfRule type="cellIs" dxfId="131" priority="333" operator="equal">
       <formula>MAX($V$14:$V$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S26">
-    <cfRule type="cellIs" dxfId="125" priority="325" operator="equal">
+    <cfRule type="cellIs" dxfId="130" priority="335" operator="equal">
       <formula>MAX($S$14:$S$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N26">
-    <cfRule type="cellIs" dxfId="124" priority="326" operator="equal">
+    <cfRule type="cellIs" dxfId="129" priority="336" operator="equal">
       <formula>MAX($N$14:$N$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P26">
-    <cfRule type="cellIs" dxfId="123" priority="327" operator="equal">
+    <cfRule type="cellIs" dxfId="128" priority="337" operator="equal">
       <formula>MAX($P$14:$P$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D20:D32 D45">
-    <cfRule type="cellIs" dxfId="122" priority="305" operator="equal">
+    <cfRule type="cellIs" dxfId="127" priority="315" operator="equal">
       <formula>MAX($D$14:$D$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L20">
-    <cfRule type="cellIs" dxfId="121" priority="296" operator="equal">
+    <cfRule type="cellIs" dxfId="126" priority="306" operator="equal">
       <formula>MAX($L$14:$L$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T20">
-    <cfRule type="cellIs" dxfId="120" priority="297" operator="equal">
+    <cfRule type="cellIs" dxfId="125" priority="307" operator="equal">
       <formula>MAX($T$14:$T$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X20">
-    <cfRule type="cellIs" dxfId="119" priority="298" operator="equal">
+    <cfRule type="cellIs" dxfId="124" priority="308" operator="equal">
       <formula>MAX($X$14:$X$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J20">
-    <cfRule type="cellIs" dxfId="118" priority="299" operator="equal">
+    <cfRule type="cellIs" dxfId="123" priority="309" operator="equal">
       <formula>MAX($J$14:$J$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V20">
-    <cfRule type="cellIs" dxfId="117" priority="300" operator="equal">
+    <cfRule type="cellIs" dxfId="122" priority="310" operator="equal">
       <formula>MAX($V$14:$V$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S20">
-    <cfRule type="cellIs" dxfId="116" priority="301" operator="equal">
+    <cfRule type="cellIs" dxfId="121" priority="311" operator="equal">
       <formula>MAX($S$14:$S$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N20">
-    <cfRule type="cellIs" dxfId="115" priority="302" operator="equal">
+    <cfRule type="cellIs" dxfId="120" priority="312" operator="equal">
       <formula>MAX($N$14:$N$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P20">
-    <cfRule type="cellIs" dxfId="114" priority="303" operator="equal">
+    <cfRule type="cellIs" dxfId="119" priority="313" operator="equal">
       <formula>MAX($P$14:$P$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E48:E64">
-    <cfRule type="top10" dxfId="113" priority="295" rank="2"/>
+    <cfRule type="top10" dxfId="118" priority="305" rank="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F79">
-    <cfRule type="top10" dxfId="112" priority="294" rank="2"/>
+    <cfRule type="top10" dxfId="117" priority="304" rank="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G48:G64">
-    <cfRule type="top10" dxfId="111" priority="293" rank="2"/>
+    <cfRule type="top10" dxfId="116" priority="303" rank="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H48:H64">
-    <cfRule type="top10" dxfId="110" priority="292" rank="2"/>
+    <cfRule type="top10" dxfId="115" priority="302" rank="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I48:I64">
-    <cfRule type="top10" dxfId="109" priority="291" rank="2"/>
+    <cfRule type="top10" dxfId="114" priority="301" rank="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="V24">
-    <cfRule type="cellIs" dxfId="108" priority="261" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="271" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V25">
-    <cfRule type="cellIs" dxfId="107" priority="260" operator="equal">
+    <cfRule type="cellIs" dxfId="112" priority="270" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G18:G32 G44:G45">
-    <cfRule type="cellIs" dxfId="106" priority="249" operator="equal">
+  <conditionalFormatting sqref="G18:G32 G45">
+    <cfRule type="cellIs" dxfId="111" priority="259" operator="equal">
       <formula>MAX($G$14:$G$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L45">
-    <cfRule type="cellIs" dxfId="105" priority="239" operator="equal">
+    <cfRule type="cellIs" dxfId="110" priority="249" operator="equal">
       <formula>MAX($L$14:$L$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T45">
-    <cfRule type="cellIs" dxfId="104" priority="240" operator="equal">
+    <cfRule type="cellIs" dxfId="109" priority="250" operator="equal">
       <formula>MAX($T$14:$T$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X45">
-    <cfRule type="cellIs" dxfId="103" priority="241" operator="equal">
+    <cfRule type="cellIs" dxfId="108" priority="251" operator="equal">
       <formula>MAX($X$14:$X$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J45">
-    <cfRule type="cellIs" dxfId="102" priority="242" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="252" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V45">
-    <cfRule type="cellIs" dxfId="101" priority="243" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="253" operator="equal">
       <formula>MAX($V$14:$V$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S45">
-    <cfRule type="cellIs" dxfId="100" priority="245" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="255" operator="equal">
       <formula>MAX($S$14:$S$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N45">
-    <cfRule type="cellIs" dxfId="99" priority="246" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="256" operator="equal">
       <formula>MAX($N$14:$N$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P45">
-    <cfRule type="cellIs" dxfId="98" priority="247" operator="equal">
+    <cfRule type="cellIs" dxfId="103" priority="257" operator="equal">
       <formula>MAX($P$14:$P$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G16:G17">
-    <cfRule type="cellIs" dxfId="92" priority="133" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="143" operator="equal">
+      <formula>MAX($G$14:$G$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D14">
+    <cfRule type="cellIs" dxfId="92" priority="97" operator="equal">
+      <formula>MAX($D$14:$D$42)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G14">
+    <cfRule type="cellIs" dxfId="91" priority="96" operator="equal">
+      <formula>MAX($G$14:$G$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L14">
+    <cfRule type="cellIs" dxfId="90" priority="88" operator="equal">
+      <formula>MAX($L$14:$L$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T14">
+    <cfRule type="cellIs" dxfId="89" priority="89" operator="equal">
+      <formula>MAX($T$14:$T$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X14">
+    <cfRule type="cellIs" dxfId="88" priority="90" operator="equal">
+      <formula>MAX($X$14:$X$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J14">
+    <cfRule type="cellIs" dxfId="87" priority="91" operator="equal">
+      <formula>MAX($J$14:$J$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V14">
+    <cfRule type="cellIs" dxfId="86" priority="92" operator="equal">
+      <formula>MAX($V$14:$V$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S14">
+    <cfRule type="cellIs" dxfId="85" priority="93" operator="equal">
+      <formula>MAX($S$14:$S$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N14">
+    <cfRule type="cellIs" dxfId="84" priority="94" operator="equal">
+      <formula>MAX($N$14:$N$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P14">
+    <cfRule type="cellIs" dxfId="83" priority="95" operator="equal">
+      <formula>MAX($P$14:$P$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15">
+    <cfRule type="cellIs" dxfId="82" priority="87" operator="equal">
+      <formula>MAX($D$14:$D$42)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15">
+    <cfRule type="cellIs" dxfId="81" priority="86" operator="equal">
+      <formula>MAX($G$14:$G$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L15">
+    <cfRule type="cellIs" dxfId="80" priority="84" operator="equal">
+      <formula>MAX($L$14:$L$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J15">
+    <cfRule type="cellIs" dxfId="79" priority="85" operator="equal">
+      <formula>MAX($J$14:$J$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T15">
+    <cfRule type="cellIs" dxfId="78" priority="80" operator="equal">
+      <formula>MAX($T$14:$T$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S15">
+    <cfRule type="cellIs" dxfId="77" priority="81" operator="equal">
+      <formula>MAX($S$14:$S$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N15">
+    <cfRule type="cellIs" dxfId="76" priority="82" operator="equal">
+      <formula>MAX($N$14:$N$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P15">
+    <cfRule type="cellIs" dxfId="75" priority="83" operator="equal">
+      <formula>MAX($P$14:$P$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X15">
+    <cfRule type="cellIs" dxfId="74" priority="78" operator="equal">
+      <formula>MAX($X$14:$X$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V15">
+    <cfRule type="cellIs" dxfId="73" priority="79" operator="equal">
+      <formula>MAX($V$14:$V$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V22">
+    <cfRule type="cellIs" dxfId="72" priority="76" operator="equal">
+      <formula>MAX($V$14:$V$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N22">
+    <cfRule type="cellIs" dxfId="71" priority="72" operator="equal">
+      <formula>MAX($N$14:$N$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P22">
+    <cfRule type="cellIs" dxfId="70" priority="73" operator="equal">
+      <formula>MAX($P$14:$P$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J22">
+    <cfRule type="cellIs" dxfId="69" priority="70" operator="equal">
+      <formula>MAX($J$14:$J$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L34:L35">
+    <cfRule type="cellIs" dxfId="68" priority="62" operator="equal">
+      <formula>MAX($L$14:$L$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T34:T35">
+    <cfRule type="cellIs" dxfId="67" priority="63" operator="equal">
+      <formula>MAX($T$14:$T$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X34:X35">
+    <cfRule type="cellIs" dxfId="66" priority="64" operator="equal">
+      <formula>MAX($X$14:$X$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J34:J35">
+    <cfRule type="cellIs" dxfId="65" priority="65" operator="equal">
+      <formula>MAX($J$14:$J$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V34:V35">
+    <cfRule type="cellIs" dxfId="64" priority="66" operator="equal">
+      <formula>MAX($V$14:$V$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S34:S35">
+    <cfRule type="cellIs" dxfId="63" priority="67" operator="equal">
+      <formula>MAX($S$14:$S$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N34:N35">
+    <cfRule type="cellIs" dxfId="62" priority="68" operator="equal">
+      <formula>MAX($N$14:$N$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P34:P35">
+    <cfRule type="cellIs" dxfId="61" priority="69" operator="equal">
+      <formula>MAX($P$14:$P$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D34:D35">
+    <cfRule type="cellIs" dxfId="60" priority="61" operator="equal">
+      <formula>MAX($D$14:$D$42)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G34:G35">
+    <cfRule type="cellIs" dxfId="59" priority="60" operator="equal">
+      <formula>MAX($G$14:$G$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L33">
+    <cfRule type="cellIs" dxfId="58" priority="52" operator="equal">
+      <formula>MAX($L$14:$L$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T33">
+    <cfRule type="cellIs" dxfId="57" priority="53" operator="equal">
+      <formula>MAX($T$14:$T$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X33">
+    <cfRule type="cellIs" dxfId="56" priority="54" operator="equal">
+      <formula>MAX($X$14:$X$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J33">
+    <cfRule type="cellIs" dxfId="55" priority="55" operator="equal">
+      <formula>MAX($J$14:$J$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V33">
+    <cfRule type="cellIs" dxfId="54" priority="56" operator="equal">
+      <formula>MAX($V$14:$V$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S33">
+    <cfRule type="cellIs" dxfId="53" priority="57" operator="equal">
+      <formula>MAX($S$14:$S$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N33">
+    <cfRule type="cellIs" dxfId="52" priority="58" operator="equal">
+      <formula>MAX($N$14:$N$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P33">
+    <cfRule type="cellIs" dxfId="51" priority="59" operator="equal">
+      <formula>MAX($P$14:$P$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D33">
+    <cfRule type="cellIs" dxfId="50" priority="51" operator="equal">
+      <formula>MAX($D$14:$D$42)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G33">
+    <cfRule type="cellIs" dxfId="49" priority="50" operator="equal">
+      <formula>MAX($G$14:$G$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L36:L39">
+    <cfRule type="cellIs" dxfId="48" priority="42" operator="equal">
+      <formula>MAX($L$14:$L$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T36:T39">
+    <cfRule type="cellIs" dxfId="47" priority="43" operator="equal">
+      <formula>MAX($T$14:$T$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X36:X39">
+    <cfRule type="cellIs" dxfId="46" priority="44" operator="equal">
+      <formula>MAX($X$14:$X$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J36:J39">
+    <cfRule type="cellIs" dxfId="45" priority="45" operator="equal">
+      <formula>MAX($J$14:$J$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V36:V39">
+    <cfRule type="cellIs" dxfId="44" priority="46" operator="equal">
+      <formula>MAX($V$14:$V$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S36:S39">
+    <cfRule type="cellIs" dxfId="43" priority="47" operator="equal">
+      <formula>MAX($S$14:$S$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N36:N39">
+    <cfRule type="cellIs" dxfId="42" priority="48" operator="equal">
+      <formula>MAX($N$14:$N$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P39 P36:P37">
+    <cfRule type="cellIs" dxfId="41" priority="49" operator="equal">
+      <formula>MAX($P$14:$P$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D36:D39">
+    <cfRule type="cellIs" dxfId="40" priority="41" operator="equal">
+      <formula>MAX($D$14:$D$42)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G36:G39">
+    <cfRule type="cellIs" dxfId="39" priority="40" operator="equal">
+      <formula>MAX($G$14:$G$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P38">
+    <cfRule type="cellIs" dxfId="38" priority="39" operator="equal">
+      <formula>MAX($P$14:$P$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L41:L42">
+    <cfRule type="cellIs" dxfId="37" priority="31" operator="equal">
+      <formula>MAX($L$14:$L$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T41:T42">
+    <cfRule type="cellIs" dxfId="36" priority="32" operator="equal">
+      <formula>MAX($T$14:$T$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X41:X42">
+    <cfRule type="cellIs" dxfId="35" priority="33" operator="equal">
+      <formula>MAX($X$14:$X$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J41:J42">
+    <cfRule type="cellIs" dxfId="34" priority="34" operator="equal">
+      <formula>MAX($J$14:$J$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V41:V42">
+    <cfRule type="cellIs" dxfId="33" priority="35" operator="equal">
+      <formula>MAX($V$14:$V$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S41:S42">
+    <cfRule type="cellIs" dxfId="32" priority="36" operator="equal">
+      <formula>MAX($S$14:$S$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N41:N42">
+    <cfRule type="cellIs" dxfId="31" priority="37" operator="equal">
+      <formula>MAX($N$14:$N$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P41:P42">
+    <cfRule type="cellIs" dxfId="30" priority="38" operator="equal">
+      <formula>MAX($P$14:$P$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L40">
+    <cfRule type="cellIs" dxfId="29" priority="23" operator="equal">
+      <formula>MAX($L$14:$L$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T40">
+    <cfRule type="cellIs" dxfId="28" priority="24" operator="equal">
+      <formula>MAX($T$14:$T$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X40">
+    <cfRule type="cellIs" dxfId="27" priority="25" operator="equal">
+      <formula>MAX($X$14:$X$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J40">
+    <cfRule type="cellIs" dxfId="26" priority="26" operator="equal">
+      <formula>MAX($J$14:$J$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V40">
+    <cfRule type="cellIs" dxfId="25" priority="27" operator="equal">
+      <formula>MAX($V$14:$V$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S40">
+    <cfRule type="cellIs" dxfId="24" priority="28" operator="equal">
+      <formula>MAX($S$14:$S$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N40">
+    <cfRule type="cellIs" dxfId="23" priority="29" operator="equal">
+      <formula>MAX($N$14:$N$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P40">
+    <cfRule type="cellIs" dxfId="22" priority="30" operator="equal">
+      <formula>MAX($P$14:$P$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D40:D42">
+    <cfRule type="cellIs" dxfId="21" priority="22" operator="equal">
+      <formula>MAX($D$14:$D$42)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G40:G42">
+    <cfRule type="cellIs" dxfId="20" priority="21" operator="equal">
+      <formula>MAX($G$14:$G$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T43">
+    <cfRule type="cellIs" dxfId="19" priority="17" operator="equal">
+      <formula>MAX($T$14:$T$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X43">
+    <cfRule type="cellIs" dxfId="18" priority="18" operator="equal">
+      <formula>MAX($X$14:$X$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V43">
+    <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
+      <formula>MAX($V$14:$V$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S43">
+    <cfRule type="cellIs" dxfId="16" priority="20" operator="equal">
+      <formula>MAX($S$14:$S$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G43">
+    <cfRule type="cellIs" dxfId="15" priority="16" operator="equal">
+      <formula>MAX($G$14:$G$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N43">
+    <cfRule type="cellIs" dxfId="14" priority="14" operator="equal">
+      <formula>MAX($N$14:$N$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P43">
+    <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
+      <formula>MAX($P$14:$P$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L43">
+    <cfRule type="cellIs" dxfId="12" priority="12" operator="equal">
+      <formula>MAX($L$14:$L$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J43">
+    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
+      <formula>MAX($J$14:$J$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D43">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+      <formula>MAX($D$14:$D$42)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G44">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
       <formula>MAX($G$14:$G$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D44">
-    <cfRule type="cellIs" dxfId="91" priority="104" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
       <formula>MAX($D$14:$D$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L44">
-    <cfRule type="cellIs" dxfId="90" priority="100" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
       <formula>MAX($L$14:$L$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J44">
-    <cfRule type="cellIs" dxfId="89" priority="101" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N44">
-    <cfRule type="cellIs" dxfId="88" priority="96" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
       <formula>MAX($N$14:$N$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P44">
-    <cfRule type="cellIs" dxfId="87" priority="97" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>MAX($P$14:$P$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T44">
-    <cfRule type="cellIs" dxfId="86" priority="92" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>MAX($T$14:$T$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S44">
-    <cfRule type="cellIs" dxfId="85" priority="93" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>MAX($S$14:$S$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X44">
-    <cfRule type="cellIs" dxfId="84" priority="88" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>MAX($X$14:$X$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V44">
-    <cfRule type="cellIs" dxfId="83" priority="89" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>MAX($V$14:$V$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D14">
-    <cfRule type="cellIs" dxfId="82" priority="87" operator="equal">
-      <formula>MAX($D$14:$D$42)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G14">
-    <cfRule type="cellIs" dxfId="81" priority="86" operator="equal">
-      <formula>MAX($G$14:$G$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L14">
-    <cfRule type="cellIs" dxfId="80" priority="78" operator="equal">
-      <formula>MAX($L$14:$L$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T14">
-    <cfRule type="cellIs" dxfId="79" priority="79" operator="equal">
-      <formula>MAX($T$14:$T$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X14">
-    <cfRule type="cellIs" dxfId="78" priority="80" operator="equal">
-      <formula>MAX($X$14:$X$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J14">
-    <cfRule type="cellIs" dxfId="77" priority="81" operator="equal">
-      <formula>MAX($J$14:$J$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V14">
-    <cfRule type="cellIs" dxfId="76" priority="82" operator="equal">
-      <formula>MAX($V$14:$V$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S14">
-    <cfRule type="cellIs" dxfId="75" priority="83" operator="equal">
-      <formula>MAX($S$14:$S$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N14">
-    <cfRule type="cellIs" dxfId="74" priority="84" operator="equal">
-      <formula>MAX($N$14:$N$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P14">
-    <cfRule type="cellIs" dxfId="73" priority="85" operator="equal">
-      <formula>MAX($P$14:$P$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D15">
-    <cfRule type="cellIs" dxfId="72" priority="77" operator="equal">
-      <formula>MAX($D$14:$D$42)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G15">
-    <cfRule type="cellIs" dxfId="71" priority="76" operator="equal">
-      <formula>MAX($G$14:$G$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L15">
-    <cfRule type="cellIs" dxfId="70" priority="74" operator="equal">
-      <formula>MAX($L$14:$L$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J15">
-    <cfRule type="cellIs" dxfId="69" priority="75" operator="equal">
-      <formula>MAX($J$14:$J$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T15">
-    <cfRule type="cellIs" dxfId="68" priority="70" operator="equal">
-      <formula>MAX($T$14:$T$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S15">
-    <cfRule type="cellIs" dxfId="67" priority="71" operator="equal">
-      <formula>MAX($S$14:$S$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N15">
-    <cfRule type="cellIs" dxfId="66" priority="72" operator="equal">
-      <formula>MAX($N$14:$N$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P15">
-    <cfRule type="cellIs" dxfId="65" priority="73" operator="equal">
-      <formula>MAX($P$14:$P$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X15">
-    <cfRule type="cellIs" dxfId="64" priority="68" operator="equal">
-      <formula>MAX($X$14:$X$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V15">
-    <cfRule type="cellIs" dxfId="63" priority="69" operator="equal">
-      <formula>MAX($V$14:$V$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V22">
-    <cfRule type="cellIs" dxfId="62" priority="66" operator="equal">
-      <formula>MAX($V$14:$V$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N22">
-    <cfRule type="cellIs" dxfId="61" priority="62" operator="equal">
-      <formula>MAX($N$14:$N$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P22">
-    <cfRule type="cellIs" dxfId="60" priority="63" operator="equal">
-      <formula>MAX($P$14:$P$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J22">
-    <cfRule type="cellIs" dxfId="59" priority="60" operator="equal">
-      <formula>MAX($J$14:$J$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L34:L35">
-    <cfRule type="cellIs" dxfId="58" priority="52" operator="equal">
-      <formula>MAX($L$14:$L$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T34:T35">
-    <cfRule type="cellIs" dxfId="57" priority="53" operator="equal">
-      <formula>MAX($T$14:$T$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X34:X35">
-    <cfRule type="cellIs" dxfId="56" priority="54" operator="equal">
-      <formula>MAX($X$14:$X$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J34:J35">
-    <cfRule type="cellIs" dxfId="55" priority="55" operator="equal">
-      <formula>MAX($J$14:$J$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V34:V35">
-    <cfRule type="cellIs" dxfId="54" priority="56" operator="equal">
-      <formula>MAX($V$14:$V$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S34:S35">
-    <cfRule type="cellIs" dxfId="53" priority="57" operator="equal">
-      <formula>MAX($S$14:$S$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N34:N35">
-    <cfRule type="cellIs" dxfId="52" priority="58" operator="equal">
-      <formula>MAX($N$14:$N$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P34:P35">
-    <cfRule type="cellIs" dxfId="51" priority="59" operator="equal">
-      <formula>MAX($P$14:$P$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D34:D35">
-    <cfRule type="cellIs" dxfId="50" priority="51" operator="equal">
-      <formula>MAX($D$14:$D$42)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G34:G35">
-    <cfRule type="cellIs" dxfId="49" priority="50" operator="equal">
-      <formula>MAX($G$14:$G$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L33">
-    <cfRule type="cellIs" dxfId="48" priority="42" operator="equal">
-      <formula>MAX($L$14:$L$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T33">
-    <cfRule type="cellIs" dxfId="47" priority="43" operator="equal">
-      <formula>MAX($T$14:$T$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X33">
-    <cfRule type="cellIs" dxfId="46" priority="44" operator="equal">
-      <formula>MAX($X$14:$X$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J33">
-    <cfRule type="cellIs" dxfId="45" priority="45" operator="equal">
-      <formula>MAX($J$14:$J$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V33">
-    <cfRule type="cellIs" dxfId="44" priority="46" operator="equal">
-      <formula>MAX($V$14:$V$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S33">
-    <cfRule type="cellIs" dxfId="43" priority="47" operator="equal">
-      <formula>MAX($S$14:$S$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N33">
-    <cfRule type="cellIs" dxfId="42" priority="48" operator="equal">
-      <formula>MAX($N$14:$N$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P33">
-    <cfRule type="cellIs" dxfId="41" priority="49" operator="equal">
-      <formula>MAX($P$14:$P$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D33">
-    <cfRule type="cellIs" dxfId="40" priority="41" operator="equal">
-      <formula>MAX($D$14:$D$42)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G33">
-    <cfRule type="cellIs" dxfId="39" priority="40" operator="equal">
-      <formula>MAX($G$14:$G$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L36:L39">
-    <cfRule type="cellIs" dxfId="38" priority="32" operator="equal">
-      <formula>MAX($L$14:$L$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T36:T39">
-    <cfRule type="cellIs" dxfId="37" priority="33" operator="equal">
-      <formula>MAX($T$14:$T$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X36:X39">
-    <cfRule type="cellIs" dxfId="36" priority="34" operator="equal">
-      <formula>MAX($X$14:$X$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J36:J39">
-    <cfRule type="cellIs" dxfId="35" priority="35" operator="equal">
-      <formula>MAX($J$14:$J$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V36:V39">
-    <cfRule type="cellIs" dxfId="34" priority="36" operator="equal">
-      <formula>MAX($V$14:$V$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S36:S39">
-    <cfRule type="cellIs" dxfId="33" priority="37" operator="equal">
-      <formula>MAX($S$14:$S$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N36:N39">
-    <cfRule type="cellIs" dxfId="32" priority="38" operator="equal">
-      <formula>MAX($N$14:$N$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P39 P36:P37">
-    <cfRule type="cellIs" dxfId="31" priority="39" operator="equal">
-      <formula>MAX($P$14:$P$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D36:D39">
-    <cfRule type="cellIs" dxfId="30" priority="31" operator="equal">
-      <formula>MAX($D$14:$D$42)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G36:G39">
-    <cfRule type="cellIs" dxfId="29" priority="30" operator="equal">
-      <formula>MAX($G$14:$G$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P38">
-    <cfRule type="cellIs" dxfId="28" priority="29" operator="equal">
-      <formula>MAX($P$14:$P$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L41:L42">
-    <cfRule type="cellIs" dxfId="27" priority="21" operator="equal">
-      <formula>MAX($L$14:$L$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T41:T42">
-    <cfRule type="cellIs" dxfId="26" priority="22" operator="equal">
-      <formula>MAX($T$14:$T$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X41:X42">
-    <cfRule type="cellIs" dxfId="25" priority="23" operator="equal">
-      <formula>MAX($X$14:$X$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J41:J42">
-    <cfRule type="cellIs" dxfId="24" priority="24" operator="equal">
-      <formula>MAX($J$14:$J$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V41:V42">
-    <cfRule type="cellIs" dxfId="23" priority="25" operator="equal">
-      <formula>MAX($V$14:$V$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S41:S42">
-    <cfRule type="cellIs" dxfId="22" priority="26" operator="equal">
-      <formula>MAX($S$14:$S$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N41:N42">
-    <cfRule type="cellIs" dxfId="21" priority="27" operator="equal">
-      <formula>MAX($N$14:$N$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P41:P42">
-    <cfRule type="cellIs" dxfId="20" priority="28" operator="equal">
-      <formula>MAX($P$14:$P$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L40">
-    <cfRule type="cellIs" dxfId="19" priority="13" operator="equal">
-      <formula>MAX($L$14:$L$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T40">
-    <cfRule type="cellIs" dxfId="18" priority="14" operator="equal">
-      <formula>MAX($T$14:$T$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X40">
-    <cfRule type="cellIs" dxfId="17" priority="15" operator="equal">
-      <formula>MAX($X$14:$X$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J40">
-    <cfRule type="cellIs" dxfId="16" priority="16" operator="equal">
-      <formula>MAX($J$14:$J$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V40">
-    <cfRule type="cellIs" dxfId="15" priority="17" operator="equal">
-      <formula>MAX($V$14:$V$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S40">
-    <cfRule type="cellIs" dxfId="14" priority="18" operator="equal">
-      <formula>MAX($S$14:$S$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N40">
-    <cfRule type="cellIs" dxfId="13" priority="19" operator="equal">
-      <formula>MAX($N$14:$N$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P40">
-    <cfRule type="cellIs" dxfId="12" priority="20" operator="equal">
-      <formula>MAX($P$14:$P$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D40:D42">
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
-      <formula>MAX($D$14:$D$42)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G40:G42">
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
-      <formula>MAX($G$14:$G$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T43">
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
-      <formula>MAX($T$14:$T$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X43">
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
-      <formula>MAX($X$14:$X$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V43">
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
-      <formula>MAX($V$14:$V$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S43">
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
-      <formula>MAX($S$14:$S$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G43">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
-      <formula>MAX($G$14:$G$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N43">
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
-      <formula>MAX($N$14:$N$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P43">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
-      <formula>MAX($P$14:$P$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L43">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
-      <formula>MAX($L$14:$L$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J43">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
-      <formula>MAX($J$14:$J$16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D43">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>MAX($D$14:$D$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19914,28 +20060,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E3C748FF7EC2ED4E8EAD43CD1EEC2D0E" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ea203103aa5aa41fa7dd49b43cb8a2de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xmlns:ns3="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49b0a91519af75797ffa607b75695ffb" ns2:_="" ns3:_="">
     <xsd:import namespace="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
@@ -20182,26 +20306,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5BCA511-7B91-4B72-B4F3-8175C2C806EF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
-    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F8AAD19-02EA-4280-B365-8810DF5CEEF3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3450C23-B9A2-45D4-8942-0C308DF3F8F2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20218,4 +20345,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F8AAD19-02EA-4280-B365-8810DF5CEEF3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5BCA511-7B91-4B72-B4F3-8175C2C806EF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/seat/06-junio2026.xlsx
+++ b/data/seat/06-junio2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoefe.sharepoint.com/sites/GOFEFEVALPARASO/Documentos compartidos/UNIDAD DE GESTION/Datos Operacionales/Energía/SEAT/2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoefe-my.sharepoint.com/personal/mvara_efevalparaiso_cl/Documents/Datos/Energía/SEAT/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="6_{022934C4-186F-4BE2-B034-0206DAC59087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DCC99C0-3FE5-4C63-9364-A866B40F38E2}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="6_{022934C4-186F-4BE2-B034-0206DAC59087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{900E5077-E362-4B08-9189-51288504B7BD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2124,6 +2124,60 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2154,39 +2208,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2199,31 +2220,10 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3874,40 +3874,40 @@
                 <c:formatCode>#,##0\ "Kwh"</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>51139</c:v>
+                  <c:v>51012</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>51214</c:v>
+                  <c:v>51087</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50512</c:v>
+                  <c:v>50385</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51566.51</c:v>
+                  <c:v>51439.51</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>50022</c:v>
+                  <c:v>49895</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>25890</c:v>
+                  <c:v>25763</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>21309</c:v>
+                  <c:v>21182</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>52192</c:v>
+                  <c:v>52065</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>51229</c:v>
+                  <c:v>51102</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>51129</c:v>
+                  <c:v>51002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>51024</c:v>
+                  <c:v>50897</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>50739</c:v>
+                  <c:v>50612</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4164,40 +4164,40 @@
                 <c:formatCode>#,##0\ "Kwh"</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>7611</c:v>
+                  <c:v>7738</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7656</c:v>
+                  <c:v>7783</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7666</c:v>
+                  <c:v>7793</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7633.49</c:v>
+                  <c:v>7760.49</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7606</c:v>
+                  <c:v>7733</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7270</c:v>
+                  <c:v>7397</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7241</c:v>
+                  <c:v>7368</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7672</c:v>
+                  <c:v>7799</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7783</c:v>
+                  <c:v>7910</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7671</c:v>
+                  <c:v>7798</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7536</c:v>
+                  <c:v>7663</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7511</c:v>
+                  <c:v>7638</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7457,293 +7457,293 @@
       <c r="A1" s="126">
         <v>1.1111111E+55</v>
       </c>
-      <c r="B1" s="218" t="s">
+      <c r="B1" s="236" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="127"/>
-      <c r="D1" s="220" t="s">
+      <c r="D1" s="238" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="221"/>
-      <c r="F1" s="221"/>
-      <c r="G1" s="221"/>
-      <c r="H1" s="221"/>
-      <c r="I1" s="221"/>
-      <c r="J1" s="221"/>
-      <c r="K1" s="221"/>
-      <c r="L1" s="221"/>
-      <c r="M1" s="221"/>
-      <c r="N1" s="221"/>
-      <c r="O1" s="222"/>
-      <c r="P1" s="223"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="239"/>
+      <c r="H1" s="239"/>
+      <c r="I1" s="239"/>
+      <c r="J1" s="239"/>
+      <c r="K1" s="239"/>
+      <c r="L1" s="239"/>
+      <c r="M1" s="239"/>
+      <c r="N1" s="239"/>
+      <c r="O1" s="240"/>
+      <c r="P1" s="241"/>
       <c r="Q1" s="128"/>
-      <c r="R1" s="228" t="s">
+      <c r="R1" s="218" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="229"/>
-      <c r="T1" s="229"/>
-      <c r="U1" s="229"/>
-      <c r="V1" s="229"/>
-      <c r="W1" s="229"/>
-      <c r="X1" s="229"/>
-      <c r="Y1" s="229"/>
-      <c r="Z1" s="229"/>
-      <c r="AA1" s="230"/>
+      <c r="S1" s="219"/>
+      <c r="T1" s="219"/>
+      <c r="U1" s="219"/>
+      <c r="V1" s="219"/>
+      <c r="W1" s="219"/>
+      <c r="X1" s="219"/>
+      <c r="Y1" s="219"/>
+      <c r="Z1" s="219"/>
+      <c r="AA1" s="220"/>
       <c r="AB1" s="129"/>
-      <c r="AC1" s="228" t="s">
+      <c r="AC1" s="218" t="s">
         <v>3</v>
       </c>
-      <c r="AD1" s="229"/>
-      <c r="AE1" s="229"/>
-      <c r="AF1" s="229"/>
-      <c r="AG1" s="229"/>
-      <c r="AH1" s="229"/>
-      <c r="AI1" s="229"/>
-      <c r="AJ1" s="229"/>
-      <c r="AK1" s="230"/>
+      <c r="AD1" s="219"/>
+      <c r="AE1" s="219"/>
+      <c r="AF1" s="219"/>
+      <c r="AG1" s="219"/>
+      <c r="AH1" s="219"/>
+      <c r="AI1" s="219"/>
+      <c r="AJ1" s="219"/>
+      <c r="AK1" s="220"/>
       <c r="AL1" s="130"/>
-      <c r="AM1" s="228" t="s">
+      <c r="AM1" s="218" t="s">
         <v>4</v>
       </c>
-      <c r="AN1" s="229"/>
-      <c r="AO1" s="229"/>
-      <c r="AP1" s="229"/>
-      <c r="AQ1" s="229"/>
-      <c r="AR1" s="229"/>
-      <c r="AS1" s="229"/>
-      <c r="AT1" s="229"/>
-      <c r="AU1" s="230"/>
+      <c r="AN1" s="219"/>
+      <c r="AO1" s="219"/>
+      <c r="AP1" s="219"/>
+      <c r="AQ1" s="219"/>
+      <c r="AR1" s="219"/>
+      <c r="AS1" s="219"/>
+      <c r="AT1" s="219"/>
+      <c r="AU1" s="220"/>
       <c r="AV1" s="130"/>
-      <c r="AW1" s="228" t="s">
+      <c r="AW1" s="218" t="s">
         <v>57</v>
       </c>
-      <c r="AX1" s="229"/>
-      <c r="AY1" s="229"/>
-      <c r="AZ1" s="229"/>
-      <c r="BA1" s="229"/>
-      <c r="BB1" s="229"/>
-      <c r="BC1" s="229"/>
-      <c r="BD1" s="229"/>
-      <c r="BE1" s="229"/>
-      <c r="BF1" s="229"/>
-      <c r="BG1" s="229"/>
-      <c r="BH1" s="230"/>
+      <c r="AX1" s="219"/>
+      <c r="AY1" s="219"/>
+      <c r="AZ1" s="219"/>
+      <c r="BA1" s="219"/>
+      <c r="BB1" s="219"/>
+      <c r="BC1" s="219"/>
+      <c r="BD1" s="219"/>
+      <c r="BE1" s="219"/>
+      <c r="BF1" s="219"/>
+      <c r="BG1" s="219"/>
+      <c r="BH1" s="220"/>
       <c r="BI1" s="130"/>
-      <c r="BJ1" s="228" t="s">
+      <c r="BJ1" s="218" t="s">
         <v>5</v>
       </c>
-      <c r="BK1" s="229"/>
-      <c r="BL1" s="229"/>
-      <c r="BM1" s="229"/>
-      <c r="BN1" s="229"/>
-      <c r="BO1" s="229"/>
-      <c r="BP1" s="229"/>
-      <c r="BQ1" s="229"/>
-      <c r="BR1" s="230"/>
+      <c r="BK1" s="219"/>
+      <c r="BL1" s="219"/>
+      <c r="BM1" s="219"/>
+      <c r="BN1" s="219"/>
+      <c r="BO1" s="219"/>
+      <c r="BP1" s="219"/>
+      <c r="BQ1" s="219"/>
+      <c r="BR1" s="220"/>
       <c r="BS1" s="131"/>
     </row>
     <row r="2" spans="1:71" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="218"/>
+      <c r="B2" s="236"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="224"/>
-      <c r="E2" s="225"/>
-      <c r="F2" s="225"/>
-      <c r="G2" s="225"/>
-      <c r="H2" s="225"/>
-      <c r="I2" s="225"/>
-      <c r="J2" s="225"/>
-      <c r="K2" s="225"/>
-      <c r="L2" s="225"/>
-      <c r="M2" s="225"/>
-      <c r="N2" s="225"/>
-      <c r="O2" s="226"/>
-      <c r="P2" s="227"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="243"/>
+      <c r="H2" s="243"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
+      <c r="M2" s="243"/>
+      <c r="N2" s="243"/>
+      <c r="O2" s="244"/>
+      <c r="P2" s="245"/>
       <c r="Q2" s="57"/>
-      <c r="R2" s="231"/>
-      <c r="S2" s="232"/>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232"/>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
-      <c r="AA2" s="233"/>
+      <c r="R2" s="221"/>
+      <c r="S2" s="222"/>
+      <c r="T2" s="222"/>
+      <c r="U2" s="222"/>
+      <c r="V2" s="222"/>
+      <c r="W2" s="222"/>
+      <c r="X2" s="222"/>
+      <c r="Y2" s="222"/>
+      <c r="Z2" s="222"/>
+      <c r="AA2" s="223"/>
       <c r="AB2" s="59"/>
-      <c r="AC2" s="231"/>
-      <c r="AD2" s="232"/>
-      <c r="AE2" s="232"/>
-      <c r="AF2" s="232"/>
-      <c r="AG2" s="232"/>
-      <c r="AH2" s="232"/>
-      <c r="AI2" s="232"/>
-      <c r="AJ2" s="232"/>
-      <c r="AK2" s="233"/>
+      <c r="AC2" s="221"/>
+      <c r="AD2" s="222"/>
+      <c r="AE2" s="222"/>
+      <c r="AF2" s="222"/>
+      <c r="AG2" s="222"/>
+      <c r="AH2" s="222"/>
+      <c r="AI2" s="222"/>
+      <c r="AJ2" s="222"/>
+      <c r="AK2" s="223"/>
       <c r="AL2" s="58"/>
-      <c r="AM2" s="231"/>
-      <c r="AN2" s="232"/>
-      <c r="AO2" s="232"/>
-      <c r="AP2" s="232"/>
-      <c r="AQ2" s="232"/>
-      <c r="AR2" s="232"/>
-      <c r="AS2" s="232"/>
-      <c r="AT2" s="232"/>
-      <c r="AU2" s="233"/>
+      <c r="AM2" s="221"/>
+      <c r="AN2" s="222"/>
+      <c r="AO2" s="222"/>
+      <c r="AP2" s="222"/>
+      <c r="AQ2" s="222"/>
+      <c r="AR2" s="222"/>
+      <c r="AS2" s="222"/>
+      <c r="AT2" s="222"/>
+      <c r="AU2" s="223"/>
       <c r="AV2" s="58"/>
-      <c r="AW2" s="231"/>
-      <c r="AX2" s="232"/>
-      <c r="AY2" s="232"/>
-      <c r="AZ2" s="232"/>
-      <c r="BA2" s="232"/>
-      <c r="BB2" s="232"/>
-      <c r="BC2" s="232"/>
-      <c r="BD2" s="232"/>
-      <c r="BE2" s="232"/>
-      <c r="BF2" s="232"/>
-      <c r="BG2" s="232"/>
-      <c r="BH2" s="233"/>
+      <c r="AW2" s="221"/>
+      <c r="AX2" s="222"/>
+      <c r="AY2" s="222"/>
+      <c r="AZ2" s="222"/>
+      <c r="BA2" s="222"/>
+      <c r="BB2" s="222"/>
+      <c r="BC2" s="222"/>
+      <c r="BD2" s="222"/>
+      <c r="BE2" s="222"/>
+      <c r="BF2" s="222"/>
+      <c r="BG2" s="222"/>
+      <c r="BH2" s="223"/>
       <c r="BI2" s="58"/>
-      <c r="BJ2" s="231"/>
-      <c r="BK2" s="232"/>
-      <c r="BL2" s="232"/>
-      <c r="BM2" s="232"/>
-      <c r="BN2" s="232"/>
-      <c r="BO2" s="232"/>
-      <c r="BP2" s="232"/>
-      <c r="BQ2" s="232"/>
-      <c r="BR2" s="233"/>
+      <c r="BJ2" s="221"/>
+      <c r="BK2" s="222"/>
+      <c r="BL2" s="222"/>
+      <c r="BM2" s="222"/>
+      <c r="BN2" s="222"/>
+      <c r="BO2" s="222"/>
+      <c r="BP2" s="222"/>
+      <c r="BQ2" s="222"/>
+      <c r="BR2" s="223"/>
       <c r="BS2" s="134"/>
     </row>
     <row r="3" spans="1:71" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="218"/>
+      <c r="B3" s="236"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="237" t="s">
+      <c r="D3" s="224" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="237" t="s">
+      <c r="E3" s="224" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="237" t="s">
+      <c r="F3" s="224" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="237" t="s">
+      <c r="G3" s="224" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="237" t="s">
+      <c r="H3" s="224" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="239" t="s">
+      <c r="I3" s="246" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="240"/>
-      <c r="K3" s="241"/>
-      <c r="L3" s="242"/>
-      <c r="M3" s="239" t="s">
+      <c r="J3" s="247"/>
+      <c r="K3" s="248"/>
+      <c r="L3" s="249"/>
+      <c r="M3" s="246" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="240"/>
-      <c r="O3" s="241"/>
-      <c r="P3" s="242"/>
+      <c r="N3" s="247"/>
+      <c r="O3" s="248"/>
+      <c r="P3" s="249"/>
       <c r="Q3" s="57"/>
-      <c r="R3" s="243" t="s">
+      <c r="R3" s="228" t="s">
         <v>13</v>
       </c>
-      <c r="S3" s="235"/>
-      <c r="T3" s="244"/>
-      <c r="U3" s="244"/>
-      <c r="V3" s="243" t="s">
+      <c r="S3" s="229"/>
+      <c r="T3" s="250"/>
+      <c r="U3" s="250"/>
+      <c r="V3" s="228" t="s">
         <v>14</v>
       </c>
-      <c r="W3" s="235"/>
-      <c r="X3" s="235"/>
-      <c r="Y3" s="235"/>
-      <c r="Z3" s="235"/>
-      <c r="AA3" s="236"/>
+      <c r="W3" s="229"/>
+      <c r="X3" s="229"/>
+      <c r="Y3" s="229"/>
+      <c r="Z3" s="229"/>
+      <c r="AA3" s="230"/>
       <c r="AB3" s="59"/>
-      <c r="AC3" s="245" t="s">
+      <c r="AC3" s="226" t="s">
         <v>15</v>
       </c>
-      <c r="AD3" s="247" t="s">
+      <c r="AD3" s="251" t="s">
         <v>9</v>
       </c>
-      <c r="AE3" s="243" t="s">
+      <c r="AE3" s="228" t="s">
         <v>13</v>
       </c>
-      <c r="AF3" s="235"/>
-      <c r="AG3" s="236"/>
-      <c r="AH3" s="243" t="s">
+      <c r="AF3" s="229"/>
+      <c r="AG3" s="230"/>
+      <c r="AH3" s="228" t="s">
         <v>14</v>
       </c>
-      <c r="AI3" s="235"/>
-      <c r="AJ3" s="235"/>
-      <c r="AK3" s="236"/>
+      <c r="AI3" s="229"/>
+      <c r="AJ3" s="229"/>
+      <c r="AK3" s="230"/>
       <c r="AL3" s="58"/>
-      <c r="AM3" s="248" t="s">
+      <c r="AM3" s="231" t="s">
         <v>15</v>
       </c>
-      <c r="AN3" s="245" t="s">
+      <c r="AN3" s="226" t="s">
         <v>9</v>
       </c>
-      <c r="AO3" s="234" t="s">
+      <c r="AO3" s="235" t="s">
         <v>13</v>
       </c>
-      <c r="AP3" s="235"/>
-      <c r="AQ3" s="236"/>
-      <c r="AR3" s="243" t="s">
+      <c r="AP3" s="229"/>
+      <c r="AQ3" s="230"/>
+      <c r="AR3" s="228" t="s">
         <v>14</v>
       </c>
-      <c r="AS3" s="235"/>
-      <c r="AT3" s="235"/>
-      <c r="AU3" s="236"/>
+      <c r="AS3" s="229"/>
+      <c r="AT3" s="229"/>
+      <c r="AU3" s="230"/>
       <c r="AV3" s="58"/>
-      <c r="AW3" s="245" t="s">
+      <c r="AW3" s="226" t="s">
         <v>15</v>
       </c>
-      <c r="AX3" s="245" t="s">
+      <c r="AX3" s="226" t="s">
         <v>9</v>
       </c>
-      <c r="AY3" s="234" t="s">
+      <c r="AY3" s="235" t="s">
         <v>13</v>
       </c>
-      <c r="AZ3" s="234"/>
-      <c r="BA3" s="235"/>
-      <c r="BB3" s="236"/>
-      <c r="BC3" s="243" t="s">
+      <c r="AZ3" s="235"/>
+      <c r="BA3" s="229"/>
+      <c r="BB3" s="230"/>
+      <c r="BC3" s="228" t="s">
         <v>14</v>
       </c>
-      <c r="BD3" s="234"/>
-      <c r="BE3" s="234"/>
-      <c r="BF3" s="235"/>
-      <c r="BG3" s="235"/>
-      <c r="BH3" s="236"/>
+      <c r="BD3" s="235"/>
+      <c r="BE3" s="235"/>
+      <c r="BF3" s="229"/>
+      <c r="BG3" s="229"/>
+      <c r="BH3" s="230"/>
       <c r="BI3" s="58"/>
-      <c r="BJ3" s="248" t="s">
+      <c r="BJ3" s="231" t="s">
         <v>16</v>
       </c>
-      <c r="BK3" s="245" t="s">
+      <c r="BK3" s="226" t="s">
         <v>17</v>
       </c>
-      <c r="BL3" s="249" t="s">
+      <c r="BL3" s="232" t="s">
         <v>18</v>
       </c>
-      <c r="BM3" s="250"/>
-      <c r="BN3" s="251"/>
-      <c r="BO3" s="234" t="s">
+      <c r="BM3" s="233"/>
+      <c r="BN3" s="234"/>
+      <c r="BO3" s="235" t="s">
         <v>14</v>
       </c>
-      <c r="BP3" s="235"/>
-      <c r="BQ3" s="235"/>
-      <c r="BR3" s="236"/>
+      <c r="BP3" s="229"/>
+      <c r="BQ3" s="229"/>
+      <c r="BR3" s="230"/>
       <c r="BS3" s="134"/>
     </row>
     <row r="4" spans="1:71" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="219"/>
+      <c r="B4" s="237"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="238"/>
-      <c r="E4" s="238"/>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
-      <c r="H4" s="238"/>
+      <c r="D4" s="225"/>
+      <c r="E4" s="225"/>
+      <c r="F4" s="225"/>
+      <c r="G4" s="225"/>
+      <c r="H4" s="225"/>
       <c r="I4" s="79" t="s">
         <v>3</v>
       </c>
@@ -7800,8 +7800,8 @@
         <v>24</v>
       </c>
       <c r="AB4" s="59"/>
-      <c r="AC4" s="246"/>
-      <c r="AD4" s="229"/>
+      <c r="AC4" s="227"/>
+      <c r="AD4" s="219"/>
       <c r="AE4" s="61" t="s">
         <v>27</v>
       </c>
@@ -7824,8 +7824,8 @@
         <v>24</v>
       </c>
       <c r="AL4" s="60"/>
-      <c r="AM4" s="228"/>
-      <c r="AN4" s="246"/>
+      <c r="AM4" s="218"/>
+      <c r="AN4" s="227"/>
       <c r="AO4" s="122" t="s">
         <v>27</v>
       </c>
@@ -7848,8 +7848,8 @@
         <v>24</v>
       </c>
       <c r="AV4" s="60"/>
-      <c r="AW4" s="246"/>
-      <c r="AX4" s="246"/>
+      <c r="AW4" s="227"/>
+      <c r="AX4" s="227"/>
       <c r="AY4" s="122" t="s">
         <v>27</v>
       </c>
@@ -7881,8 +7881,8 @@
         <v>24</v>
       </c>
       <c r="BI4" s="60"/>
-      <c r="BJ4" s="228"/>
-      <c r="BK4" s="246"/>
+      <c r="BJ4" s="218"/>
+      <c r="BK4" s="227"/>
       <c r="BL4" s="122" t="s">
         <v>32</v>
       </c>
@@ -8228,19 +8228,19 @@
       </c>
       <c r="E7" s="158">
         <f t="shared" si="1"/>
-        <v>0.87045106382978721</v>
+        <v>0.86828936170212767</v>
       </c>
       <c r="F7" s="86">
         <f t="shared" si="2"/>
-        <v>51139</v>
+        <v>51012</v>
       </c>
       <c r="G7" s="158">
         <f t="shared" si="3"/>
-        <v>0.12954893617021276</v>
+        <v>0.13171063829787233</v>
       </c>
       <c r="H7" s="145">
         <f t="shared" si="4"/>
-        <v>7611</v>
+        <v>7738</v>
       </c>
       <c r="I7" s="159">
         <f t="shared" si="5"/>
@@ -8381,11 +8381,11 @@
       </c>
       <c r="AW7" s="109">
         <f t="shared" ref="AW7:AW10" si="31">BA7/AZ7</f>
-        <v>0.63055555555555554</v>
+        <v>0.61748971193415636</v>
       </c>
       <c r="AX7" s="109">
         <f t="shared" ref="AX7:AX10" si="32">BB7/AZ7</f>
-        <v>0.36944444444444446</v>
+        <v>0.38251028806584364</v>
       </c>
       <c r="AY7" s="110">
         <f t="shared" ref="AY7" si="33">BA7+BB7</f>
@@ -8396,11 +8396,11 @@
       </c>
       <c r="BA7" s="186">
         <f t="shared" si="18"/>
-        <v>6129</v>
+        <v>6002</v>
       </c>
       <c r="BB7" s="202">
-        <f>3020+571</f>
-        <v>3591</v>
+        <f>3020+698</f>
+        <v>3718</v>
       </c>
       <c r="BC7" s="201">
         <v>4210</v>
@@ -8468,19 +8468,19 @@
       </c>
       <c r="E8" s="158">
         <f t="shared" si="1"/>
-        <v>0.86995073891625618</v>
+        <v>0.86779344317988794</v>
       </c>
       <c r="F8" s="86">
         <f t="shared" si="2"/>
-        <v>51214</v>
+        <v>51087</v>
       </c>
       <c r="G8" s="158">
         <f t="shared" si="3"/>
-        <v>0.13004926108374384</v>
+        <v>0.13220655682011212</v>
       </c>
       <c r="H8" s="145">
         <f t="shared" si="4"/>
-        <v>7656</v>
+        <v>7783</v>
       </c>
       <c r="I8" s="159">
         <f t="shared" si="5"/>
@@ -8622,11 +8622,11 @@
       </c>
       <c r="AW8" s="109">
         <f t="shared" si="31"/>
-        <v>0.63088685015290524</v>
+        <v>0.61794087665647301</v>
       </c>
       <c r="AX8" s="109">
         <f t="shared" si="32"/>
-        <v>0.36911314984709481</v>
+        <v>0.38205912334352704</v>
       </c>
       <c r="AY8" s="110">
         <f>BA8+BB8</f>
@@ -8637,11 +8637,11 @@
       </c>
       <c r="BA8" s="119">
         <f t="shared" ref="BA8:BA39" si="42">AZ8-BB8</f>
-        <v>6189</v>
+        <v>6062</v>
       </c>
       <c r="BB8" s="112">
-        <f>3050+571</f>
-        <v>3621</v>
+        <f>3050+698</f>
+        <v>3748</v>
       </c>
       <c r="BC8" s="111">
         <v>4225</v>
@@ -8711,19 +8711,19 @@
       </c>
       <c r="E9" s="158">
         <f t="shared" si="1"/>
-        <v>0.86823197772353811</v>
+        <v>0.86604902196706657</v>
       </c>
       <c r="F9" s="86">
         <f t="shared" si="2"/>
-        <v>50512</v>
+        <v>50385</v>
       </c>
       <c r="G9" s="158">
         <f t="shared" si="3"/>
-        <v>0.13176802227646189</v>
+        <v>0.1339509780329334</v>
       </c>
       <c r="H9" s="145">
         <f t="shared" si="4"/>
-        <v>7666</v>
+        <v>7793</v>
       </c>
       <c r="I9" s="159">
         <f t="shared" si="5"/>
@@ -8865,11 +8865,11 @@
       </c>
       <c r="AW9" s="109">
         <f t="shared" si="31"/>
-        <v>0.63298310671611047</v>
+        <v>0.61990111248454882</v>
       </c>
       <c r="AX9" s="109">
         <f t="shared" si="32"/>
-        <v>0.36701689328388959</v>
+        <v>0.38009888751545118</v>
       </c>
       <c r="AY9" s="110">
         <f t="shared" ref="AY9:AY39" si="45">BA9+BB9</f>
@@ -8880,11 +8880,11 @@
       </c>
       <c r="BA9" s="119">
         <f t="shared" si="42"/>
-        <v>6145</v>
+        <v>6018</v>
       </c>
       <c r="BB9" s="112">
-        <f>2992+571</f>
-        <v>3563</v>
+        <f>2992+698</f>
+        <v>3690</v>
       </c>
       <c r="BC9" s="111">
         <v>4794</v>
@@ -8951,19 +8951,19 @@
       </c>
       <c r="E10" s="158">
         <f t="shared" si="1"/>
-        <v>0.87105591216216216</v>
+        <v>0.86891064189189193</v>
       </c>
       <c r="F10" s="86">
         <f t="shared" si="2"/>
-        <v>51566.51</v>
+        <v>51439.51</v>
       </c>
       <c r="G10" s="158">
         <f t="shared" si="3"/>
-        <v>0.12894408783783784</v>
+        <v>0.13108935810810809</v>
       </c>
       <c r="H10" s="145">
         <f t="shared" si="4"/>
-        <v>7633.49</v>
+        <v>7760.49</v>
       </c>
       <c r="I10" s="159">
         <f t="shared" si="5"/>
@@ -9105,11 +9105,11 @@
       </c>
       <c r="AW10" s="109">
         <f t="shared" si="31"/>
-        <v>0.63773661921526603</v>
+        <v>0.62477677432522072</v>
       </c>
       <c r="AX10" s="109">
         <f t="shared" si="32"/>
-        <v>0.36226338078473391</v>
+        <v>0.37522322567477934</v>
       </c>
       <c r="AY10" s="110">
         <f t="shared" si="45"/>
@@ -9120,11 +9120,11 @@
       </c>
       <c r="BA10" s="119">
         <f t="shared" si="42"/>
-        <v>6249.5</v>
+        <v>6122.5</v>
       </c>
       <c r="BB10" s="112">
-        <f>2979+571</f>
-        <v>3550</v>
+        <f>2979+698</f>
+        <v>3677</v>
       </c>
       <c r="BC10" s="111">
         <v>3871.16</v>
@@ -9194,19 +9194,19 @@
       </c>
       <c r="E11" s="158">
         <f t="shared" si="1"/>
-        <v>0.86801554799750125</v>
+        <v>0.86581175817311029</v>
       </c>
       <c r="F11" s="86">
         <f t="shared" si="2"/>
-        <v>50022</v>
+        <v>49895</v>
       </c>
       <c r="G11" s="158">
         <f t="shared" si="3"/>
-        <v>0.13198445200249878</v>
+        <v>0.13418824182688971</v>
       </c>
       <c r="H11" s="145">
         <f t="shared" si="4"/>
-        <v>7606</v>
+        <v>7733</v>
       </c>
       <c r="I11" s="159">
         <f t="shared" si="5"/>
@@ -9348,11 +9348,11 @@
       </c>
       <c r="AW11" s="109">
         <f t="shared" ref="AW11:AW36" si="50">BA11/AZ11</f>
-        <v>0.63236836584854206</v>
+        <v>0.61904761904761907</v>
       </c>
       <c r="AX11" s="109">
         <f t="shared" ref="AX11:AX36" si="51">BB11/AZ11</f>
-        <v>0.36763163415145794</v>
+        <v>0.38095238095238093</v>
       </c>
       <c r="AY11" s="110">
         <f t="shared" si="45"/>
@@ -9363,11 +9363,11 @@
       </c>
       <c r="BA11" s="119">
         <f t="shared" si="42"/>
-        <v>6029</v>
+        <v>5902</v>
       </c>
       <c r="BB11" s="112">
-        <f>2934+571</f>
-        <v>3505</v>
+        <f>2934+698</f>
+        <v>3632</v>
       </c>
       <c r="BC11" s="111">
         <v>4046</v>
@@ -9434,19 +9434,19 @@
       </c>
       <c r="E12" s="158">
         <f t="shared" si="1"/>
-        <v>0.78075995174909529</v>
+        <v>0.77693003618817857</v>
       </c>
       <c r="F12" s="86">
         <f t="shared" si="2"/>
-        <v>25890</v>
+        <v>25763</v>
       </c>
       <c r="G12" s="158">
         <f t="shared" si="3"/>
-        <v>0.21924004825090471</v>
+        <v>0.22306996381182148</v>
       </c>
       <c r="H12" s="145">
         <f t="shared" si="4"/>
-        <v>7270</v>
+        <v>7397</v>
       </c>
       <c r="I12" s="159">
         <f t="shared" si="5"/>
@@ -9588,11 +9588,11 @@
       </c>
       <c r="AW12" s="109">
         <f t="shared" si="50"/>
-        <v>0.30273156705689053</v>
+        <v>0.27664818237831179</v>
       </c>
       <c r="AX12" s="109">
         <f t="shared" si="51"/>
-        <v>0.69726843294310947</v>
+        <v>0.72335181762168821</v>
       </c>
       <c r="AY12" s="110">
         <f t="shared" si="45"/>
@@ -9603,11 +9603,11 @@
       </c>
       <c r="BA12" s="119">
         <f t="shared" si="42"/>
-        <v>1474</v>
+        <v>1347</v>
       </c>
       <c r="BB12" s="112">
-        <f>2824+571</f>
-        <v>3395</v>
+        <f>2824+698</f>
+        <v>3522</v>
       </c>
       <c r="BC12" s="111">
         <v>1741</v>
@@ -9674,19 +9674,19 @@
       </c>
       <c r="E13" s="158">
         <f t="shared" si="1"/>
-        <v>0.74637478108581434</v>
+        <v>0.74192644483362524</v>
       </c>
       <c r="F13" s="86">
         <f t="shared" si="2"/>
-        <v>21309</v>
+        <v>21182</v>
       </c>
       <c r="G13" s="158">
         <f t="shared" si="3"/>
-        <v>0.25362521891418566</v>
+        <v>0.25807355516637476</v>
       </c>
       <c r="H13" s="145">
         <f t="shared" si="4"/>
-        <v>7241</v>
+        <v>7368</v>
       </c>
       <c r="I13" s="159">
         <f t="shared" si="5"/>
@@ -9828,11 +9828,11 @@
       </c>
       <c r="AW13" s="168">
         <f t="shared" si="50"/>
-        <v>0.25468409586056645</v>
+        <v>0.22701525054466232</v>
       </c>
       <c r="AX13" s="168">
         <f t="shared" si="51"/>
-        <v>0.7453159041394336</v>
+        <v>0.77298474945533768</v>
       </c>
       <c r="AY13" s="110">
         <f t="shared" si="45"/>
@@ -9843,11 +9843,11 @@
       </c>
       <c r="BA13" s="119">
         <f t="shared" si="42"/>
-        <v>1169</v>
+        <v>1042</v>
       </c>
       <c r="BB13" s="112">
-        <f>2850+571</f>
-        <v>3421</v>
+        <f>2850+698</f>
+        <v>3548</v>
       </c>
       <c r="BC13" s="111">
         <v>1690</v>
@@ -9914,19 +9914,19 @@
       </c>
       <c r="E14" s="158">
         <f t="shared" si="1"/>
-        <v>0.87184284377923293</v>
+        <v>0.8697213684351196</v>
       </c>
       <c r="F14" s="86">
         <f t="shared" si="2"/>
-        <v>52192</v>
+        <v>52065</v>
       </c>
       <c r="G14" s="158">
         <f t="shared" si="3"/>
-        <v>0.12815715622076707</v>
+        <v>0.1302786315648804</v>
       </c>
       <c r="H14" s="145">
         <f t="shared" si="4"/>
-        <v>7672</v>
+        <v>7799</v>
       </c>
       <c r="I14" s="159">
         <f t="shared" si="5"/>
@@ -10068,11 +10068,11 @@
       </c>
       <c r="AW14" s="109">
         <f t="shared" si="50"/>
-        <v>0.6488893336001601</v>
+        <v>0.63618170902541527</v>
       </c>
       <c r="AX14" s="109">
         <f t="shared" si="51"/>
-        <v>0.3511106663998399</v>
+        <v>0.36381829097458473</v>
       </c>
       <c r="AY14" s="110">
         <f t="shared" si="45"/>
@@ -10083,11 +10083,11 @@
       </c>
       <c r="BA14" s="119">
         <f t="shared" si="42"/>
-        <v>6485</v>
+        <v>6358</v>
       </c>
       <c r="BB14" s="112">
-        <f>2938+571</f>
-        <v>3509</v>
+        <f>2938+698</f>
+        <v>3636</v>
       </c>
       <c r="BC14" s="111">
         <v>4682</v>
@@ -10154,19 +10154,19 @@
       </c>
       <c r="E15" s="158">
         <f t="shared" si="1"/>
-        <v>0.86811157052802823</v>
+        <v>0.8659594658713482</v>
       </c>
       <c r="F15" s="86">
         <f t="shared" si="2"/>
-        <v>51229</v>
+        <v>51102</v>
       </c>
       <c r="G15" s="158">
         <f t="shared" si="3"/>
-        <v>0.1318884294719718</v>
+        <v>0.1340405341286518</v>
       </c>
       <c r="H15" s="145">
         <f t="shared" si="4"/>
-        <v>7783</v>
+        <v>7910</v>
       </c>
       <c r="I15" s="159">
         <f t="shared" si="5"/>
@@ -10308,11 +10308,11 @@
       </c>
       <c r="AW15" s="168">
         <f t="shared" si="50"/>
-        <v>0.6326614141000716</v>
+        <v>0.61966642791363957</v>
       </c>
       <c r="AX15" s="168">
         <f t="shared" si="51"/>
-        <v>0.36733858589992835</v>
+        <v>0.38033357208636037</v>
       </c>
       <c r="AY15" s="110">
         <f t="shared" si="45"/>
@@ -10323,11 +10323,11 @@
       </c>
       <c r="BA15" s="119">
         <f t="shared" si="42"/>
-        <v>6183</v>
+        <v>6056</v>
       </c>
       <c r="BB15" s="112">
-        <f>3019+571</f>
-        <v>3590</v>
+        <f>3019+698</f>
+        <v>3717</v>
       </c>
       <c r="BC15" s="111">
         <v>4069</v>
@@ -10394,19 +10394,19 @@
       </c>
       <c r="E16" s="158">
         <f t="shared" si="1"/>
-        <v>0.86954081632653057</v>
+        <v>0.86738095238095236</v>
       </c>
       <c r="F16" s="86">
         <f t="shared" si="2"/>
-        <v>51129</v>
+        <v>51002</v>
       </c>
       <c r="G16" s="158">
         <f t="shared" si="3"/>
-        <v>0.1304591836734694</v>
+        <v>0.13261904761904761</v>
       </c>
       <c r="H16" s="145">
         <f t="shared" si="4"/>
-        <v>7671</v>
+        <v>7798</v>
       </c>
       <c r="I16" s="159">
         <f t="shared" si="5"/>
@@ -10548,11 +10548,11 @@
       </c>
       <c r="AW16" s="109">
         <f t="shared" si="50"/>
-        <v>0.62492172824045089</v>
+        <v>0.61166771029012734</v>
       </c>
       <c r="AX16" s="109">
         <f t="shared" si="51"/>
-        <v>0.37507827175954916</v>
+        <v>0.38833228970987266</v>
       </c>
       <c r="AY16" s="110">
         <f t="shared" si="45"/>
@@ -10563,11 +10563,11 @@
       </c>
       <c r="BA16" s="119">
         <f t="shared" si="42"/>
-        <v>5988</v>
+        <v>5861</v>
       </c>
       <c r="BB16" s="112">
-        <f>3023+571</f>
-        <v>3594</v>
+        <f>3023+698</f>
+        <v>3721</v>
       </c>
       <c r="BC16" s="111">
         <v>4411</v>
@@ -10634,19 +10634,19 @@
       </c>
       <c r="E17" s="158">
         <f t="shared" si="1"/>
-        <v>0.87131147540983611</v>
+        <v>0.86914275956284148</v>
       </c>
       <c r="F17" s="86">
         <f t="shared" si="2"/>
-        <v>51024</v>
+        <v>50897</v>
       </c>
       <c r="G17" s="158">
         <f t="shared" si="3"/>
-        <v>0.12868852459016394</v>
+        <v>0.13085724043715846</v>
       </c>
       <c r="H17" s="145">
         <f t="shared" si="4"/>
-        <v>7536</v>
+        <v>7663</v>
       </c>
       <c r="I17" s="159">
         <f t="shared" si="5"/>
@@ -10788,11 +10788,11 @@
       </c>
       <c r="AW17" s="109">
         <f t="shared" si="50"/>
-        <v>0.63193364437532396</v>
+        <v>0.61876620010368066</v>
       </c>
       <c r="AX17" s="109">
         <f t="shared" si="51"/>
-        <v>0.36806635562467599</v>
+        <v>0.38123379989631934</v>
       </c>
       <c r="AY17" s="110">
         <f t="shared" si="45"/>
@@ -10803,11 +10803,11 @@
       </c>
       <c r="BA17" s="119">
         <f t="shared" si="42"/>
-        <v>6095</v>
+        <v>5968</v>
       </c>
       <c r="BB17" s="112">
-        <f>2979+571</f>
-        <v>3550</v>
+        <f>2979+698</f>
+        <v>3677</v>
       </c>
       <c r="BC17" s="111">
         <v>3917</v>
@@ -10874,19 +10874,19 @@
       </c>
       <c r="E18" s="158">
         <f t="shared" si="1"/>
-        <v>0.87105579399141631</v>
+        <v>0.86887553648068672</v>
       </c>
       <c r="F18" s="86">
         <f t="shared" si="2"/>
-        <v>50739</v>
+        <v>50612</v>
       </c>
       <c r="G18" s="158">
         <f t="shared" si="3"/>
-        <v>0.12894420600858369</v>
+        <v>0.13112446351931331</v>
       </c>
       <c r="H18" s="145">
         <f t="shared" si="4"/>
-        <v>7511</v>
+        <v>7638</v>
       </c>
       <c r="I18" s="159">
         <f t="shared" si="5"/>
@@ -11028,11 +11028,11 @@
       </c>
       <c r="AW18" s="109">
         <f t="shared" si="50"/>
-        <v>0.63340314136125653</v>
+        <v>0.62010471204188478</v>
       </c>
       <c r="AX18" s="109">
         <f t="shared" si="51"/>
-        <v>0.36659685863874347</v>
+        <v>0.37989528795811517</v>
       </c>
       <c r="AY18" s="110">
         <f t="shared" si="45"/>
@@ -11043,11 +11043,11 @@
       </c>
       <c r="BA18" s="119">
         <f t="shared" si="42"/>
-        <v>6049</v>
+        <v>5922</v>
       </c>
       <c r="BB18" s="112">
-        <f>2930+571</f>
-        <v>3501</v>
+        <f>2930+698</f>
+        <v>3628</v>
       </c>
       <c r="BC18" s="111">
         <v>4020</v>
@@ -11114,19 +11114,19 @@
       </c>
       <c r="E19" s="158">
         <f t="shared" si="1"/>
-        <v>0.77808679706601469</v>
+        <v>0.77420537897310515</v>
       </c>
       <c r="F19" s="86">
         <f t="shared" si="2"/>
-        <v>25459</v>
+        <v>25332</v>
       </c>
       <c r="G19" s="158">
         <f t="shared" si="3"/>
-        <v>0.22191320293398534</v>
+        <v>0.22579462102689488</v>
       </c>
       <c r="H19" s="145">
         <f t="shared" si="4"/>
-        <v>7261</v>
+        <v>7388</v>
       </c>
       <c r="I19" s="159">
         <f t="shared" si="5"/>
@@ -11268,11 +11268,11 @@
       </c>
       <c r="AW19" s="109">
         <f t="shared" ref="AW19" si="58">BA19/AZ19</f>
-        <v>0.28399999999999997</v>
+        <v>0.25726315789473686</v>
       </c>
       <c r="AX19" s="109">
         <f t="shared" ref="AX19" si="59">BB19/AZ19</f>
-        <v>0.71599999999999997</v>
+        <v>0.74273684210526314</v>
       </c>
       <c r="AY19" s="110">
         <f t="shared" si="45"/>
@@ -11283,11 +11283,11 @@
       </c>
       <c r="BA19" s="119">
         <f t="shared" si="42"/>
-        <v>1349</v>
+        <v>1222</v>
       </c>
       <c r="BB19" s="112">
-        <f>2830+571</f>
-        <v>3401</v>
+        <f>2830+698</f>
+        <v>3528</v>
       </c>
       <c r="BC19" s="180">
         <v>1720</v>
@@ -11354,19 +11354,19 @@
       </c>
       <c r="E20" s="158">
         <f t="shared" si="1"/>
-        <v>0.7663176265270506</v>
+        <v>0.74195462478184993</v>
       </c>
       <c r="F20" s="86">
         <f t="shared" si="2"/>
-        <v>21955</v>
+        <v>21257</v>
       </c>
       <c r="G20" s="158">
         <f t="shared" si="3"/>
-        <v>0.2336823734729494</v>
+        <v>0.25804537521815007</v>
       </c>
       <c r="H20" s="145">
         <f t="shared" si="4"/>
-        <v>6695</v>
+        <v>7393</v>
       </c>
       <c r="I20" s="159">
         <f t="shared" si="5"/>
@@ -11508,11 +11508,11 @@
       </c>
       <c r="AW20" s="109">
         <f t="shared" si="50"/>
-        <v>0.38419913419913421</v>
+        <v>0.23311688311688311</v>
       </c>
       <c r="AX20" s="109">
         <f t="shared" si="51"/>
-        <v>0.61580086580086579</v>
+        <v>0.76688311688311683</v>
       </c>
       <c r="AY20" s="110">
         <f t="shared" si="45"/>
@@ -11523,10 +11523,11 @@
       </c>
       <c r="BA20" s="119">
         <f t="shared" si="42"/>
-        <v>1775</v>
+        <v>1077</v>
       </c>
       <c r="BB20" s="112">
-        <v>2845</v>
+        <f>2845+698</f>
+        <v>3543</v>
       </c>
       <c r="BC20" s="111">
         <v>1670</v>
@@ -11594,19 +11595,19 @@
       </c>
       <c r="E21" s="158">
         <f t="shared" si="1"/>
-        <v>0.86923879742786925</v>
+        <v>0.8671009662323671</v>
       </c>
       <c r="F21" s="86">
         <f t="shared" si="2"/>
-        <v>51638</v>
+        <v>51511</v>
       </c>
       <c r="G21" s="158">
         <f t="shared" si="3"/>
-        <v>0.13076120257213075</v>
+        <v>0.1328990337676329</v>
       </c>
       <c r="H21" s="145">
         <f t="shared" si="4"/>
-        <v>7768</v>
+        <v>7895</v>
       </c>
       <c r="I21" s="159">
         <f t="shared" si="5"/>
@@ -11748,11 +11749,11 @@
       </c>
       <c r="AW21" s="109">
         <f t="shared" si="50"/>
-        <v>0.62820117247763041</v>
+        <v>0.61513936027974903</v>
       </c>
       <c r="AX21" s="109">
         <f t="shared" si="51"/>
-        <v>0.37179882752236965</v>
+        <v>0.38486063972025097</v>
       </c>
       <c r="AY21" s="110">
         <f t="shared" si="45"/>
@@ -11763,11 +11764,11 @@
       </c>
       <c r="BA21" s="119">
         <f t="shared" si="42"/>
-        <v>6108</v>
+        <v>5981</v>
       </c>
       <c r="BB21" s="112">
-        <f>3044+571</f>
-        <v>3615</v>
+        <f>3044+698</f>
+        <v>3742</v>
       </c>
       <c r="BC21" s="111">
         <v>4423</v>
@@ -11835,19 +11836,19 @@
       </c>
       <c r="E22" s="158">
         <f t="shared" si="1"/>
-        <v>0.86853731745978213</v>
+        <v>0.86639573707463491</v>
       </c>
       <c r="F22" s="86">
         <f t="shared" si="2"/>
-        <v>51506</v>
+        <v>51379</v>
       </c>
       <c r="G22" s="158">
         <f t="shared" si="3"/>
-        <v>0.13146268254021787</v>
+        <v>0.13360426292536509</v>
       </c>
       <c r="H22" s="145">
         <f t="shared" si="4"/>
-        <v>7796</v>
+        <v>7923</v>
       </c>
       <c r="I22" s="159">
         <f t="shared" si="5"/>
@@ -11989,11 +11990,11 @@
       </c>
       <c r="AW22" s="109">
         <f t="shared" si="50"/>
-        <v>0.62863006670087229</v>
+        <v>0.61559774243201637</v>
       </c>
       <c r="AX22" s="109">
         <f t="shared" si="51"/>
-        <v>0.37136993329912776</v>
+        <v>0.38440225756798357</v>
       </c>
       <c r="AY22" s="110">
         <f t="shared" si="45"/>
@@ -12004,11 +12005,11 @@
       </c>
       <c r="BA22" s="119">
         <f t="shared" si="42"/>
-        <v>6126</v>
+        <v>5999</v>
       </c>
       <c r="BB22" s="112">
-        <f>3048+571</f>
-        <v>3619</v>
+        <f>3048+698</f>
+        <v>3746</v>
       </c>
       <c r="BC22" s="111">
         <v>4152</v>
@@ -12076,19 +12077,19 @@
       </c>
       <c r="E23" s="158">
         <f t="shared" si="1"/>
-        <v>0.86721485456471958</v>
+        <v>0.86504443381071194</v>
       </c>
       <c r="F23" s="86">
         <f t="shared" si="2"/>
-        <v>50744.21</v>
+        <v>50617.21</v>
       </c>
       <c r="G23" s="158">
         <f t="shared" si="3"/>
-        <v>0.13278514543528044</v>
+        <v>0.13495556618928803</v>
       </c>
       <c r="H23" s="145">
         <f t="shared" si="4"/>
-        <v>7769.79</v>
+        <v>7896.79</v>
       </c>
       <c r="I23" s="159">
         <f t="shared" si="5"/>
@@ -12230,11 +12231,11 @@
       </c>
       <c r="AW23" s="109">
         <f t="shared" si="50"/>
-        <v>0.62656619018023618</v>
+        <v>0.61341102133830538</v>
       </c>
       <c r="AX23" s="109">
         <f t="shared" si="51"/>
-        <v>0.37343380981976382</v>
+        <v>0.38658897866169467</v>
       </c>
       <c r="AY23" s="110">
         <f t="shared" si="45"/>
@@ -12245,11 +12246,11 @@
       </c>
       <c r="BA23" s="119">
         <f t="shared" si="42"/>
-        <v>6048.87</v>
+        <v>5921.87</v>
       </c>
       <c r="BB23" s="112">
-        <f>3034.13+571</f>
-        <v>3605.13</v>
+        <f>3034.13+698</f>
+        <v>3732.13</v>
       </c>
       <c r="BC23" s="111">
         <v>3737.28</v>
@@ -12317,19 +12318,19 @@
       </c>
       <c r="E24" s="158">
         <f t="shared" si="1"/>
-        <v>0.86573889218526401</v>
+        <v>0.86352256465742905</v>
       </c>
       <c r="F24" s="86">
         <f t="shared" si="2"/>
-        <v>49608.57</v>
+        <v>49481.57</v>
       </c>
       <c r="G24" s="158">
         <f t="shared" si="3"/>
-        <v>0.13426110781473596</v>
+        <v>0.13647743534257095</v>
       </c>
       <c r="H24" s="145">
         <f t="shared" si="4"/>
-        <v>7693.43</v>
+        <v>7820.43</v>
       </c>
       <c r="I24" s="159">
         <f t="shared" si="5"/>
@@ -12471,11 +12472,11 @@
       </c>
       <c r="AW24" s="109">
         <f t="shared" si="50"/>
-        <v>0.61607089312486618</v>
+        <v>0.60247055043906617</v>
       </c>
       <c r="AX24" s="109">
         <f t="shared" si="51"/>
-        <v>0.38392910687513387</v>
+        <v>0.39752944956093383</v>
       </c>
       <c r="AY24" s="110">
         <f t="shared" si="45"/>
@@ -12486,11 +12487,11 @@
       </c>
       <c r="BA24" s="119">
         <f t="shared" si="42"/>
-        <v>5752.87</v>
+        <v>5625.87</v>
       </c>
       <c r="BB24" s="112">
-        <f>3014.13+571</f>
-        <v>3585.13</v>
+        <f>3014.13+698</f>
+        <v>3712.13</v>
       </c>
       <c r="BC24" s="111">
         <v>4001.6</v>
@@ -12558,19 +12559,19 @@
       </c>
       <c r="E25" s="158">
         <f t="shared" si="1"/>
-        <v>0.86989370571071278</v>
+        <v>0.86768792552452412</v>
       </c>
       <c r="F25" s="86">
         <f t="shared" si="2"/>
-        <v>50085</v>
+        <v>49958</v>
       </c>
       <c r="G25" s="158">
         <f t="shared" si="3"/>
-        <v>0.13010629428928722</v>
+        <v>0.13231207447547588</v>
       </c>
       <c r="H25" s="145">
         <f t="shared" si="4"/>
-        <v>7491</v>
+        <v>7618</v>
       </c>
       <c r="I25" s="159">
         <f t="shared" si="5"/>
@@ -12712,11 +12713,11 @@
       </c>
       <c r="AW25" s="168">
         <f t="shared" si="50"/>
-        <v>0.61728395061728392</v>
+        <v>0.60388308536456681</v>
       </c>
       <c r="AX25" s="168">
         <f t="shared" si="51"/>
-        <v>0.38271604938271603</v>
+        <v>0.39611691463543314</v>
       </c>
       <c r="AY25" s="110">
         <f t="shared" si="45"/>
@@ -12727,11 +12728,11 @@
       </c>
       <c r="BA25" s="216">
         <f t="shared" si="42"/>
-        <v>5850</v>
+        <v>5723</v>
       </c>
       <c r="BB25" s="112">
-        <f>3056+571</f>
-        <v>3627</v>
+        <f>3056+698</f>
+        <v>3754</v>
       </c>
       <c r="BC25" s="111">
         <v>3663</v>
@@ -12799,19 +12800,19 @@
       </c>
       <c r="E26" s="158">
         <f t="shared" si="1"/>
-        <v>0.8042504906771345</v>
+        <v>0.80035574092247297</v>
       </c>
       <c r="F26" s="86">
         <f t="shared" si="2"/>
-        <v>26225</v>
+        <v>26098</v>
       </c>
       <c r="G26" s="158">
         <f t="shared" si="3"/>
-        <v>0.19574950932286556</v>
+        <v>0.19964425907752698</v>
       </c>
       <c r="H26" s="145">
         <f t="shared" si="4"/>
-        <v>6383</v>
+        <v>6510</v>
       </c>
       <c r="I26" s="159">
         <f t="shared" si="5"/>
@@ -12953,11 +12954,11 @@
       </c>
       <c r="AW26" s="168">
         <f t="shared" si="50"/>
-        <v>0.31987891019172554</v>
+        <v>0.29424823410696266</v>
       </c>
       <c r="AX26" s="168">
         <f t="shared" si="51"/>
-        <v>0.68012108980827446</v>
+        <v>0.70575176589303734</v>
       </c>
       <c r="AY26" s="110">
         <f t="shared" si="45"/>
@@ -12968,11 +12969,11 @@
       </c>
       <c r="BA26" s="216">
         <f t="shared" si="42"/>
-        <v>1585</v>
+        <v>1458</v>
       </c>
       <c r="BB26" s="112">
-        <f>2799+571</f>
-        <v>3370</v>
+        <f>2799+698</f>
+        <v>3497</v>
       </c>
       <c r="BC26" s="111">
         <v>1516</v>
@@ -13040,19 +13041,19 @@
       </c>
       <c r="E27" s="158">
         <f t="shared" si="1"/>
-        <v>0.75755329662572357</v>
+        <v>0.75307073274036429</v>
       </c>
       <c r="F27" s="86">
         <f t="shared" si="2"/>
-        <v>21463</v>
+        <v>21336</v>
       </c>
       <c r="G27" s="158">
         <f t="shared" si="3"/>
-        <v>0.24244670337427643</v>
+        <v>0.24692926725963574</v>
       </c>
       <c r="H27" s="145">
         <f t="shared" si="4"/>
-        <v>6869</v>
+        <v>6996</v>
       </c>
       <c r="I27" s="159">
         <f t="shared" si="5"/>
@@ -13194,11 +13195,11 @@
       </c>
       <c r="AW27" s="168">
         <f t="shared" si="50"/>
-        <v>0.2532139577594123</v>
+        <v>0.22405876951331496</v>
       </c>
       <c r="AX27" s="168">
         <f t="shared" si="51"/>
-        <v>0.74678604224058764</v>
+        <v>0.77594123048668506</v>
       </c>
       <c r="AY27" s="110">
         <f t="shared" si="45"/>
@@ -13209,11 +13210,11 @@
       </c>
       <c r="BA27" s="216">
         <f t="shared" si="42"/>
-        <v>1103</v>
+        <v>976</v>
       </c>
       <c r="BB27" s="112">
-        <f>2682+571</f>
-        <v>3253</v>
+        <f>2682+698</f>
+        <v>3380</v>
       </c>
       <c r="BC27" s="111">
         <v>1880</v>
@@ -13281,19 +13282,19 @@
       </c>
       <c r="E28" s="158">
         <f t="shared" si="1"/>
-        <v>0.87540436368642027</v>
+        <v>0.87321907908321283</v>
       </c>
       <c r="F28" s="86">
         <f t="shared" si="2"/>
-        <v>50875</v>
+        <v>50748</v>
       </c>
       <c r="G28" s="158">
         <f t="shared" si="3"/>
-        <v>0.12459563631357974</v>
+        <v>0.12678092091678711</v>
       </c>
       <c r="H28" s="145">
         <f t="shared" si="4"/>
-        <v>7241</v>
+        <v>7368</v>
       </c>
       <c r="I28" s="159">
         <f t="shared" si="5"/>
@@ -13435,11 +13436,11 @@
       </c>
       <c r="AW28" s="168">
         <f t="shared" si="50"/>
-        <v>0.65343511450381675</v>
+        <v>0.64050890585241727</v>
       </c>
       <c r="AX28" s="168">
         <f t="shared" si="51"/>
-        <v>0.34656488549618319</v>
+        <v>0.35949109414758268</v>
       </c>
       <c r="AY28" s="110">
         <f t="shared" si="45"/>
@@ -13450,11 +13451,11 @@
       </c>
       <c r="BA28" s="216">
         <f t="shared" si="42"/>
-        <v>6420</v>
+        <v>6293</v>
       </c>
       <c r="BB28" s="112">
-        <f>2834+571</f>
-        <v>3405</v>
+        <f>2834+698</f>
+        <v>3532</v>
       </c>
       <c r="BC28" s="111">
         <v>4068</v>
@@ -13522,19 +13523,19 @@
       </c>
       <c r="E29" s="158">
         <f t="shared" si="1"/>
-        <v>0.8783716366780856</v>
+        <v>0.876259686699704</v>
       </c>
       <c r="F29" s="86">
         <f t="shared" si="2"/>
-        <v>52820</v>
+        <v>52693</v>
       </c>
       <c r="G29" s="158">
         <f t="shared" si="3"/>
-        <v>0.12162836332191439</v>
+        <v>0.123740313300296</v>
       </c>
       <c r="H29" s="145">
         <f t="shared" si="4"/>
-        <v>7314</v>
+        <v>7441</v>
       </c>
       <c r="I29" s="159">
         <f t="shared" si="5"/>
@@ -13676,11 +13677,11 @@
       </c>
       <c r="AW29" s="168">
         <f t="shared" si="50"/>
-        <v>0.65856841682561995</v>
+        <v>0.64581869290231908</v>
       </c>
       <c r="AX29" s="168">
         <f t="shared" si="51"/>
-        <v>0.3414315831743801</v>
+        <v>0.35418130709768098</v>
       </c>
       <c r="AY29" s="110">
         <f t="shared" si="45"/>
@@ -13691,11 +13692,11 @@
       </c>
       <c r="BA29" s="216">
         <f t="shared" si="42"/>
-        <v>6560</v>
+        <v>6433</v>
       </c>
       <c r="BB29" s="112">
-        <f>2830+571</f>
-        <v>3401</v>
+        <f>2830+698</f>
+        <v>3528</v>
       </c>
       <c r="BC29" s="111">
         <v>4131</v>
@@ -13763,19 +13764,19 @@
       </c>
       <c r="E30" s="158">
         <f t="shared" si="1"/>
-        <v>0.87335953520164045</v>
+        <v>0.87118933697881062</v>
       </c>
       <c r="F30" s="86">
         <f t="shared" si="2"/>
-        <v>51109</v>
+        <v>50982</v>
       </c>
       <c r="G30" s="158">
         <f t="shared" si="3"/>
-        <v>0.12664046479835953</v>
+        <v>0.12881066302118935</v>
       </c>
       <c r="H30" s="145">
         <f t="shared" si="4"/>
-        <v>7411</v>
+        <v>7538</v>
       </c>
       <c r="I30" s="159">
         <f t="shared" si="5"/>
@@ -13917,11 +13918,11 @@
       </c>
       <c r="AW30" s="168">
         <f t="shared" si="50"/>
-        <v>0.64502564102564097</v>
+        <v>0.63200000000000001</v>
       </c>
       <c r="AX30" s="168">
         <f t="shared" si="51"/>
-        <v>0.35497435897435897</v>
+        <v>0.36799999999999999</v>
       </c>
       <c r="AY30" s="110">
         <f t="shared" si="45"/>
@@ -13932,11 +13933,11 @@
       </c>
       <c r="BA30" s="216">
         <f t="shared" si="42"/>
-        <v>6289</v>
+        <v>6162</v>
       </c>
       <c r="BB30" s="112">
-        <f>2890+571</f>
-        <v>3461</v>
+        <f>2890+698</f>
+        <v>3588</v>
       </c>
       <c r="BC30" s="111">
         <v>3980</v>
@@ -14004,19 +14005,19 @@
       </c>
       <c r="E31" s="158">
         <f t="shared" si="1"/>
-        <v>0.8759146445223428</v>
+        <v>0.87375353095327235</v>
       </c>
       <c r="F31" s="86">
         <f t="shared" si="2"/>
-        <v>51474</v>
+        <v>51347</v>
       </c>
       <c r="G31" s="158">
         <f t="shared" si="3"/>
-        <v>0.12408535547765714</v>
+        <v>0.12624646904672771</v>
       </c>
       <c r="H31" s="145">
         <f t="shared" si="4"/>
-        <v>7292</v>
+        <v>7419</v>
       </c>
       <c r="I31" s="159">
         <f t="shared" si="5"/>
@@ -14158,11 +14159,11 @@
       </c>
       <c r="AW31" s="168">
         <f t="shared" si="50"/>
-        <v>0.64926758819888586</v>
+        <v>0.63616670105219719</v>
       </c>
       <c r="AX31" s="168">
         <f t="shared" si="51"/>
-        <v>0.35073241180111409</v>
+        <v>0.36383329894780275</v>
       </c>
       <c r="AY31" s="110">
         <f t="shared" si="45"/>
@@ -14173,11 +14174,11 @@
       </c>
       <c r="BA31" s="216">
         <f t="shared" si="42"/>
-        <v>6294</v>
+        <v>6167</v>
       </c>
       <c r="BB31" s="112">
-        <f>2829+571</f>
-        <v>3400</v>
+        <f>2829+698</f>
+        <v>3527</v>
       </c>
       <c r="BC31" s="111">
         <v>3828</v>
@@ -14245,19 +14246,19 @@
       </c>
       <c r="E32" s="158">
         <f t="shared" si="1"/>
-        <v>0.87547984644913623</v>
+        <v>0.87330340005483964</v>
       </c>
       <c r="F32" s="86">
         <f t="shared" si="2"/>
-        <v>51086</v>
+        <v>50959</v>
       </c>
       <c r="G32" s="158">
         <f t="shared" si="3"/>
-        <v>0.12452015355086372</v>
+        <v>0.12669659994516042</v>
       </c>
       <c r="H32" s="145">
         <f t="shared" si="4"/>
-        <v>7266</v>
+        <v>7393</v>
       </c>
       <c r="I32" s="159">
         <f t="shared" si="5"/>
@@ -14399,11 +14400,11 @@
       </c>
       <c r="AW32" s="168">
         <f t="shared" si="50"/>
-        <v>0.6475171410762518</v>
+        <v>0.63432370662788284</v>
       </c>
       <c r="AX32" s="168">
         <f t="shared" si="51"/>
-        <v>0.3524828589237482</v>
+        <v>0.36567629337211716</v>
       </c>
       <c r="AY32" s="110">
         <f t="shared" si="45"/>
@@ -14414,11 +14415,11 @@
       </c>
       <c r="BA32" s="216">
         <f t="shared" si="42"/>
-        <v>6233</v>
+        <v>6106</v>
       </c>
       <c r="BB32" s="112">
-        <f>2822+571</f>
-        <v>3393</v>
+        <f>2822+698</f>
+        <v>3520</v>
       </c>
       <c r="BC32" s="111">
         <v>3803</v>
@@ -14486,19 +14487,19 @@
       </c>
       <c r="E33" s="158">
         <f t="shared" si="1"/>
-        <v>0.78651109503135552</v>
+        <v>0.78268210323203091</v>
       </c>
       <c r="F33" s="86">
         <f t="shared" si="2"/>
-        <v>26087</v>
+        <v>25960</v>
       </c>
       <c r="G33" s="158">
         <f t="shared" si="3"/>
-        <v>0.21348890496864448</v>
+        <v>0.21731789676796912</v>
       </c>
       <c r="H33" s="145">
         <f t="shared" si="4"/>
-        <v>7081</v>
+        <v>7208</v>
       </c>
       <c r="I33" s="159">
         <f t="shared" si="5"/>
@@ -14640,11 +14641,11 @@
       </c>
       <c r="AW33" s="168">
         <f t="shared" si="50"/>
-        <v>0.31881390593047032</v>
+        <v>0.29284253578732106</v>
       </c>
       <c r="AX33" s="168">
         <f t="shared" si="51"/>
-        <v>0.68118609406952968</v>
+        <v>0.70715746421267889</v>
       </c>
       <c r="AY33" s="110">
         <f t="shared" si="45"/>
@@ -14655,11 +14656,11 @@
       </c>
       <c r="BA33" s="216">
         <f t="shared" si="42"/>
-        <v>1559</v>
+        <v>1432</v>
       </c>
       <c r="BB33" s="112">
-        <f>2760+571</f>
-        <v>3331</v>
+        <f>2760+698</f>
+        <v>3458</v>
       </c>
       <c r="BC33" s="111">
         <v>1824</v>
@@ -14727,19 +14728,19 @@
       </c>
       <c r="E34" s="158">
         <f t="shared" si="1"/>
-        <v>0.75030050201513121</v>
+        <v>0.74581064837728916</v>
       </c>
       <c r="F34" s="86">
         <f t="shared" si="2"/>
-        <v>21223</v>
+        <v>21096</v>
       </c>
       <c r="G34" s="158">
         <f t="shared" si="3"/>
-        <v>0.24969949798486885</v>
+        <v>0.25418935162271089</v>
       </c>
       <c r="H34" s="145">
         <f t="shared" si="4"/>
-        <v>7063</v>
+        <v>7190</v>
       </c>
       <c r="I34" s="159">
         <f t="shared" si="5"/>
@@ -14880,11 +14881,11 @@
       </c>
       <c r="AW34" s="168">
         <f t="shared" si="50"/>
-        <v>0.2488849241748439</v>
+        <v>0.22056199821587869</v>
       </c>
       <c r="AX34" s="168">
         <f t="shared" si="51"/>
-        <v>0.75111507582515613</v>
+        <v>0.77943800178412137</v>
       </c>
       <c r="AY34" s="110">
         <f t="shared" si="45"/>
@@ -14895,11 +14896,11 @@
       </c>
       <c r="BA34" s="216">
         <f t="shared" si="42"/>
-        <v>1116</v>
+        <v>989</v>
       </c>
       <c r="BB34" s="112">
-        <f>2797+571</f>
-        <v>3368</v>
+        <f>2797+698</f>
+        <v>3495</v>
       </c>
       <c r="BC34" s="111">
         <v>1401</v>
@@ -14967,19 +14968,19 @@
       </c>
       <c r="E35" s="158">
         <f t="shared" si="1"/>
-        <v>0.75188863092725489</v>
+        <v>0.74742120444632065</v>
       </c>
       <c r="F35" s="86">
         <f t="shared" si="2"/>
-        <v>21374.690000000002</v>
+        <v>21247.690000000002</v>
       </c>
       <c r="G35" s="158">
         <f t="shared" si="3"/>
-        <v>0.24811136907274517</v>
+        <v>0.25257879555367946</v>
       </c>
       <c r="H35" s="145">
         <f t="shared" si="4"/>
-        <v>7053.3099999999995</v>
+        <v>7180.3099999999995</v>
       </c>
       <c r="I35" s="159">
         <f t="shared" si="5"/>
@@ -15121,11 +15122,11 @@
       </c>
       <c r="AW35" s="168">
         <f t="shared" si="50"/>
-        <v>0.263954814652336</v>
+        <v>0.23609782847115593</v>
       </c>
       <c r="AX35" s="168">
         <f t="shared" si="51"/>
-        <v>0.73604518534766394</v>
+        <v>0.7639021715288441</v>
       </c>
       <c r="AY35" s="110">
         <f t="shared" si="45"/>
@@ -15136,11 +15137,11 @@
       </c>
       <c r="BA35" s="216">
         <f t="shared" si="42"/>
-        <v>1203.3699999999999</v>
+        <v>1076.3699999999999</v>
       </c>
       <c r="BB35" s="112">
-        <f>2784.63+571</f>
-        <v>3355.63</v>
+        <f>2784.63+698</f>
+        <v>3482.63</v>
       </c>
       <c r="BC35" s="111">
         <v>1438.3</v>
@@ -15208,19 +15209,19 @@
       </c>
       <c r="E36" s="158">
         <f t="shared" si="1"/>
-        <v>0.87303796173130044</v>
+        <v>0.87087213070022851</v>
       </c>
       <c r="F36" s="86">
         <f t="shared" si="2"/>
-        <v>51193.2</v>
+        <v>51066.2</v>
       </c>
       <c r="G36" s="158">
         <f t="shared" si="3"/>
-        <v>0.12696203826869948</v>
+        <v>0.12912786929977149</v>
       </c>
       <c r="H36" s="145">
         <f t="shared" si="4"/>
-        <v>7444.8</v>
+        <v>7571.8</v>
       </c>
       <c r="I36" s="159">
         <f t="shared" si="5"/>
@@ -15362,11 +15363,11 @@
       </c>
       <c r="AW36" s="168">
         <f t="shared" si="50"/>
-        <v>0.64051625636231435</v>
+        <v>0.62732419237561021</v>
       </c>
       <c r="AX36" s="168">
         <f t="shared" si="51"/>
-        <v>0.35948374363768565</v>
+        <v>0.37267580762438973</v>
       </c>
       <c r="AY36" s="110">
         <f t="shared" si="45"/>
@@ -15377,11 +15378,11 @@
       </c>
       <c r="BA36" s="216">
         <f t="shared" si="42"/>
-        <v>6166.25</v>
+        <v>6039.25</v>
       </c>
       <c r="BB36" s="112">
-        <f>2889.75+571</f>
-        <v>3460.75</v>
+        <f>2889.75+698</f>
+        <v>3587.75</v>
       </c>
       <c r="BC36" s="111">
         <v>3669.13</v>
@@ -15646,6 +15647,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="D1:P2"/>
+    <mergeCell ref="R1:AA2"/>
+    <mergeCell ref="AC1:AK2"/>
+    <mergeCell ref="AM1:AU2"/>
+    <mergeCell ref="AO3:AQ3"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:AA3"/>
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="AD3:AD4"/>
+    <mergeCell ref="AE3:AG3"/>
+    <mergeCell ref="AH3:AK3"/>
+    <mergeCell ref="AM3:AM4"/>
     <mergeCell ref="BJ1:BR2"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
@@ -15662,22 +15679,6 @@
     <mergeCell ref="AX3:AX4"/>
     <mergeCell ref="AY3:BB3"/>
     <mergeCell ref="BC3:BH3"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="D1:P2"/>
-    <mergeCell ref="R1:AA2"/>
-    <mergeCell ref="AC1:AK2"/>
-    <mergeCell ref="AM1:AU2"/>
-    <mergeCell ref="AO3:AQ3"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="M3:P3"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:AA3"/>
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="AD3:AD4"/>
-    <mergeCell ref="AE3:AG3"/>
-    <mergeCell ref="AH3:AK3"/>
-    <mergeCell ref="AM3:AM4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="88" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -19997,15 +19998,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E3C748FF7EC2ED4E8EAD43CD1EEC2D0E" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ea203103aa5aa41fa7dd49b43cb8a2de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xmlns:ns3="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49b0a91519af75797ffa607b75695ffb" ns2:_="" ns3:_="">
     <xsd:import namespace="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
@@ -20252,6 +20244,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -20266,14 +20267,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F8AAD19-02EA-4280-B365-8810DF5CEEF3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3450C23-B9A2-45D4-8942-0C308DF3F8F2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20292,6 +20285,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F8AAD19-02EA-4280-B365-8810DF5CEEF3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5BCA511-7B91-4B72-B4F3-8175C2C806EF}">
   <ds:schemaRefs>
